--- a/docs/test-cases/SPM-28_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-28_Test_Cases.xlsx
@@ -4,21 +4,22 @@
   <workbookPr/>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="TC01" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="TC02" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="TC03" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="TC04" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="TC05" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="TC06" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TC07" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="TC08" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="TC09" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="TC10" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="TC11" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="TC12" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="TC13" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="TC14" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="TC15" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Open Questions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TC01" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="TC02" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="TC03" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="TC04" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="TC05" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TC06" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="TC07" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TC08" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="TC09" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="TC10" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="TC11" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="TC12" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="TC13" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="TC14" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="TC15" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -158,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -247,6 +248,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -538,12 +545,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1" s="32">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="35" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="35" t="inlineStr">
         <is>
           <t>SPM-28: As an Event Coordinator, I want to review a submitted event request so that I can determine whether sufficient information is available to proceed with planning</t>
         </is>
@@ -555,32 +562,32 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="35" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="35" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="35" t="inlineStr">
         <is>
           <t>Linked AC</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="35" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="35" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -607,27 +614,27 @@
           <t>TC01</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="36" t="inlineStr">
         <is>
           <t>SPM-28-TC01</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="36" t="inlineStr">
         <is>
           <t>Review Queue lists only the Under review events assigned to the logged-in coordinator</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="36" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="36" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="36" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -646,27 +653,27 @@
           <t>TC02</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>SPM-28-TC02</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>Events past review are not in the coordinator's Review Queue</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="36" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -685,7 +692,7 @@
           <t>TC03</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>SPM-28-TC03</t>
         </is>
@@ -695,17 +702,17 @@
           <t>A coordinator cannot review an event assigned to another coordinator</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="36" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -724,27 +731,27 @@
           <t>TC04</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>SPM-28-TC04</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>Non-coordinator roles cannot open the Review Queue</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="36" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="36" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -763,27 +770,27 @@
           <t>TC05</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>SPM-28-TC05</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>Review page displays all requirements of the request</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="36" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -802,27 +809,27 @@
           <t>TC06</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>SPM-28-TC06</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>Missing information is clearly flagged on the review page</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="36" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -841,27 +848,27 @@
           <t>TC07</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>SPM-28-TC07</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>Assigned coordinator can start a review from the event page</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="36" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -880,27 +887,27 @@
           <t>TC08</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>SPM-28-TC08</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="36" t="inlineStr">
         <is>
           <t>Coordinator approves a request for planning</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="36" t="inlineStr">
         <is>
           <t>AC4, AC6</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="36" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="36" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -919,27 +926,27 @@
           <t>TC09</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>SPM-28-TC09</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t>Cancelling the approve confirmation leaves the request unchanged</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="36" t="inlineStr">
         <is>
           <t>AC4, AC6</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="36" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="36" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1187,20 +1194,21 @@
       <c r="I18" s="22" t="n"/>
     </row>
     <row r="19"/>
+    <row r="20"/>
     <row r="21" ht="15.75" customHeight="1" s="32">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
         </is>
       </c>
       <c r="C21" s="33" t="n"/>
       <c r="D21" s="34" t="n"/>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="35" t="inlineStr">
         <is>
           <t>Covered by</t>
         </is>
@@ -1208,19 +1216,19 @@
       <c r="F21" s="34" t="n"/>
     </row>
     <row r="22" ht="71.25" customHeight="1" s="32">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="36" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="36" t="inlineStr">
         <is>
           <t>The Event Coordinator can view submitted event requests they are authorised to review.</t>
         </is>
       </c>
       <c r="C22" s="33" t="n"/>
       <c r="D22" s="34" t="n"/>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="36" t="inlineStr">
         <is>
           <t>SPM-28-TC01
 SPM-28-TC02
@@ -1232,19 +1240,19 @@
       <c r="F22" s="34" t="n"/>
     </row>
     <row r="23" ht="17.25" customHeight="1" s="32">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="36" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="36" t="inlineStr">
         <is>
           <t>All relevant event requirements are displayed.</t>
         </is>
       </c>
       <c r="C23" s="33" t="n"/>
       <c r="D23" s="34" t="n"/>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="36" t="inlineStr">
         <is>
           <t>SPM-28-TC05</t>
         </is>
@@ -1252,19 +1260,19 @@
       <c r="F23" s="34" t="n"/>
     </row>
     <row r="24" ht="17.25" customHeight="1" s="32">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="36" t="inlineStr">
         <is>
           <t>The Event Coordinator can identify incomplete or unclear information.</t>
         </is>
       </c>
       <c r="C24" s="33" t="n"/>
       <c r="D24" s="34" t="n"/>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="36" t="inlineStr">
         <is>
           <t>SPM-28-TC06</t>
         </is>
@@ -1272,19 +1280,19 @@
       <c r="F24" s="34" t="n"/>
     </row>
     <row r="25" ht="44.25" customHeight="1" s="32">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="36" t="inlineStr">
         <is>
           <t>The Event Coordinator can approve the request for planning.</t>
         </is>
       </c>
       <c r="C25" s="33" t="n"/>
       <c r="D25" s="34" t="n"/>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="36" t="inlineStr">
         <is>
           <t>SPM-28-TC08
 SPM-28-TC09
@@ -1294,19 +1302,19 @@
       <c r="F25" s="34" t="n"/>
     </row>
     <row r="26" ht="71.25" customHeight="1" s="32">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="36" t="inlineStr">
         <is>
           <t>The Event Coordinator can reject the request.</t>
         </is>
       </c>
       <c r="C26" s="33" t="n"/>
       <c r="D26" s="34" t="n"/>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="36" t="inlineStr">
         <is>
           <t>SPM-28-TC10
 SPM-28-TC11
@@ -1318,19 +1326,19 @@
       <c r="F26" s="34" t="n"/>
     </row>
     <row r="27" ht="71.25" customHeight="1" s="32">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="36" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="36" t="inlineStr">
         <is>
           <t>The event status is updated according to the review outcome.</t>
         </is>
       </c>
       <c r="C27" s="33" t="n"/>
       <c r="D27" s="34" t="n"/>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="36" t="inlineStr">
         <is>
           <t>SPM-28-TC08
 SPM-28-TC09
@@ -1343,12 +1351,12 @@
     </row>
     <row r="28" ht="15.75" customHeight="1" s="32"/>
     <row r="29" ht="192.75" customHeight="1" s="32">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="35" t="inlineStr">
         <is>
           <t>Code reviewed</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="36" t="inlineStr">
         <is>
           <t>scripts/seed-spm28.ts
 design/mockups/EventReview.dc.html
@@ -2411,13 +2419,13 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-28-TC09</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="98.25" customHeight="1" s="32">
+      <c r="B2" s="36" t="inlineStr">
+        <is>
+          <t>SPM-28-TC08</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="179.25" customHeight="1" s="32">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2426,12 +2434,13 @@
       <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm28` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM28 …' events, EVT-000124 to EVT-000130, never anyone else's data).
- Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), Event Coordinator.
- 'SPM28 Nusantara Product Launch' review page is open.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="57.75" customHeight="1" s="32">
+ Before: run `npm run fixtures:spm28` so 'SPM28 Harbourline Client Seminar' is back to Under review.
+ Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), coordinator of 'SPM28 Harbourline Client Seminar' (Under review).
+ After: run `npm run fixtures:spm28` so the next tester starts from the same state. It deletes and recreates only the 'SPM28 …' events - do NOT run `npx prisma db seed`, which wipes everyone's data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="111.75" customHeight="1" s="32">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2439,14 +2448,17 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>1. Select 'Approve — planning can start'
- 2. Click 'Approve request'
- 3. Click 'Cancel' in the dialog
- 4. Click 'Review Queue' in the sidebar</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30.75" customHeight="1" s="32">
+          <t>1. Click 'Review Queue' in the sidebar
+ 2. Click 'SPM28 Harbourline Client Seminar'
+ 3. Select 'Approve — planning can start'
+ 4. Click 'Approve request'
+ 5. Click 'Approve' in the dialog
+ 6. Click 'Review Queue' in the sidebar
+ 7. Click 'All Events' in the sidebar and look for 'SPM28 Harbourline Client Seminar'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="32">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -2454,11 +2466,11 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Event: SPM28 Nusantara Product Launch (EVT-000124) | Outcome: Approve, then cancelled</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="84.75" customHeight="1" s="32">
+          <t>Event: SPM28 Harbourline Client Seminar (EVT-000125) | Outcome: Approve</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="206.25" customHeight="1" s="32">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -2466,10 +2478,12 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Step 1: The option is highlighted and an 'Approve request' button is shown.
- Step 2: The 'Approve this request?' dialog appears.
- Step 3: The dialog closes, no success message is shown, and the status badge still shows 'Under review'.
- Step 4: 'SPM28 Nusantara Product Launch' is still listed.</t>
+          <t>Step 2: The 'Review request' page opens with the 'Under review' badge.
+ Step 3: The option is highlighted and an 'Approve request' button is shown.
+ Step 4: A dialog 'Approve this request?' appears, saying the event moves from Under review to Approved. The status has not changed yet.
+ Step 5: A green 'Request approved' alert reads '"SPM28 Harbourline Client Seminar" is now Approved. Planning can start.' The status badge changes from 'Under review' to 'Approved' and the 'Your decision' card disappears.
+ Step 6: 'SPM28 Harbourline Client Seminar' is no longer listed.
+ Step 7: The event page shows the 'Approved' status badge, and no 'This request is waiting for your review' alert.</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2493,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -2513,10 +2527,12 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Step 1: The option is highlighted and an 'Approve request' button is shown.
- Step 2: The 'Approve this request?' dialog appears.
- Step 3: The dialog closes, no success message is shown, and the status badge still shows 'Under review'.
- Step 4: 'SPM28 Nusantara Product Launch' is still listed.</t>
+          <t>Step 2: The 'Review request' page opens with the 'Under review' badge.
+ Step 3: The option is highlighted and an 'Approve request' button is shown.
+ Step 4: A dialog 'Approve this request?' appears, saying the event moves from Under review to Approved. The status has not changed yet.
+ Step 5: A green 'Request approved' alert reads '"SPM28 Harbourline Client Seminar" is now Approved. Planning can start.' The status badge changes from 'Under review' to 'Approved' and the 'Your decision' card disappears.
+ Step 6: 'SPM28 Harbourline Client Seminar' is no longer listed.
+ Step 7: The event page shows the 'Approved' status badge, and no 'This request is waiting for your review' alert.</t>
         </is>
       </c>
     </row>
@@ -2583,10 +2599,12 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Step 1: The option is highlighted and an 'Approve request' button is shown.
- Step 2: The 'Approve this request?' dialog appears.
- Step 3: The dialog closes, no success message is shown, and the status badge still shows 'Under review'.
- Step 4: 'SPM28 Nusantara Product Launch' is still listed.</t>
+          <t>Step 2: The 'Review request' page opens with the 'Under review' badge.
+ Step 3: The option is highlighted and an 'Approve request' button is shown.
+ Step 4: A dialog 'Approve this request?' appears, saying the event moves from Under review to Approved. The status has not changed yet.
+ Step 5: A green 'Request approved' alert reads '"SPM28 Harbourline Client Seminar" is now Approved. Planning can start.' The status badge changes from 'Under review' to 'Approved' and the 'Your decision' card disappears.
+ Step 6: 'SPM28 Harbourline Client Seminar' is no longer listed.
+ Step 7: The event page shows the 'Approved' status badge, and no 'This request is waiting for your review' alert.</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2614,7 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2608,7 +2626,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2632,7 +2650,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B22" s="31" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -3648,13 +3666,13 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-28-TC10</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="179.25" customHeight="1" s="32">
+      <c r="B2" s="36" t="inlineStr">
+        <is>
+          <t>SPM-28-TC09</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="98.25" customHeight="1" s="32">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3663,12 +3681,12 @@
       <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm28` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM28 …' events, EVT-000124 to EVT-000130, never anyone else's data).
- Before: run `npm run fixtures:spm28` so 'SPM28 Kirana Regional Offsite' is back to Under review.
- Logged in as Priya Raj (priya.raj@connectsphere.com / password123), Event Coordinator assigned to 'SPM28 Kirana Regional Offsite' (Under review).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="84.75" customHeight="1" s="32">
+ Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), Event Coordinator.
+ 'SPM28 Nusantara Product Launch' review page is open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="57.75" customHeight="1" s="32">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -3676,16 +3694,14 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>1. Click 'Review Queue' in the sidebar
- 2. Click 'SPM28 Kirana Regional Offsite'
- 3. Select 'Reject this request'
- 4. Type the reason into 'Reason for rejection'
- 5. Click 'Reject request'
- 6. Click 'Review Queue' in the sidebar</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.25" customHeight="1" s="32">
+          <t>1. Select 'Approve — planning can start'
+ 2. Click 'Approve request'
+ 3. Click 'Cancel' in the dialog
+ 4. Click 'Review Queue' in the sidebar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30.75" customHeight="1" s="32">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -3693,11 +3709,11 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Event: SPM28 Kirana Regional Offsite (EVT-000126) | Reason for rejection: Headcount was not confirmed after two reminders; please resubmit once numbers are final.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="138.75" customHeight="1" s="32">
+          <t>Event: SPM28 Nusantara Product Launch (EVT-000124) | Outcome: Approve, then cancelled</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="84.75" customHeight="1" s="32">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -3705,10 +3721,10 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Step 2: The 'Review request' page opens with the 'Under review' badge.
- Step 3: The 'Reason for rejection' field (marked required) and the 'Reject request' and 'Cancel' buttons appear.
- Step 5: A green 'Request rejected' alert reads '"SPM28 Kirana Regional Offsite" is now Rejected. The organiser can see your reason on the event.' followed by 'Reason:' and the reason exactly as typed. The status badge changes from 'Under review' to 'Rejected'.
- Step 6: 'SPM28 Kirana Regional Offsite' is no longer listed.</t>
+          <t>Step 1: The option is highlighted and an 'Approve request' button is shown.
+ Step 2: The 'Approve this request?' dialog appears.
+ Step 3: The dialog closes, no success message is shown, and the status badge still shows 'Under review'.
+ Step 4: 'SPM28 Nusantara Product Launch' is still listed.</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3734,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -3752,10 +3768,10 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Step 2: The 'Review request' page opens with the 'Under review' badge.
- Step 3: The 'Reason for rejection' field (marked required) and the 'Reject request' and 'Cancel' buttons appear.
- Step 5: A green 'Request rejected' alert reads '"SPM28 Kirana Regional Offsite" is now Rejected. The organiser can see your reason on the event.' followed by 'Reason:' and the reason exactly as typed. The status badge changes from 'Under review' to 'Rejected'.
- Step 6: 'SPM28 Kirana Regional Offsite' is no longer listed.</t>
+          <t>Step 1: The option is highlighted and an 'Approve request' button is shown.
+ Step 2: The 'Approve this request?' dialog appears.
+ Step 3: The dialog closes, no success message is shown, and the status badge still shows 'Under review'.
+ Step 4: 'SPM28 Nusantara Product Launch' is still listed.</t>
         </is>
       </c>
     </row>
@@ -3822,10 +3838,10 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Step 2: The 'Review request' page opens with the 'Under review' badge.
- Step 3: The 'Reason for rejection' field (marked required) and the 'Reject request' and 'Cancel' buttons appear.
- Step 5: A green 'Request rejected' alert reads '"SPM28 Kirana Regional Offsite" is now Rejected. The organiser can see your reason on the event.' followed by 'Reason:' and the reason exactly as typed. The status badge changes from 'Under review' to 'Rejected'.
- Step 6: 'SPM28 Kirana Regional Offsite' is no longer listed.</t>
+          <t>Step 1: The option is highlighted and an 'Approve request' button is shown.
+ Step 2: The 'Approve this request?' dialog appears.
+ Step 3: The dialog closes, no success message is shown, and the status badge still shows 'Under review'.
+ Step 4: 'SPM28 Nusantara Product Launch' is still listed.</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3851,7 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3847,7 +3863,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -3871,7 +3887,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B22" s="31" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -4887,13 +4903,13 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-28-TC11</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="125.25" customHeight="1" s="32">
+      <c r="B2" s="36" t="inlineStr">
+        <is>
+          <t>SPM-28-TC10</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="179.25" customHeight="1" s="32">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -4901,13 +4917,13 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>SPM-28-TC10 has just been run ('SPM28 Kirana Regional Offsite' rejected by Priya Raj).
- Logged in as Faridah Aziz (faridah.aziz@kiranaretail.com / password123), Event Organiser of 'SPM28 Kirana Regional Offsite'.
- After: run `npm run fixtures:spm28` so the next tester starts from the same state. It deletes and recreates only the 'SPM28 …' events - do NOT run `npx prisma db seed`, which wipes everyone's data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30.75" customHeight="1" s="32">
+          <t>Test data loaded: `npm run fixtures:spm28` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM28 …' events, EVT-000124 to EVT-000130, never anyone else's data).
+ Before: run `npm run fixtures:spm28` so 'SPM28 Kirana Regional Offsite' is back to Under review.
+ Logged in as Priya Raj (priya.raj@connectsphere.com / password123), Event Coordinator assigned to 'SPM28 Kirana Regional Offsite' (Under review).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="84.75" customHeight="1" s="32">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -4915,12 +4931,16 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>1. Click 'My Events' in the sidebar
- 2. Click 'SPM28 Kirana Regional Offsite'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30.75" customHeight="1" s="32">
+          <t>1. Click 'Review Queue' in the sidebar
+ 2. Click 'SPM28 Kirana Regional Offsite'
+ 3. Select 'Reject this request'
+ 4. Type the reason into 'Reason for rejection'
+ 5. Click 'Reject request'
+ 6. Click 'Review Queue' in the sidebar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.25" customHeight="1" s="32">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -4928,11 +4948,11 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Expected reason: Headcount was not confirmed after two reminders; please resubmit once numbers are final.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="71.25" customHeight="1" s="32">
+          <t>Event: SPM28 Kirana Regional Offsite (EVT-000126) | Reason for rejection: Headcount was not confirmed after two reminders; please resubmit once numbers are final.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="138.75" customHeight="1" s="32">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -4940,8 +4960,10 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Step 1: 'SPM28 Kirana Regional Offsite' is listed with the 'Rejected' badge.
- Step 2: A red alert banner at the top of the Overview reads 'This request was rejected' followed by the reason exactly as Priya Raj typed it.</t>
+          <t>Step 2: The 'Review request' page opens with the 'Under review' badge.
+ Step 3: The 'Reason for rejection' field (marked required) and the 'Reject request' and 'Cancel' buttons appear.
+ Step 5: A green 'Request rejected' alert reads '"SPM28 Kirana Regional Offsite" is now Rejected. The organiser can see your reason on the event.' followed by 'Reason:' and the reason exactly as typed. The status badge changes from 'Under review' to 'Rejected'.
+ Step 6: 'SPM28 Kirana Regional Offsite' is no longer listed.</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4973,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -4985,8 +5007,10 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Step 1: 'SPM28 Kirana Regional Offsite' is listed with the 'Rejected' badge.
- Step 2: A red alert banner at the top of the Overview reads 'This request was rejected' followed by the reason exactly as Priya Raj typed it.</t>
+          <t>Step 2: The 'Review request' page opens with the 'Under review' badge.
+ Step 3: The 'Reason for rejection' field (marked required) and the 'Reject request' and 'Cancel' buttons appear.
+ Step 5: A green 'Request rejected' alert reads '"SPM28 Kirana Regional Offsite" is now Rejected. The organiser can see your reason on the event.' followed by 'Reason:' and the reason exactly as typed. The status badge changes from 'Under review' to 'Rejected'.
+ Step 6: 'SPM28 Kirana Regional Offsite' is no longer listed.</t>
         </is>
       </c>
     </row>
@@ -5053,8 +5077,10 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Step 1: 'SPM28 Kirana Regional Offsite' is listed with the 'Rejected' badge.
- Step 2: A red alert banner at the top of the Overview reads 'This request was rejected' followed by the reason exactly as Priya Raj typed it.</t>
+          <t>Step 2: The 'Review request' page opens with the 'Under review' badge.
+ Step 3: The 'Reason for rejection' field (marked required) and the 'Reject request' and 'Cancel' buttons appear.
+ Step 5: A green 'Request rejected' alert reads '"SPM28 Kirana Regional Offsite" is now Rejected. The organiser can see your reason on the event.' followed by 'Reason:' and the reason exactly as typed. The status badge changes from 'Under review' to 'Rejected'.
+ Step 6: 'SPM28 Kirana Regional Offsite' is no longer listed.</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5090,7 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5076,7 +5102,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -5100,7 +5126,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B22" s="31" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -6116,13 +6142,13 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-28-TC12</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="98.25" customHeight="1" s="32">
+      <c r="B2" s="36" t="inlineStr">
+        <is>
+          <t>SPM-28-TC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="125.25" customHeight="1" s="32">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -6130,13 +6156,13 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>Test data loaded: `npm run fixtures:spm28` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM28 …' events, EVT-000124 to EVT-000130, never anyone else's data).
- Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), Event Coordinator.
- 'SPM28 Nusantara Product Launch' review page is open.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.25" customHeight="1" s="32">
+          <t>SPM-28-TC10 has just been run ('SPM28 Kirana Regional Offsite' rejected by Priya Raj).
+ Logged in as Faridah Aziz (faridah.aziz@kiranaretail.com / password123), Event Organiser of 'SPM28 Kirana Regional Offsite'.
+ After: run `npm run fixtures:spm28` so the next tester starts from the same state. It deletes and recreates only the 'SPM28 …' events - do NOT run `npx prisma db seed`, which wipes everyone's data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30.75" customHeight="1" s="32">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -6144,13 +6170,12 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>1. Select 'Reject this request'
- 2. Click 'Reject request' without typing a reason
- 3. Click 'Review Queue' in the sidebar</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.25" customHeight="1" s="32">
+          <t>1. Click 'My Events' in the sidebar
+ 2. Click 'SPM28 Kirana Regional Offsite'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30.75" customHeight="1" s="32">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -6158,11 +6183,11 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Reason for rejection: (empty)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="84.75" customHeight="1" s="32">
+          <t>Expected reason: Headcount was not confirmed after two reminders; please resubmit once numbers are final.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="71.25" customHeight="1" s="32">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -6170,9 +6195,8 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Step 1: The 'Reason for rejection' field appears, empty.
- Step 2: The 'Reason for rejection' field is outlined in red with the error 'A reason is required when rejecting. The organiser sees this message.' The status badge still shows 'Under review'.
- Step 3: 'SPM28 Nusantara Product Launch' is still listed.</t>
+          <t>Step 1: 'SPM28 Kirana Regional Offsite' is listed with the 'Rejected' badge.
+ Step 2: A red alert banner at the top of the Overview reads 'This request was rejected' followed by the reason exactly as Priya Raj typed it.</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6206,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -6216,9 +6240,8 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Step 1: The 'Reason for rejection' field appears, empty.
- Step 2: The 'Reason for rejection' field is outlined in red with the error 'A reason is required when rejecting. The organiser sees this message.' The status badge still shows 'Under review'.
- Step 3: 'SPM28 Nusantara Product Launch' is still listed.</t>
+          <t>Step 1: 'SPM28 Kirana Regional Offsite' is listed with the 'Rejected' badge.
+ Step 2: A red alert banner at the top of the Overview reads 'This request was rejected' followed by the reason exactly as Priya Raj typed it.</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6251,7 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6240,7 +6263,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -6252,7 +6275,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -6264,7 +6287,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="31" t="n">
+      <c r="B15" s="27" t="n">
         <v>46295</v>
       </c>
     </row>
@@ -6285,9 +6308,8 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Step 1: The 'Reason for rejection' field appears, empty.
- Step 2: The 'Reason for rejection' field is outlined in red with the error 'A reason is required when rejecting. The organiser sees this message.' The status badge still shows 'Under review'.
- Step 3: 'SPM28 Nusantara Product Launch' is still listed.</t>
+          <t>Step 1: 'SPM28 Kirana Regional Offsite' is listed with the 'Rejected' badge.
+ Step 2: A red alert banner at the top of the Overview reads 'This request was rejected' followed by the reason exactly as Priya Raj typed it.</t>
         </is>
       </c>
     </row>
@@ -6297,7 +6319,7 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6309,7 +6331,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -6333,7 +6355,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B22" s="31" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -7349,9 +7371,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-28-TC13</t>
+      <c r="B2" s="36" t="inlineStr">
+        <is>
+          <t>SPM-28-TC12</t>
         </is>
       </c>
     </row>
@@ -7378,8 +7400,8 @@
       <c r="B4" s="9" t="inlineStr">
         <is>
           <t>1. Select 'Reject this request'
- 2. Type three spaces into 'Reason for rejection'
- 3. Click 'Reject request'</t>
+ 2. Click 'Reject request' without typing a reason
+ 3. Click 'Review Queue' in the sidebar</t>
         </is>
       </c>
     </row>
@@ -7391,11 +7413,11 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Reason for rejection: ' ' (3 spaces)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="57.75" customHeight="1" s="32">
+          <t>Reason for rejection: (empty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="84.75" customHeight="1" s="32">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -7404,7 +7426,8 @@
       <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Step 1: The 'Reason for rejection' field appears, empty.
- Step 3: The same error as SPM-28-TC11 is shown: 'A reason is required when rejecting. The organiser sees this message.' The status badge still shows 'Under review'.</t>
+ Step 2: The 'Reason for rejection' field is outlined in red with the error 'A reason is required when rejecting. The organiser sees this message.' The status badge still shows 'Under review'.
+ Step 3: 'SPM28 Nusantara Product Launch' is still listed.</t>
         </is>
       </c>
     </row>
@@ -7414,7 +7437,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -7449,7 +7472,8 @@
       <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Step 1: The 'Reason for rejection' field appears, empty.
- Step 3: The same error as SPM-28-TC11 is shown: 'A reason is required when rejecting. The organiser sees this message.' The status badge still shows 'Under review'.</t>
+ Step 2: The 'Reason for rejection' field is outlined in red with the error 'A reason is required when rejecting. The organiser sees this message.' The status badge still shows 'Under review'.
+ Step 3: 'SPM28 Nusantara Product Launch' is still listed.</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7483,7 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7471,7 +7495,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -7483,7 +7507,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -7495,7 +7519,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="27" t="n">
+      <c r="B15" s="31" t="n">
         <v>46295</v>
       </c>
     </row>
@@ -7517,7 +7541,8 @@
       <c r="B18" s="9" t="inlineStr">
         <is>
           <t>Step 1: The 'Reason for rejection' field appears, empty.
- Step 3: The same error as SPM-28-TC11 is shown: 'A reason is required when rejecting. The organiser sees this message.' The status badge still shows 'Under review'.</t>
+ Step 2: The 'Reason for rejection' field is outlined in red with the error 'A reason is required when rejecting. The organiser sees this message.' The status badge still shows 'Under review'.
+ Step 3: 'SPM28 Nusantara Product Launch' is still listed.</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7552,7 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7539,7 +7564,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -7563,7 +7588,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B22" s="31" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -8579,9 +8604,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-28-TC14</t>
+      <c r="B2" s="36" t="inlineStr">
+        <is>
+          <t>SPM-28-TC13</t>
         </is>
       </c>
     </row>
@@ -8599,7 +8624,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="71.25" customHeight="1" s="32">
+    <row r="4" ht="44.25" customHeight="1" s="32">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -8608,10 +8633,8 @@
       <c r="B4" s="9" t="inlineStr">
         <is>
           <t>1. Select 'Reject this request'
- 2. Type 'Test reason' into 'Reason for rejection'
- 3. Click 'Cancel'
- 4. Select 'Reject this request' again
- 5. Click 'Review Queue' in the sidebar</t>
+ 2. Type three spaces into 'Reason for rejection'
+ 3. Click 'Reject request'</t>
         </is>
       </c>
     </row>
@@ -8623,11 +8646,11 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Reason for rejection: Test reason (then cancelled)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="84.75" customHeight="1" s="32">
+          <t>Reason for rejection: ' ' (3 spaces)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="57.75" customHeight="1" s="32">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -8635,10 +8658,8 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Step 1: The 'Reason for rejection' field appears.
- Step 3: The reason field closes and neither option is selected. The status badge still shows 'Under review'.
- Step 4: The 'Reason for rejection' field is empty (the cancelled text was discarded).
- Step 5: 'SPM28 Nusantara Product Launch' is still listed.</t>
+          <t>Step 1: The 'Reason for rejection' field appears, empty.
+ Step 3: The same error as SPM-28-TC11 is shown: 'A reason is required when rejecting. The organiser sees this message.' The status badge still shows 'Under review'.</t>
         </is>
       </c>
     </row>
@@ -8648,7 +8669,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -8682,10 +8703,8 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Step 1: The 'Reason for rejection' field appears.
- Step 3: The reason field closes and neither option is selected. The status badge still shows 'Under review'.
- Step 4: The 'Reason for rejection' field is empty (the cancelled text was discarded).
- Step 5: 'SPM28 Nusantara Product Launch' is still listed.</t>
+          <t>Step 1: The 'Reason for rejection' field appears, empty.
+ Step 3: The same error as SPM-28-TC11 is shown: 'A reason is required when rejecting. The organiser sees this message.' The status badge still shows 'Under review'.</t>
         </is>
       </c>
     </row>
@@ -8695,7 +8714,7 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8707,7 +8726,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -8719,7 +8738,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -8731,7 +8750,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="21" t="n">
+      <c r="B15" s="27" t="n">
         <v>46295</v>
       </c>
     </row>
@@ -8752,10 +8771,8 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Step 1: The 'Reason for rejection' field appears.
- Step 3: The reason field closes and neither option is selected. The status badge still shows 'Under review'.
- Step 4: The 'Reason for rejection' field is empty (the cancelled text was discarded).
- Step 5: 'SPM28 Nusantara Product Launch' is still listed.</t>
+          <t>Step 1: The 'Reason for rejection' field appears, empty.
+ Step 3: The same error as SPM-28-TC11 is shown: 'A reason is required when rejecting. The organiser sees this message.' The status badge still shows 'Under review'.</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8782,7 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8777,7 +8794,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -8801,7 +8818,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B22" s="31" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -9817,7 +9834,1245 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="36" t="inlineStr">
+        <is>
+          <t>SPM-28-TC14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="98.25" customHeight="1" s="32">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Test data loaded: `npm run fixtures:spm28` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM28 …' events, EVT-000124 to EVT-000130, never anyone else's data).
+ Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), Event Coordinator.
+ 'SPM28 Nusantara Product Launch' review page is open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="71.25" customHeight="1" s="32">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>1. Select 'Reject this request'
+ 2. Type 'Test reason' into 'Reason for rejection'
+ 3. Click 'Cancel'
+ 4. Select 'Reject this request' again
+ 5. Click 'Review Queue' in the sidebar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="32">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Reason for rejection: Test reason (then cancelled)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="84.75" customHeight="1" s="32">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Step 1: The 'Reason for rejection' field appears.
+ Step 3: The reason field closes and neither option is selected. The status badge still shows 'Under review'.
+ Step 4: The 'Reason for rejection' field is empty (the cancelled text was discarded).
+ Step 5: 'SPM28 Nusantara Product Launch' is still listed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" s="32">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" s="32">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="32"/>
+    <row r="10" ht="15.75" customHeight="1" s="32">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="15" t="n"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" s="32">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Step 1: The 'Reason for rejection' field appears.
+ Step 3: The reason field closes and neither option is selected. The status badge still shows 'Under review'.
+ Step 4: The 'Reason for rejection' field is empty (the cancelled text was discarded).
+ Step 5: 'SPM28 Nusantara Product Launch' is still listed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="32">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" s="32">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" s="32">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" s="32">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="n">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="32"/>
+    <row r="17" ht="15.75" customHeight="1" s="32">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="n"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" s="32">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Step 1: The 'Reason for rejection' field appears.
+ Step 3: The reason field closes and neither option is selected. The status badge still shows 'Under review'.
+ Step 4: The 'Reason for rejection' field is empty (the cancelled text was discarded).
+ Step 5: 'SPM28 Nusantara Product Launch' is still listed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="32">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="32">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B20" s="29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="32">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>Sammi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" s="32">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B22" s="31" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="32"/>
+    <row r="24" ht="15.75" customHeight="1" s="32"/>
+    <row r="25" ht="15.75" customHeight="1" s="32"/>
+    <row r="26" ht="15.75" customHeight="1" s="32"/>
+    <row r="27" ht="15.75" customHeight="1" s="32"/>
+    <row r="28" ht="15.75" customHeight="1" s="32"/>
+    <row r="29" ht="15.75" customHeight="1" s="32"/>
+    <row r="30" ht="15.75" customHeight="1" s="32"/>
+    <row r="31" ht="15.75" customHeight="1" s="32"/>
+    <row r="32" ht="15.75" customHeight="1" s="32"/>
+    <row r="33" ht="15.75" customHeight="1" s="32"/>
+    <row r="34" ht="15.75" customHeight="1" s="32"/>
+    <row r="35" ht="15.75" customHeight="1" s="32"/>
+    <row r="36" ht="15.75" customHeight="1" s="32"/>
+    <row r="37" ht="15.75" customHeight="1" s="32"/>
+    <row r="38" ht="15.75" customHeight="1" s="32"/>
+    <row r="39" ht="15.75" customHeight="1" s="32"/>
+    <row r="40" ht="15.75" customHeight="1" s="32"/>
+    <row r="41" ht="15.75" customHeight="1" s="32"/>
+    <row r="42" ht="15.75" customHeight="1" s="32"/>
+    <row r="43" ht="15.75" customHeight="1" s="32"/>
+    <row r="44" ht="15.75" customHeight="1" s="32"/>
+    <row r="45" ht="15.75" customHeight="1" s="32"/>
+    <row r="46" ht="15.75" customHeight="1" s="32"/>
+    <row r="47" ht="15.75" customHeight="1" s="32"/>
+    <row r="48" ht="15.75" customHeight="1" s="32"/>
+    <row r="49" ht="15.75" customHeight="1" s="32"/>
+    <row r="50" ht="15.75" customHeight="1" s="32"/>
+    <row r="51" ht="15.75" customHeight="1" s="32"/>
+    <row r="52" ht="15.75" customHeight="1" s="32"/>
+    <row r="53" ht="15.75" customHeight="1" s="32"/>
+    <row r="54" ht="15.75" customHeight="1" s="32"/>
+    <row r="55" ht="15.75" customHeight="1" s="32"/>
+    <row r="56" ht="15.75" customHeight="1" s="32"/>
+    <row r="57" ht="15.75" customHeight="1" s="32"/>
+    <row r="58" ht="15.75" customHeight="1" s="32"/>
+    <row r="59" ht="15.75" customHeight="1" s="32"/>
+    <row r="60" ht="15.75" customHeight="1" s="32"/>
+    <row r="61" ht="15.75" customHeight="1" s="32"/>
+    <row r="62" ht="15.75" customHeight="1" s="32"/>
+    <row r="63" ht="15.75" customHeight="1" s="32"/>
+    <row r="64" ht="15.75" customHeight="1" s="32"/>
+    <row r="65" ht="15.75" customHeight="1" s="32"/>
+    <row r="66" ht="15.75" customHeight="1" s="32"/>
+    <row r="67" ht="15.75" customHeight="1" s="32"/>
+    <row r="68" ht="15.75" customHeight="1" s="32"/>
+    <row r="69" ht="15.75" customHeight="1" s="32"/>
+    <row r="70" ht="15.75" customHeight="1" s="32"/>
+    <row r="71" ht="15.75" customHeight="1" s="32"/>
+    <row r="72" ht="15.75" customHeight="1" s="32"/>
+    <row r="73" ht="15.75" customHeight="1" s="32"/>
+    <row r="74" ht="15.75" customHeight="1" s="32"/>
+    <row r="75" ht="15.75" customHeight="1" s="32"/>
+    <row r="76" ht="15.75" customHeight="1" s="32"/>
+    <row r="77" ht="15.75" customHeight="1" s="32"/>
+    <row r="78" ht="15.75" customHeight="1" s="32"/>
+    <row r="79" ht="15.75" customHeight="1" s="32"/>
+    <row r="80" ht="15.75" customHeight="1" s="32"/>
+    <row r="81" ht="15.75" customHeight="1" s="32"/>
+    <row r="82" ht="15.75" customHeight="1" s="32"/>
+    <row r="83" ht="15.75" customHeight="1" s="32"/>
+    <row r="84" ht="15.75" customHeight="1" s="32"/>
+    <row r="85" ht="15.75" customHeight="1" s="32"/>
+    <row r="86" ht="15.75" customHeight="1" s="32"/>
+    <row r="87" ht="15.75" customHeight="1" s="32"/>
+    <row r="88" ht="15.75" customHeight="1" s="32"/>
+    <row r="89" ht="15.75" customHeight="1" s="32"/>
+    <row r="90" ht="15.75" customHeight="1" s="32"/>
+    <row r="91" ht="15.75" customHeight="1" s="32"/>
+    <row r="92" ht="15.75" customHeight="1" s="32"/>
+    <row r="93" ht="15.75" customHeight="1" s="32"/>
+    <row r="94" ht="15.75" customHeight="1" s="32"/>
+    <row r="95" ht="15.75" customHeight="1" s="32"/>
+    <row r="96" ht="15.75" customHeight="1" s="32"/>
+    <row r="97" ht="15.75" customHeight="1" s="32"/>
+    <row r="98" ht="15.75" customHeight="1" s="32"/>
+    <row r="99" ht="15.75" customHeight="1" s="32"/>
+    <row r="100" ht="15.75" customHeight="1" s="32"/>
+    <row r="101" ht="15.75" customHeight="1" s="32"/>
+    <row r="102" ht="15.75" customHeight="1" s="32"/>
+    <row r="103" ht="15.75" customHeight="1" s="32"/>
+    <row r="104" ht="15.75" customHeight="1" s="32"/>
+    <row r="105" ht="15.75" customHeight="1" s="32"/>
+    <row r="106" ht="15.75" customHeight="1" s="32"/>
+    <row r="107" ht="15.75" customHeight="1" s="32"/>
+    <row r="108" ht="15.75" customHeight="1" s="32"/>
+    <row r="109" ht="15.75" customHeight="1" s="32"/>
+    <row r="110" ht="15.75" customHeight="1" s="32"/>
+    <row r="111" ht="15.75" customHeight="1" s="32"/>
+    <row r="112" ht="15.75" customHeight="1" s="32"/>
+    <row r="113" ht="15.75" customHeight="1" s="32"/>
+    <row r="114" ht="15.75" customHeight="1" s="32"/>
+    <row r="115" ht="15.75" customHeight="1" s="32"/>
+    <row r="116" ht="15.75" customHeight="1" s="32"/>
+    <row r="117" ht="15.75" customHeight="1" s="32"/>
+    <row r="118" ht="15.75" customHeight="1" s="32"/>
+    <row r="119" ht="15.75" customHeight="1" s="32"/>
+    <row r="120" ht="15.75" customHeight="1" s="32"/>
+    <row r="121" ht="15.75" customHeight="1" s="32"/>
+    <row r="122" ht="15.75" customHeight="1" s="32"/>
+    <row r="123" ht="15.75" customHeight="1" s="32"/>
+    <row r="124" ht="15.75" customHeight="1" s="32"/>
+    <row r="125" ht="15.75" customHeight="1" s="32"/>
+    <row r="126" ht="15.75" customHeight="1" s="32"/>
+    <row r="127" ht="15.75" customHeight="1" s="32"/>
+    <row r="128" ht="15.75" customHeight="1" s="32"/>
+    <row r="129" ht="15.75" customHeight="1" s="32"/>
+    <row r="130" ht="15.75" customHeight="1" s="32"/>
+    <row r="131" ht="15.75" customHeight="1" s="32"/>
+    <row r="132" ht="15.75" customHeight="1" s="32"/>
+    <row r="133" ht="15.75" customHeight="1" s="32"/>
+    <row r="134" ht="15.75" customHeight="1" s="32"/>
+    <row r="135" ht="15.75" customHeight="1" s="32"/>
+    <row r="136" ht="15.75" customHeight="1" s="32"/>
+    <row r="137" ht="15.75" customHeight="1" s="32"/>
+    <row r="138" ht="15.75" customHeight="1" s="32"/>
+    <row r="139" ht="15.75" customHeight="1" s="32"/>
+    <row r="140" ht="15.75" customHeight="1" s="32"/>
+    <row r="141" ht="15.75" customHeight="1" s="32"/>
+    <row r="142" ht="15.75" customHeight="1" s="32"/>
+    <row r="143" ht="15.75" customHeight="1" s="32"/>
+    <row r="144" ht="15.75" customHeight="1" s="32"/>
+    <row r="145" ht="15.75" customHeight="1" s="32"/>
+    <row r="146" ht="15.75" customHeight="1" s="32"/>
+    <row r="147" ht="15.75" customHeight="1" s="32"/>
+    <row r="148" ht="15.75" customHeight="1" s="32"/>
+    <row r="149" ht="15.75" customHeight="1" s="32"/>
+    <row r="150" ht="15.75" customHeight="1" s="32"/>
+    <row r="151" ht="15.75" customHeight="1" s="32"/>
+    <row r="152" ht="15.75" customHeight="1" s="32"/>
+    <row r="153" ht="15.75" customHeight="1" s="32"/>
+    <row r="154" ht="15.75" customHeight="1" s="32"/>
+    <row r="155" ht="15.75" customHeight="1" s="32"/>
+    <row r="156" ht="15.75" customHeight="1" s="32"/>
+    <row r="157" ht="15.75" customHeight="1" s="32"/>
+    <row r="158" ht="15.75" customHeight="1" s="32"/>
+    <row r="159" ht="15.75" customHeight="1" s="32"/>
+    <row r="160" ht="15.75" customHeight="1" s="32"/>
+    <row r="161" ht="15.75" customHeight="1" s="32"/>
+    <row r="162" ht="15.75" customHeight="1" s="32"/>
+    <row r="163" ht="15.75" customHeight="1" s="32"/>
+    <row r="164" ht="15.75" customHeight="1" s="32"/>
+    <row r="165" ht="15.75" customHeight="1" s="32"/>
+    <row r="166" ht="15.75" customHeight="1" s="32"/>
+    <row r="167" ht="15.75" customHeight="1" s="32"/>
+    <row r="168" ht="15.75" customHeight="1" s="32"/>
+    <row r="169" ht="15.75" customHeight="1" s="32"/>
+    <row r="170" ht="15.75" customHeight="1" s="32"/>
+    <row r="171" ht="15.75" customHeight="1" s="32"/>
+    <row r="172" ht="15.75" customHeight="1" s="32"/>
+    <row r="173" ht="15.75" customHeight="1" s="32"/>
+    <row r="174" ht="15.75" customHeight="1" s="32"/>
+    <row r="175" ht="15.75" customHeight="1" s="32"/>
+    <row r="176" ht="15.75" customHeight="1" s="32"/>
+    <row r="177" ht="15.75" customHeight="1" s="32"/>
+    <row r="178" ht="15.75" customHeight="1" s="32"/>
+    <row r="179" ht="15.75" customHeight="1" s="32"/>
+    <row r="180" ht="15.75" customHeight="1" s="32"/>
+    <row r="181" ht="15.75" customHeight="1" s="32"/>
+    <row r="182" ht="15.75" customHeight="1" s="32"/>
+    <row r="183" ht="15.75" customHeight="1" s="32"/>
+    <row r="184" ht="15.75" customHeight="1" s="32"/>
+    <row r="185" ht="15.75" customHeight="1" s="32"/>
+    <row r="186" ht="15.75" customHeight="1" s="32"/>
+    <row r="187" ht="15.75" customHeight="1" s="32"/>
+    <row r="188" ht="15.75" customHeight="1" s="32"/>
+    <row r="189" ht="15.75" customHeight="1" s="32"/>
+    <row r="190" ht="15.75" customHeight="1" s="32"/>
+    <row r="191" ht="15.75" customHeight="1" s="32"/>
+    <row r="192" ht="15.75" customHeight="1" s="32"/>
+    <row r="193" ht="15.75" customHeight="1" s="32"/>
+    <row r="194" ht="15.75" customHeight="1" s="32"/>
+    <row r="195" ht="15.75" customHeight="1" s="32"/>
+    <row r="196" ht="15.75" customHeight="1" s="32"/>
+    <row r="197" ht="15.75" customHeight="1" s="32"/>
+    <row r="198" ht="15.75" customHeight="1" s="32"/>
+    <row r="199" ht="15.75" customHeight="1" s="32"/>
+    <row r="200" ht="15.75" customHeight="1" s="32"/>
+    <row r="201" ht="15.75" customHeight="1" s="32"/>
+    <row r="202" ht="15.75" customHeight="1" s="32"/>
+    <row r="203" ht="15.75" customHeight="1" s="32"/>
+    <row r="204" ht="15.75" customHeight="1" s="32"/>
+    <row r="205" ht="15.75" customHeight="1" s="32"/>
+    <row r="206" ht="15.75" customHeight="1" s="32"/>
+    <row r="207" ht="15.75" customHeight="1" s="32"/>
+    <row r="208" ht="15.75" customHeight="1" s="32"/>
+    <row r="209" ht="15.75" customHeight="1" s="32"/>
+    <row r="210" ht="15.75" customHeight="1" s="32"/>
+    <row r="211" ht="15.75" customHeight="1" s="32"/>
+    <row r="212" ht="15.75" customHeight="1" s="32"/>
+    <row r="213" ht="15.75" customHeight="1" s="32"/>
+    <row r="214" ht="15.75" customHeight="1" s="32"/>
+    <row r="215" ht="15.75" customHeight="1" s="32"/>
+    <row r="216" ht="15.75" customHeight="1" s="32"/>
+    <row r="217" ht="15.75" customHeight="1" s="32"/>
+    <row r="218" ht="15.75" customHeight="1" s="32"/>
+    <row r="219" ht="15.75" customHeight="1" s="32"/>
+    <row r="220" ht="15.75" customHeight="1" s="32"/>
+    <row r="221" ht="15.75" customHeight="1" s="32"/>
+    <row r="222" ht="15.75" customHeight="1" s="32"/>
+    <row r="223" ht="15.75" customHeight="1" s="32"/>
+    <row r="224" ht="15.75" customHeight="1" s="32"/>
+    <row r="225" ht="15.75" customHeight="1" s="32"/>
+    <row r="226" ht="15.75" customHeight="1" s="32"/>
+    <row r="227" ht="15.75" customHeight="1" s="32"/>
+    <row r="228" ht="15.75" customHeight="1" s="32"/>
+    <row r="229" ht="15.75" customHeight="1" s="32"/>
+    <row r="230" ht="15.75" customHeight="1" s="32"/>
+    <row r="231" ht="15.75" customHeight="1" s="32"/>
+    <row r="232" ht="15.75" customHeight="1" s="32"/>
+    <row r="233" ht="15.75" customHeight="1" s="32"/>
+    <row r="234" ht="15.75" customHeight="1" s="32"/>
+    <row r="235" ht="15.75" customHeight="1" s="32"/>
+    <row r="236" ht="15.75" customHeight="1" s="32"/>
+    <row r="237" ht="15.75" customHeight="1" s="32"/>
+    <row r="238" ht="15.75" customHeight="1" s="32"/>
+    <row r="239" ht="15.75" customHeight="1" s="32"/>
+    <row r="240" ht="15.75" customHeight="1" s="32"/>
+    <row r="241" ht="15.75" customHeight="1" s="32"/>
+    <row r="242" ht="15.75" customHeight="1" s="32"/>
+    <row r="243" ht="15.75" customHeight="1" s="32"/>
+    <row r="244" ht="15.75" customHeight="1" s="32"/>
+    <row r="245" ht="15.75" customHeight="1" s="32"/>
+    <row r="246" ht="15.75" customHeight="1" s="32"/>
+    <row r="247" ht="15.75" customHeight="1" s="32"/>
+    <row r="248" ht="15.75" customHeight="1" s="32"/>
+    <row r="249" ht="15.75" customHeight="1" s="32"/>
+    <row r="250" ht="15.75" customHeight="1" s="32"/>
+    <row r="251" ht="15.75" customHeight="1" s="32"/>
+    <row r="252" ht="15.75" customHeight="1" s="32"/>
+    <row r="253" ht="15.75" customHeight="1" s="32"/>
+    <row r="254" ht="15.75" customHeight="1" s="32"/>
+    <row r="255" ht="15.75" customHeight="1" s="32"/>
+    <row r="256" ht="15.75" customHeight="1" s="32"/>
+    <row r="257" ht="15.75" customHeight="1" s="32"/>
+    <row r="258" ht="15.75" customHeight="1" s="32"/>
+    <row r="259" ht="15.75" customHeight="1" s="32"/>
+    <row r="260" ht="15.75" customHeight="1" s="32"/>
+    <row r="261" ht="15.75" customHeight="1" s="32"/>
+    <row r="262" ht="15.75" customHeight="1" s="32"/>
+    <row r="263" ht="15.75" customHeight="1" s="32"/>
+    <row r="264" ht="15.75" customHeight="1" s="32"/>
+    <row r="265" ht="15.75" customHeight="1" s="32"/>
+    <row r="266" ht="15.75" customHeight="1" s="32"/>
+    <row r="267" ht="15.75" customHeight="1" s="32"/>
+    <row r="268" ht="15.75" customHeight="1" s="32"/>
+    <row r="269" ht="15.75" customHeight="1" s="32"/>
+    <row r="270" ht="15.75" customHeight="1" s="32"/>
+    <row r="271" ht="15.75" customHeight="1" s="32"/>
+    <row r="272" ht="15.75" customHeight="1" s="32"/>
+    <row r="273" ht="15.75" customHeight="1" s="32"/>
+    <row r="274" ht="15.75" customHeight="1" s="32"/>
+    <row r="275" ht="15.75" customHeight="1" s="32"/>
+    <row r="276" ht="15.75" customHeight="1" s="32"/>
+    <row r="277" ht="15.75" customHeight="1" s="32"/>
+    <row r="278" ht="15.75" customHeight="1" s="32"/>
+    <row r="279" ht="15.75" customHeight="1" s="32"/>
+    <row r="280" ht="15.75" customHeight="1" s="32"/>
+    <row r="281" ht="15.75" customHeight="1" s="32"/>
+    <row r="282" ht="15.75" customHeight="1" s="32"/>
+    <row r="283" ht="15.75" customHeight="1" s="32"/>
+    <row r="284" ht="15.75" customHeight="1" s="32"/>
+    <row r="285" ht="15.75" customHeight="1" s="32"/>
+    <row r="286" ht="15.75" customHeight="1" s="32"/>
+    <row r="287" ht="15.75" customHeight="1" s="32"/>
+    <row r="288" ht="15.75" customHeight="1" s="32"/>
+    <row r="289" ht="15.75" customHeight="1" s="32"/>
+    <row r="290" ht="15.75" customHeight="1" s="32"/>
+    <row r="291" ht="15.75" customHeight="1" s="32"/>
+    <row r="292" ht="15.75" customHeight="1" s="32"/>
+    <row r="293" ht="15.75" customHeight="1" s="32"/>
+    <row r="294" ht="15.75" customHeight="1" s="32"/>
+    <row r="295" ht="15.75" customHeight="1" s="32"/>
+    <row r="296" ht="15.75" customHeight="1" s="32"/>
+    <row r="297" ht="15.75" customHeight="1" s="32"/>
+    <row r="298" ht="15.75" customHeight="1" s="32"/>
+    <row r="299" ht="15.75" customHeight="1" s="32"/>
+    <row r="300" ht="15.75" customHeight="1" s="32"/>
+    <row r="301" ht="15.75" customHeight="1" s="32"/>
+    <row r="302" ht="15.75" customHeight="1" s="32"/>
+    <row r="303" ht="15.75" customHeight="1" s="32"/>
+    <row r="304" ht="15.75" customHeight="1" s="32"/>
+    <row r="305" ht="15.75" customHeight="1" s="32"/>
+    <row r="306" ht="15.75" customHeight="1" s="32"/>
+    <row r="307" ht="15.75" customHeight="1" s="32"/>
+    <row r="308" ht="15.75" customHeight="1" s="32"/>
+    <row r="309" ht="15.75" customHeight="1" s="32"/>
+    <row r="310" ht="15.75" customHeight="1" s="32"/>
+    <row r="311" ht="15.75" customHeight="1" s="32"/>
+    <row r="312" ht="15.75" customHeight="1" s="32"/>
+    <row r="313" ht="15.75" customHeight="1" s="32"/>
+    <row r="314" ht="15.75" customHeight="1" s="32"/>
+    <row r="315" ht="15.75" customHeight="1" s="32"/>
+    <row r="316" ht="15.75" customHeight="1" s="32"/>
+    <row r="317" ht="15.75" customHeight="1" s="32"/>
+    <row r="318" ht="15.75" customHeight="1" s="32"/>
+    <row r="319" ht="15.75" customHeight="1" s="32"/>
+    <row r="320" ht="15.75" customHeight="1" s="32"/>
+    <row r="321" ht="15.75" customHeight="1" s="32"/>
+    <row r="322" ht="15.75" customHeight="1" s="32"/>
+    <row r="323" ht="15.75" customHeight="1" s="32"/>
+    <row r="324" ht="15.75" customHeight="1" s="32"/>
+    <row r="325" ht="15.75" customHeight="1" s="32"/>
+    <row r="326" ht="15.75" customHeight="1" s="32"/>
+    <row r="327" ht="15.75" customHeight="1" s="32"/>
+    <row r="328" ht="15.75" customHeight="1" s="32"/>
+    <row r="329" ht="15.75" customHeight="1" s="32"/>
+    <row r="330" ht="15.75" customHeight="1" s="32"/>
+    <row r="331" ht="15.75" customHeight="1" s="32"/>
+    <row r="332" ht="15.75" customHeight="1" s="32"/>
+    <row r="333" ht="15.75" customHeight="1" s="32"/>
+    <row r="334" ht="15.75" customHeight="1" s="32"/>
+    <row r="335" ht="15.75" customHeight="1" s="32"/>
+    <row r="336" ht="15.75" customHeight="1" s="32"/>
+    <row r="337" ht="15.75" customHeight="1" s="32"/>
+    <row r="338" ht="15.75" customHeight="1" s="32"/>
+    <row r="339" ht="15.75" customHeight="1" s="32"/>
+    <row r="340" ht="15.75" customHeight="1" s="32"/>
+    <row r="341" ht="15.75" customHeight="1" s="32"/>
+    <row r="342" ht="15.75" customHeight="1" s="32"/>
+    <row r="343" ht="15.75" customHeight="1" s="32"/>
+    <row r="344" ht="15.75" customHeight="1" s="32"/>
+    <row r="345" ht="15.75" customHeight="1" s="32"/>
+    <row r="346" ht="15.75" customHeight="1" s="32"/>
+    <row r="347" ht="15.75" customHeight="1" s="32"/>
+    <row r="348" ht="15.75" customHeight="1" s="32"/>
+    <row r="349" ht="15.75" customHeight="1" s="32"/>
+    <row r="350" ht="15.75" customHeight="1" s="32"/>
+    <row r="351" ht="15.75" customHeight="1" s="32"/>
+    <row r="352" ht="15.75" customHeight="1" s="32"/>
+    <row r="353" ht="15.75" customHeight="1" s="32"/>
+    <row r="354" ht="15.75" customHeight="1" s="32"/>
+    <row r="355" ht="15.75" customHeight="1" s="32"/>
+    <row r="356" ht="15.75" customHeight="1" s="32"/>
+    <row r="357" ht="15.75" customHeight="1" s="32"/>
+    <row r="358" ht="15.75" customHeight="1" s="32"/>
+    <row r="359" ht="15.75" customHeight="1" s="32"/>
+    <row r="360" ht="15.75" customHeight="1" s="32"/>
+    <row r="361" ht="15.75" customHeight="1" s="32"/>
+    <row r="362" ht="15.75" customHeight="1" s="32"/>
+    <row r="363" ht="15.75" customHeight="1" s="32"/>
+    <row r="364" ht="15.75" customHeight="1" s="32"/>
+    <row r="365" ht="15.75" customHeight="1" s="32"/>
+    <row r="366" ht="15.75" customHeight="1" s="32"/>
+    <row r="367" ht="15.75" customHeight="1" s="32"/>
+    <row r="368" ht="15.75" customHeight="1" s="32"/>
+    <row r="369" ht="15.75" customHeight="1" s="32"/>
+    <row r="370" ht="15.75" customHeight="1" s="32"/>
+    <row r="371" ht="15.75" customHeight="1" s="32"/>
+    <row r="372" ht="15.75" customHeight="1" s="32"/>
+    <row r="373" ht="15.75" customHeight="1" s="32"/>
+    <row r="374" ht="15.75" customHeight="1" s="32"/>
+    <row r="375" ht="15.75" customHeight="1" s="32"/>
+    <row r="376" ht="15.75" customHeight="1" s="32"/>
+    <row r="377" ht="15.75" customHeight="1" s="32"/>
+    <row r="378" ht="15.75" customHeight="1" s="32"/>
+    <row r="379" ht="15.75" customHeight="1" s="32"/>
+    <row r="380" ht="15.75" customHeight="1" s="32"/>
+    <row r="381" ht="15.75" customHeight="1" s="32"/>
+    <row r="382" ht="15.75" customHeight="1" s="32"/>
+    <row r="383" ht="15.75" customHeight="1" s="32"/>
+    <row r="384" ht="15.75" customHeight="1" s="32"/>
+    <row r="385" ht="15.75" customHeight="1" s="32"/>
+    <row r="386" ht="15.75" customHeight="1" s="32"/>
+    <row r="387" ht="15.75" customHeight="1" s="32"/>
+    <row r="388" ht="15.75" customHeight="1" s="32"/>
+    <row r="389" ht="15.75" customHeight="1" s="32"/>
+    <row r="390" ht="15.75" customHeight="1" s="32"/>
+    <row r="391" ht="15.75" customHeight="1" s="32"/>
+    <row r="392" ht="15.75" customHeight="1" s="32"/>
+    <row r="393" ht="15.75" customHeight="1" s="32"/>
+    <row r="394" ht="15.75" customHeight="1" s="32"/>
+    <row r="395" ht="15.75" customHeight="1" s="32"/>
+    <row r="396" ht="15.75" customHeight="1" s="32"/>
+    <row r="397" ht="15.75" customHeight="1" s="32"/>
+    <row r="398" ht="15.75" customHeight="1" s="32"/>
+    <row r="399" ht="15.75" customHeight="1" s="32"/>
+    <row r="400" ht="15.75" customHeight="1" s="32"/>
+    <row r="401" ht="15.75" customHeight="1" s="32"/>
+    <row r="402" ht="15.75" customHeight="1" s="32"/>
+    <row r="403" ht="15.75" customHeight="1" s="32"/>
+    <row r="404" ht="15.75" customHeight="1" s="32"/>
+    <row r="405" ht="15.75" customHeight="1" s="32"/>
+    <row r="406" ht="15.75" customHeight="1" s="32"/>
+    <row r="407" ht="15.75" customHeight="1" s="32"/>
+    <row r="408" ht="15.75" customHeight="1" s="32"/>
+    <row r="409" ht="15.75" customHeight="1" s="32"/>
+    <row r="410" ht="15.75" customHeight="1" s="32"/>
+    <row r="411" ht="15.75" customHeight="1" s="32"/>
+    <row r="412" ht="15.75" customHeight="1" s="32"/>
+    <row r="413" ht="15.75" customHeight="1" s="32"/>
+    <row r="414" ht="15.75" customHeight="1" s="32"/>
+    <row r="415" ht="15.75" customHeight="1" s="32"/>
+    <row r="416" ht="15.75" customHeight="1" s="32"/>
+    <row r="417" ht="15.75" customHeight="1" s="32"/>
+    <row r="418" ht="15.75" customHeight="1" s="32"/>
+    <row r="419" ht="15.75" customHeight="1" s="32"/>
+    <row r="420" ht="15.75" customHeight="1" s="32"/>
+    <row r="421" ht="15.75" customHeight="1" s="32"/>
+    <row r="422" ht="15.75" customHeight="1" s="32"/>
+    <row r="423" ht="15.75" customHeight="1" s="32"/>
+    <row r="424" ht="15.75" customHeight="1" s="32"/>
+    <row r="425" ht="15.75" customHeight="1" s="32"/>
+    <row r="426" ht="15.75" customHeight="1" s="32"/>
+    <row r="427" ht="15.75" customHeight="1" s="32"/>
+    <row r="428" ht="15.75" customHeight="1" s="32"/>
+    <row r="429" ht="15.75" customHeight="1" s="32"/>
+    <row r="430" ht="15.75" customHeight="1" s="32"/>
+    <row r="431" ht="15.75" customHeight="1" s="32"/>
+    <row r="432" ht="15.75" customHeight="1" s="32"/>
+    <row r="433" ht="15.75" customHeight="1" s="32"/>
+    <row r="434" ht="15.75" customHeight="1" s="32"/>
+    <row r="435" ht="15.75" customHeight="1" s="32"/>
+    <row r="436" ht="15.75" customHeight="1" s="32"/>
+    <row r="437" ht="15.75" customHeight="1" s="32"/>
+    <row r="438" ht="15.75" customHeight="1" s="32"/>
+    <row r="439" ht="15.75" customHeight="1" s="32"/>
+    <row r="440" ht="15.75" customHeight="1" s="32"/>
+    <row r="441" ht="15.75" customHeight="1" s="32"/>
+    <row r="442" ht="15.75" customHeight="1" s="32"/>
+    <row r="443" ht="15.75" customHeight="1" s="32"/>
+    <row r="444" ht="15.75" customHeight="1" s="32"/>
+    <row r="445" ht="15.75" customHeight="1" s="32"/>
+    <row r="446" ht="15.75" customHeight="1" s="32"/>
+    <row r="447" ht="15.75" customHeight="1" s="32"/>
+    <row r="448" ht="15.75" customHeight="1" s="32"/>
+    <row r="449" ht="15.75" customHeight="1" s="32"/>
+    <row r="450" ht="15.75" customHeight="1" s="32"/>
+    <row r="451" ht="15.75" customHeight="1" s="32"/>
+    <row r="452" ht="15.75" customHeight="1" s="32"/>
+    <row r="453" ht="15.75" customHeight="1" s="32"/>
+    <row r="454" ht="15.75" customHeight="1" s="32"/>
+    <row r="455" ht="15.75" customHeight="1" s="32"/>
+    <row r="456" ht="15.75" customHeight="1" s="32"/>
+    <row r="457" ht="15.75" customHeight="1" s="32"/>
+    <row r="458" ht="15.75" customHeight="1" s="32"/>
+    <row r="459" ht="15.75" customHeight="1" s="32"/>
+    <row r="460" ht="15.75" customHeight="1" s="32"/>
+    <row r="461" ht="15.75" customHeight="1" s="32"/>
+    <row r="462" ht="15.75" customHeight="1" s="32"/>
+    <row r="463" ht="15.75" customHeight="1" s="32"/>
+    <row r="464" ht="15.75" customHeight="1" s="32"/>
+    <row r="465" ht="15.75" customHeight="1" s="32"/>
+    <row r="466" ht="15.75" customHeight="1" s="32"/>
+    <row r="467" ht="15.75" customHeight="1" s="32"/>
+    <row r="468" ht="15.75" customHeight="1" s="32"/>
+    <row r="469" ht="15.75" customHeight="1" s="32"/>
+    <row r="470" ht="15.75" customHeight="1" s="32"/>
+    <row r="471" ht="15.75" customHeight="1" s="32"/>
+    <row r="472" ht="15.75" customHeight="1" s="32"/>
+    <row r="473" ht="15.75" customHeight="1" s="32"/>
+    <row r="474" ht="15.75" customHeight="1" s="32"/>
+    <row r="475" ht="15.75" customHeight="1" s="32"/>
+    <row r="476" ht="15.75" customHeight="1" s="32"/>
+    <row r="477" ht="15.75" customHeight="1" s="32"/>
+    <row r="478" ht="15.75" customHeight="1" s="32"/>
+    <row r="479" ht="15.75" customHeight="1" s="32"/>
+    <row r="480" ht="15.75" customHeight="1" s="32"/>
+    <row r="481" ht="15.75" customHeight="1" s="32"/>
+    <row r="482" ht="15.75" customHeight="1" s="32"/>
+    <row r="483" ht="15.75" customHeight="1" s="32"/>
+    <row r="484" ht="15.75" customHeight="1" s="32"/>
+    <row r="485" ht="15.75" customHeight="1" s="32"/>
+    <row r="486" ht="15.75" customHeight="1" s="32"/>
+    <row r="487" ht="15.75" customHeight="1" s="32"/>
+    <row r="488" ht="15.75" customHeight="1" s="32"/>
+    <row r="489" ht="15.75" customHeight="1" s="32"/>
+    <row r="490" ht="15.75" customHeight="1" s="32"/>
+    <row r="491" ht="15.75" customHeight="1" s="32"/>
+    <row r="492" ht="15.75" customHeight="1" s="32"/>
+    <row r="493" ht="15.75" customHeight="1" s="32"/>
+    <row r="494" ht="15.75" customHeight="1" s="32"/>
+    <row r="495" ht="15.75" customHeight="1" s="32"/>
+    <row r="496" ht="15.75" customHeight="1" s="32"/>
+    <row r="497" ht="15.75" customHeight="1" s="32"/>
+    <row r="498" ht="15.75" customHeight="1" s="32"/>
+    <row r="499" ht="15.75" customHeight="1" s="32"/>
+    <row r="500" ht="15.75" customHeight="1" s="32"/>
+    <row r="501" ht="15.75" customHeight="1" s="32"/>
+    <row r="502" ht="15.75" customHeight="1" s="32"/>
+    <row r="503" ht="15.75" customHeight="1" s="32"/>
+    <row r="504" ht="15.75" customHeight="1" s="32"/>
+    <row r="505" ht="15.75" customHeight="1" s="32"/>
+    <row r="506" ht="15.75" customHeight="1" s="32"/>
+    <row r="507" ht="15.75" customHeight="1" s="32"/>
+    <row r="508" ht="15.75" customHeight="1" s="32"/>
+    <row r="509" ht="15.75" customHeight="1" s="32"/>
+    <row r="510" ht="15.75" customHeight="1" s="32"/>
+    <row r="511" ht="15.75" customHeight="1" s="32"/>
+    <row r="512" ht="15.75" customHeight="1" s="32"/>
+    <row r="513" ht="15.75" customHeight="1" s="32"/>
+    <row r="514" ht="15.75" customHeight="1" s="32"/>
+    <row r="515" ht="15.75" customHeight="1" s="32"/>
+    <row r="516" ht="15.75" customHeight="1" s="32"/>
+    <row r="517" ht="15.75" customHeight="1" s="32"/>
+    <row r="518" ht="15.75" customHeight="1" s="32"/>
+    <row r="519" ht="15.75" customHeight="1" s="32"/>
+    <row r="520" ht="15.75" customHeight="1" s="32"/>
+    <row r="521" ht="15.75" customHeight="1" s="32"/>
+    <row r="522" ht="15.75" customHeight="1" s="32"/>
+    <row r="523" ht="15.75" customHeight="1" s="32"/>
+    <row r="524" ht="15.75" customHeight="1" s="32"/>
+    <row r="525" ht="15.75" customHeight="1" s="32"/>
+    <row r="526" ht="15.75" customHeight="1" s="32"/>
+    <row r="527" ht="15.75" customHeight="1" s="32"/>
+    <row r="528" ht="15.75" customHeight="1" s="32"/>
+    <row r="529" ht="15.75" customHeight="1" s="32"/>
+    <row r="530" ht="15.75" customHeight="1" s="32"/>
+    <row r="531" ht="15.75" customHeight="1" s="32"/>
+    <row r="532" ht="15.75" customHeight="1" s="32"/>
+    <row r="533" ht="15.75" customHeight="1" s="32"/>
+    <row r="534" ht="15.75" customHeight="1" s="32"/>
+    <row r="535" ht="15.75" customHeight="1" s="32"/>
+    <row r="536" ht="15.75" customHeight="1" s="32"/>
+    <row r="537" ht="15.75" customHeight="1" s="32"/>
+    <row r="538" ht="15.75" customHeight="1" s="32"/>
+    <row r="539" ht="15.75" customHeight="1" s="32"/>
+    <row r="540" ht="15.75" customHeight="1" s="32"/>
+    <row r="541" ht="15.75" customHeight="1" s="32"/>
+    <row r="542" ht="15.75" customHeight="1" s="32"/>
+    <row r="543" ht="15.75" customHeight="1" s="32"/>
+    <row r="544" ht="15.75" customHeight="1" s="32"/>
+    <row r="545" ht="15.75" customHeight="1" s="32"/>
+    <row r="546" ht="15.75" customHeight="1" s="32"/>
+    <row r="547" ht="15.75" customHeight="1" s="32"/>
+    <row r="548" ht="15.75" customHeight="1" s="32"/>
+    <row r="549" ht="15.75" customHeight="1" s="32"/>
+    <row r="550" ht="15.75" customHeight="1" s="32"/>
+    <row r="551" ht="15.75" customHeight="1" s="32"/>
+    <row r="552" ht="15.75" customHeight="1" s="32"/>
+    <row r="553" ht="15.75" customHeight="1" s="32"/>
+    <row r="554" ht="15.75" customHeight="1" s="32"/>
+    <row r="555" ht="15.75" customHeight="1" s="32"/>
+    <row r="556" ht="15.75" customHeight="1" s="32"/>
+    <row r="557" ht="15.75" customHeight="1" s="32"/>
+    <row r="558" ht="15.75" customHeight="1" s="32"/>
+    <row r="559" ht="15.75" customHeight="1" s="32"/>
+    <row r="560" ht="15.75" customHeight="1" s="32"/>
+    <row r="561" ht="15.75" customHeight="1" s="32"/>
+    <row r="562" ht="15.75" customHeight="1" s="32"/>
+    <row r="563" ht="15.75" customHeight="1" s="32"/>
+    <row r="564" ht="15.75" customHeight="1" s="32"/>
+    <row r="565" ht="15.75" customHeight="1" s="32"/>
+    <row r="566" ht="15.75" customHeight="1" s="32"/>
+    <row r="567" ht="15.75" customHeight="1" s="32"/>
+    <row r="568" ht="15.75" customHeight="1" s="32"/>
+    <row r="569" ht="15.75" customHeight="1" s="32"/>
+    <row r="570" ht="15.75" customHeight="1" s="32"/>
+    <row r="571" ht="15.75" customHeight="1" s="32"/>
+    <row r="572" ht="15.75" customHeight="1" s="32"/>
+    <row r="573" ht="15.75" customHeight="1" s="32"/>
+    <row r="574" ht="15.75" customHeight="1" s="32"/>
+    <row r="575" ht="15.75" customHeight="1" s="32"/>
+    <row r="576" ht="15.75" customHeight="1" s="32"/>
+    <row r="577" ht="15.75" customHeight="1" s="32"/>
+    <row r="578" ht="15.75" customHeight="1" s="32"/>
+    <row r="579" ht="15.75" customHeight="1" s="32"/>
+    <row r="580" ht="15.75" customHeight="1" s="32"/>
+    <row r="581" ht="15.75" customHeight="1" s="32"/>
+    <row r="582" ht="15.75" customHeight="1" s="32"/>
+    <row r="583" ht="15.75" customHeight="1" s="32"/>
+    <row r="584" ht="15.75" customHeight="1" s="32"/>
+    <row r="585" ht="15.75" customHeight="1" s="32"/>
+    <row r="586" ht="15.75" customHeight="1" s="32"/>
+    <row r="587" ht="15.75" customHeight="1" s="32"/>
+    <row r="588" ht="15.75" customHeight="1" s="32"/>
+    <row r="589" ht="15.75" customHeight="1" s="32"/>
+    <row r="590" ht="15.75" customHeight="1" s="32"/>
+    <row r="591" ht="15.75" customHeight="1" s="32"/>
+    <row r="592" ht="15.75" customHeight="1" s="32"/>
+    <row r="593" ht="15.75" customHeight="1" s="32"/>
+    <row r="594" ht="15.75" customHeight="1" s="32"/>
+    <row r="595" ht="15.75" customHeight="1" s="32"/>
+    <row r="596" ht="15.75" customHeight="1" s="32"/>
+    <row r="597" ht="15.75" customHeight="1" s="32"/>
+    <row r="598" ht="15.75" customHeight="1" s="32"/>
+    <row r="599" ht="15.75" customHeight="1" s="32"/>
+    <row r="600" ht="15.75" customHeight="1" s="32"/>
+    <row r="601" ht="15.75" customHeight="1" s="32"/>
+    <row r="602" ht="15.75" customHeight="1" s="32"/>
+    <row r="603" ht="15.75" customHeight="1" s="32"/>
+    <row r="604" ht="15.75" customHeight="1" s="32"/>
+    <row r="605" ht="15.75" customHeight="1" s="32"/>
+    <row r="606" ht="15.75" customHeight="1" s="32"/>
+    <row r="607" ht="15.75" customHeight="1" s="32"/>
+    <row r="608" ht="15.75" customHeight="1" s="32"/>
+    <row r="609" ht="15.75" customHeight="1" s="32"/>
+    <row r="610" ht="15.75" customHeight="1" s="32"/>
+    <row r="611" ht="15.75" customHeight="1" s="32"/>
+    <row r="612" ht="15.75" customHeight="1" s="32"/>
+    <row r="613" ht="15.75" customHeight="1" s="32"/>
+    <row r="614" ht="15.75" customHeight="1" s="32"/>
+    <row r="615" ht="15.75" customHeight="1" s="32"/>
+    <row r="616" ht="15.75" customHeight="1" s="32"/>
+    <row r="617" ht="15.75" customHeight="1" s="32"/>
+    <row r="618" ht="15.75" customHeight="1" s="32"/>
+    <row r="619" ht="15.75" customHeight="1" s="32"/>
+    <row r="620" ht="15.75" customHeight="1" s="32"/>
+    <row r="621" ht="15.75" customHeight="1" s="32"/>
+    <row r="622" ht="15.75" customHeight="1" s="32"/>
+    <row r="623" ht="15.75" customHeight="1" s="32"/>
+    <row r="624" ht="15.75" customHeight="1" s="32"/>
+    <row r="625" ht="15.75" customHeight="1" s="32"/>
+    <row r="626" ht="15.75" customHeight="1" s="32"/>
+    <row r="627" ht="15.75" customHeight="1" s="32"/>
+    <row r="628" ht="15.75" customHeight="1" s="32"/>
+    <row r="629" ht="15.75" customHeight="1" s="32"/>
+    <row r="630" ht="15.75" customHeight="1" s="32"/>
+    <row r="631" ht="15.75" customHeight="1" s="32"/>
+    <row r="632" ht="15.75" customHeight="1" s="32"/>
+    <row r="633" ht="15.75" customHeight="1" s="32"/>
+    <row r="634" ht="15.75" customHeight="1" s="32"/>
+    <row r="635" ht="15.75" customHeight="1" s="32"/>
+    <row r="636" ht="15.75" customHeight="1" s="32"/>
+    <row r="637" ht="15.75" customHeight="1" s="32"/>
+    <row r="638" ht="15.75" customHeight="1" s="32"/>
+    <row r="639" ht="15.75" customHeight="1" s="32"/>
+    <row r="640" ht="15.75" customHeight="1" s="32"/>
+    <row r="641" ht="15.75" customHeight="1" s="32"/>
+    <row r="642" ht="15.75" customHeight="1" s="32"/>
+    <row r="643" ht="15.75" customHeight="1" s="32"/>
+    <row r="644" ht="15.75" customHeight="1" s="32"/>
+    <row r="645" ht="15.75" customHeight="1" s="32"/>
+    <row r="646" ht="15.75" customHeight="1" s="32"/>
+    <row r="647" ht="15.75" customHeight="1" s="32"/>
+    <row r="648" ht="15.75" customHeight="1" s="32"/>
+    <row r="649" ht="15.75" customHeight="1" s="32"/>
+    <row r="650" ht="15.75" customHeight="1" s="32"/>
+    <row r="651" ht="15.75" customHeight="1" s="32"/>
+    <row r="652" ht="15.75" customHeight="1" s="32"/>
+    <row r="653" ht="15.75" customHeight="1" s="32"/>
+    <row r="654" ht="15.75" customHeight="1" s="32"/>
+    <row r="655" ht="15.75" customHeight="1" s="32"/>
+    <row r="656" ht="15.75" customHeight="1" s="32"/>
+    <row r="657" ht="15.75" customHeight="1" s="32"/>
+    <row r="658" ht="15.75" customHeight="1" s="32"/>
+    <row r="659" ht="15.75" customHeight="1" s="32"/>
+    <row r="660" ht="15.75" customHeight="1" s="32"/>
+    <row r="661" ht="15.75" customHeight="1" s="32"/>
+    <row r="662" ht="15.75" customHeight="1" s="32"/>
+    <row r="663" ht="15.75" customHeight="1" s="32"/>
+    <row r="664" ht="15.75" customHeight="1" s="32"/>
+    <row r="665" ht="15.75" customHeight="1" s="32"/>
+    <row r="666" ht="15.75" customHeight="1" s="32"/>
+    <row r="667" ht="15.75" customHeight="1" s="32"/>
+    <row r="668" ht="15.75" customHeight="1" s="32"/>
+    <row r="669" ht="15.75" customHeight="1" s="32"/>
+    <row r="670" ht="15.75" customHeight="1" s="32"/>
+    <row r="671" ht="15.75" customHeight="1" s="32"/>
+    <row r="672" ht="15.75" customHeight="1" s="32"/>
+    <row r="673" ht="15.75" customHeight="1" s="32"/>
+    <row r="674" ht="15.75" customHeight="1" s="32"/>
+    <row r="675" ht="15.75" customHeight="1" s="32"/>
+    <row r="676" ht="15.75" customHeight="1" s="32"/>
+    <row r="677" ht="15.75" customHeight="1" s="32"/>
+    <row r="678" ht="15.75" customHeight="1" s="32"/>
+    <row r="679" ht="15.75" customHeight="1" s="32"/>
+    <row r="680" ht="15.75" customHeight="1" s="32"/>
+    <row r="681" ht="15.75" customHeight="1" s="32"/>
+    <row r="682" ht="15.75" customHeight="1" s="32"/>
+    <row r="683" ht="15.75" customHeight="1" s="32"/>
+    <row r="684" ht="15.75" customHeight="1" s="32"/>
+    <row r="685" ht="15.75" customHeight="1" s="32"/>
+    <row r="686" ht="15.75" customHeight="1" s="32"/>
+    <row r="687" ht="15.75" customHeight="1" s="32"/>
+    <row r="688" ht="15.75" customHeight="1" s="32"/>
+    <row r="689" ht="15.75" customHeight="1" s="32"/>
+    <row r="690" ht="15.75" customHeight="1" s="32"/>
+    <row r="691" ht="15.75" customHeight="1" s="32"/>
+    <row r="692" ht="15.75" customHeight="1" s="32"/>
+    <row r="693" ht="15.75" customHeight="1" s="32"/>
+    <row r="694" ht="15.75" customHeight="1" s="32"/>
+    <row r="695" ht="15.75" customHeight="1" s="32"/>
+    <row r="696" ht="15.75" customHeight="1" s="32"/>
+    <row r="697" ht="15.75" customHeight="1" s="32"/>
+    <row r="698" ht="15.75" customHeight="1" s="32"/>
+    <row r="699" ht="15.75" customHeight="1" s="32"/>
+    <row r="700" ht="15.75" customHeight="1" s="32"/>
+    <row r="701" ht="15.75" customHeight="1" s="32"/>
+    <row r="702" ht="15.75" customHeight="1" s="32"/>
+    <row r="703" ht="15.75" customHeight="1" s="32"/>
+    <row r="704" ht="15.75" customHeight="1" s="32"/>
+    <row r="705" ht="15.75" customHeight="1" s="32"/>
+    <row r="706" ht="15.75" customHeight="1" s="32"/>
+    <row r="707" ht="15.75" customHeight="1" s="32"/>
+    <row r="708" ht="15.75" customHeight="1" s="32"/>
+    <row r="709" ht="15.75" customHeight="1" s="32"/>
+    <row r="710" ht="15.75" customHeight="1" s="32"/>
+    <row r="711" ht="15.75" customHeight="1" s="32"/>
+    <row r="712" ht="15.75" customHeight="1" s="32"/>
+    <row r="713" ht="15.75" customHeight="1" s="32"/>
+    <row r="714" ht="15.75" customHeight="1" s="32"/>
+    <row r="715" ht="15.75" customHeight="1" s="32"/>
+    <row r="716" ht="15.75" customHeight="1" s="32"/>
+    <row r="717" ht="15.75" customHeight="1" s="32"/>
+    <row r="718" ht="15.75" customHeight="1" s="32"/>
+    <row r="719" ht="15.75" customHeight="1" s="32"/>
+    <row r="720" ht="15.75" customHeight="1" s="32"/>
+    <row r="721" ht="15.75" customHeight="1" s="32"/>
+    <row r="722" ht="15.75" customHeight="1" s="32"/>
+    <row r="723" ht="15.75" customHeight="1" s="32"/>
+    <row r="724" ht="15.75" customHeight="1" s="32"/>
+    <row r="725" ht="15.75" customHeight="1" s="32"/>
+    <row r="726" ht="15.75" customHeight="1" s="32"/>
+    <row r="727" ht="15.75" customHeight="1" s="32"/>
+    <row r="728" ht="15.75" customHeight="1" s="32"/>
+    <row r="729" ht="15.75" customHeight="1" s="32"/>
+    <row r="730" ht="15.75" customHeight="1" s="32"/>
+    <row r="731" ht="15.75" customHeight="1" s="32"/>
+    <row r="732" ht="15.75" customHeight="1" s="32"/>
+    <row r="733" ht="15.75" customHeight="1" s="32"/>
+    <row r="734" ht="15.75" customHeight="1" s="32"/>
+    <row r="735" ht="15.75" customHeight="1" s="32"/>
+    <row r="736" ht="15.75" customHeight="1" s="32"/>
+    <row r="737" ht="15.75" customHeight="1" s="32"/>
+    <row r="738" ht="15.75" customHeight="1" s="32"/>
+    <row r="739" ht="15.75" customHeight="1" s="32"/>
+    <row r="740" ht="15.75" customHeight="1" s="32"/>
+    <row r="741" ht="15.75" customHeight="1" s="32"/>
+    <row r="742" ht="15.75" customHeight="1" s="32"/>
+    <row r="743" ht="15.75" customHeight="1" s="32"/>
+    <row r="744" ht="15.75" customHeight="1" s="32"/>
+    <row r="745" ht="15.75" customHeight="1" s="32"/>
+    <row r="746" ht="15.75" customHeight="1" s="32"/>
+    <row r="747" ht="15.75" customHeight="1" s="32"/>
+    <row r="748" ht="15.75" customHeight="1" s="32"/>
+    <row r="749" ht="15.75" customHeight="1" s="32"/>
+    <row r="750" ht="15.75" customHeight="1" s="32"/>
+    <row r="751" ht="15.75" customHeight="1" s="32"/>
+    <row r="752" ht="15.75" customHeight="1" s="32"/>
+    <row r="753" ht="15.75" customHeight="1" s="32"/>
+    <row r="754" ht="15.75" customHeight="1" s="32"/>
+    <row r="755" ht="15.75" customHeight="1" s="32"/>
+    <row r="756" ht="15.75" customHeight="1" s="32"/>
+    <row r="757" ht="15.75" customHeight="1" s="32"/>
+    <row r="758" ht="15.75" customHeight="1" s="32"/>
+    <row r="759" ht="15.75" customHeight="1" s="32"/>
+    <row r="760" ht="15.75" customHeight="1" s="32"/>
+    <row r="761" ht="15.75" customHeight="1" s="32"/>
+    <row r="762" ht="15.75" customHeight="1" s="32"/>
+    <row r="763" ht="15.75" customHeight="1" s="32"/>
+    <row r="764" ht="15.75" customHeight="1" s="32"/>
+    <row r="765" ht="15.75" customHeight="1" s="32"/>
+    <row r="766" ht="15.75" customHeight="1" s="32"/>
+    <row r="767" ht="15.75" customHeight="1" s="32"/>
+    <row r="768" ht="15.75" customHeight="1" s="32"/>
+    <row r="769" ht="15.75" customHeight="1" s="32"/>
+    <row r="770" ht="15.75" customHeight="1" s="32"/>
+    <row r="771" ht="15.75" customHeight="1" s="32"/>
+    <row r="772" ht="15.75" customHeight="1" s="32"/>
+    <row r="773" ht="15.75" customHeight="1" s="32"/>
+    <row r="774" ht="15.75" customHeight="1" s="32"/>
+    <row r="775" ht="15.75" customHeight="1" s="32"/>
+    <row r="776" ht="15.75" customHeight="1" s="32"/>
+    <row r="777" ht="15.75" customHeight="1" s="32"/>
+    <row r="778" ht="15.75" customHeight="1" s="32"/>
+    <row r="779" ht="15.75" customHeight="1" s="32"/>
+    <row r="780" ht="15.75" customHeight="1" s="32"/>
+    <row r="781" ht="15.75" customHeight="1" s="32"/>
+    <row r="782" ht="15.75" customHeight="1" s="32"/>
+    <row r="783" ht="15.75" customHeight="1" s="32"/>
+    <row r="784" ht="15.75" customHeight="1" s="32"/>
+    <row r="785" ht="15.75" customHeight="1" s="32"/>
+    <row r="786" ht="15.75" customHeight="1" s="32"/>
+    <row r="787" ht="15.75" customHeight="1" s="32"/>
+    <row r="788" ht="15.75" customHeight="1" s="32"/>
+    <row r="789" ht="15.75" customHeight="1" s="32"/>
+    <row r="790" ht="15.75" customHeight="1" s="32"/>
+    <row r="791" ht="15.75" customHeight="1" s="32"/>
+    <row r="792" ht="15.75" customHeight="1" s="32"/>
+    <row r="793" ht="15.75" customHeight="1" s="32"/>
+    <row r="794" ht="15.75" customHeight="1" s="32"/>
+    <row r="795" ht="15.75" customHeight="1" s="32"/>
+    <row r="796" ht="15.75" customHeight="1" s="32"/>
+    <row r="797" ht="15.75" customHeight="1" s="32"/>
+    <row r="798" ht="15.75" customHeight="1" s="32"/>
+    <row r="799" ht="15.75" customHeight="1" s="32"/>
+    <row r="800" ht="15.75" customHeight="1" s="32"/>
+    <row r="801" ht="15.75" customHeight="1" s="32"/>
+    <row r="802" ht="15.75" customHeight="1" s="32"/>
+    <row r="803" ht="15.75" customHeight="1" s="32"/>
+    <row r="804" ht="15.75" customHeight="1" s="32"/>
+    <row r="805" ht="15.75" customHeight="1" s="32"/>
+    <row r="806" ht="15.75" customHeight="1" s="32"/>
+    <row r="807" ht="15.75" customHeight="1" s="32"/>
+    <row r="808" ht="15.75" customHeight="1" s="32"/>
+    <row r="809" ht="15.75" customHeight="1" s="32"/>
+    <row r="810" ht="15.75" customHeight="1" s="32"/>
+    <row r="811" ht="15.75" customHeight="1" s="32"/>
+    <row r="812" ht="15.75" customHeight="1" s="32"/>
+    <row r="813" ht="15.75" customHeight="1" s="32"/>
+    <row r="814" ht="15.75" customHeight="1" s="32"/>
+    <row r="815" ht="15.75" customHeight="1" s="32"/>
+    <row r="816" ht="15.75" customHeight="1" s="32"/>
+    <row r="817" ht="15.75" customHeight="1" s="32"/>
+    <row r="818" ht="15.75" customHeight="1" s="32"/>
+    <row r="819" ht="15.75" customHeight="1" s="32"/>
+    <row r="820" ht="15.75" customHeight="1" s="32"/>
+    <row r="821" ht="15.75" customHeight="1" s="32"/>
+    <row r="822" ht="15.75" customHeight="1" s="32"/>
+    <row r="823" ht="15.75" customHeight="1" s="32"/>
+    <row r="824" ht="15.75" customHeight="1" s="32"/>
+    <row r="825" ht="15.75" customHeight="1" s="32"/>
+    <row r="826" ht="15.75" customHeight="1" s="32"/>
+    <row r="827" ht="15.75" customHeight="1" s="32"/>
+    <row r="828" ht="15.75" customHeight="1" s="32"/>
+    <row r="829" ht="15.75" customHeight="1" s="32"/>
+    <row r="830" ht="15.75" customHeight="1" s="32"/>
+    <row r="831" ht="15.75" customHeight="1" s="32"/>
+    <row r="832" ht="15.75" customHeight="1" s="32"/>
+    <row r="833" ht="15.75" customHeight="1" s="32"/>
+    <row r="834" ht="15.75" customHeight="1" s="32"/>
+    <row r="835" ht="15.75" customHeight="1" s="32"/>
+    <row r="836" ht="15.75" customHeight="1" s="32"/>
+    <row r="837" ht="15.75" customHeight="1" s="32"/>
+    <row r="838" ht="15.75" customHeight="1" s="32"/>
+    <row r="839" ht="15.75" customHeight="1" s="32"/>
+    <row r="840" ht="15.75" customHeight="1" s="32"/>
+    <row r="841" ht="15.75" customHeight="1" s="32"/>
+    <row r="842" ht="15.75" customHeight="1" s="32"/>
+    <row r="843" ht="15.75" customHeight="1" s="32"/>
+    <row r="844" ht="15.75" customHeight="1" s="32"/>
+    <row r="845" ht="15.75" customHeight="1" s="32"/>
+    <row r="846" ht="15.75" customHeight="1" s="32"/>
+    <row r="847" ht="15.75" customHeight="1" s="32"/>
+    <row r="848" ht="15.75" customHeight="1" s="32"/>
+    <row r="849" ht="15.75" customHeight="1" s="32"/>
+    <row r="850" ht="15.75" customHeight="1" s="32"/>
+    <row r="851" ht="15.75" customHeight="1" s="32"/>
+    <row r="852" ht="15.75" customHeight="1" s="32"/>
+    <row r="853" ht="15.75" customHeight="1" s="32"/>
+    <row r="854" ht="15.75" customHeight="1" s="32"/>
+    <row r="855" ht="15.75" customHeight="1" s="32"/>
+    <row r="856" ht="15.75" customHeight="1" s="32"/>
+    <row r="857" ht="15.75" customHeight="1" s="32"/>
+    <row r="858" ht="15.75" customHeight="1" s="32"/>
+    <row r="859" ht="15.75" customHeight="1" s="32"/>
+    <row r="860" ht="15.75" customHeight="1" s="32"/>
+    <row r="861" ht="15.75" customHeight="1" s="32"/>
+    <row r="862" ht="15.75" customHeight="1" s="32"/>
+    <row r="863" ht="15.75" customHeight="1" s="32"/>
+    <row r="864" ht="15.75" customHeight="1" s="32"/>
+    <row r="865" ht="15.75" customHeight="1" s="32"/>
+    <row r="866" ht="15.75" customHeight="1" s="32"/>
+    <row r="867" ht="15.75" customHeight="1" s="32"/>
+    <row r="868" ht="15.75" customHeight="1" s="32"/>
+    <row r="869" ht="15.75" customHeight="1" s="32"/>
+    <row r="870" ht="15.75" customHeight="1" s="32"/>
+    <row r="871" ht="15.75" customHeight="1" s="32"/>
+    <row r="872" ht="15.75" customHeight="1" s="32"/>
+    <row r="873" ht="15.75" customHeight="1" s="32"/>
+    <row r="874" ht="15.75" customHeight="1" s="32"/>
+    <row r="875" ht="15.75" customHeight="1" s="32"/>
+    <row r="876" ht="15.75" customHeight="1" s="32"/>
+    <row r="877" ht="15.75" customHeight="1" s="32"/>
+    <row r="878" ht="15.75" customHeight="1" s="32"/>
+    <row r="879" ht="15.75" customHeight="1" s="32"/>
+    <row r="880" ht="15.75" customHeight="1" s="32"/>
+    <row r="881" ht="15.75" customHeight="1" s="32"/>
+    <row r="882" ht="15.75" customHeight="1" s="32"/>
+    <row r="883" ht="15.75" customHeight="1" s="32"/>
+    <row r="884" ht="15.75" customHeight="1" s="32"/>
+    <row r="885" ht="15.75" customHeight="1" s="32"/>
+    <row r="886" ht="15.75" customHeight="1" s="32"/>
+    <row r="887" ht="15.75" customHeight="1" s="32"/>
+    <row r="888" ht="15.75" customHeight="1" s="32"/>
+    <row r="889" ht="15.75" customHeight="1" s="32"/>
+    <row r="890" ht="15.75" customHeight="1" s="32"/>
+    <row r="891" ht="15.75" customHeight="1" s="32"/>
+    <row r="892" ht="15.75" customHeight="1" s="32"/>
+    <row r="893" ht="15.75" customHeight="1" s="32"/>
+    <row r="894" ht="15.75" customHeight="1" s="32"/>
+    <row r="895" ht="15.75" customHeight="1" s="32"/>
+    <row r="896" ht="15.75" customHeight="1" s="32"/>
+    <row r="897" ht="15.75" customHeight="1" s="32"/>
+    <row r="898" ht="15.75" customHeight="1" s="32"/>
+    <row r="899" ht="15.75" customHeight="1" s="32"/>
+    <row r="900" ht="15.75" customHeight="1" s="32"/>
+    <row r="901" ht="15.75" customHeight="1" s="32"/>
+    <row r="902" ht="15.75" customHeight="1" s="32"/>
+    <row r="903" ht="15.75" customHeight="1" s="32"/>
+    <row r="904" ht="15.75" customHeight="1" s="32"/>
+    <row r="905" ht="15.75" customHeight="1" s="32"/>
+    <row r="906" ht="15.75" customHeight="1" s="32"/>
+    <row r="907" ht="15.75" customHeight="1" s="32"/>
+    <row r="908" ht="15.75" customHeight="1" s="32"/>
+    <row r="909" ht="15.75" customHeight="1" s="32"/>
+    <row r="910" ht="15.75" customHeight="1" s="32"/>
+    <row r="911" ht="15.75" customHeight="1" s="32"/>
+    <row r="912" ht="15.75" customHeight="1" s="32"/>
+    <row r="913" ht="15.75" customHeight="1" s="32"/>
+    <row r="914" ht="15.75" customHeight="1" s="32"/>
+    <row r="915" ht="15.75" customHeight="1" s="32"/>
+    <row r="916" ht="15.75" customHeight="1" s="32"/>
+    <row r="917" ht="15.75" customHeight="1" s="32"/>
+    <row r="918" ht="15.75" customHeight="1" s="32"/>
+    <row r="919" ht="15.75" customHeight="1" s="32"/>
+    <row r="920" ht="15.75" customHeight="1" s="32"/>
+    <row r="921" ht="15.75" customHeight="1" s="32"/>
+    <row r="922" ht="15.75" customHeight="1" s="32"/>
+    <row r="923" ht="15.75" customHeight="1" s="32"/>
+    <row r="924" ht="15.75" customHeight="1" s="32"/>
+    <row r="925" ht="15.75" customHeight="1" s="32"/>
+    <row r="926" ht="15.75" customHeight="1" s="32"/>
+    <row r="927" ht="15.75" customHeight="1" s="32"/>
+    <row r="928" ht="15.75" customHeight="1" s="32"/>
+    <row r="929" ht="15.75" customHeight="1" s="32"/>
+    <row r="930" ht="15.75" customHeight="1" s="32"/>
+    <row r="931" ht="15.75" customHeight="1" s="32"/>
+    <row r="932" ht="15.75" customHeight="1" s="32"/>
+    <row r="933" ht="15.75" customHeight="1" s="32"/>
+    <row r="934" ht="15.75" customHeight="1" s="32"/>
+    <row r="935" ht="15.75" customHeight="1" s="32"/>
+    <row r="936" ht="15.75" customHeight="1" s="32"/>
+    <row r="937" ht="15.75" customHeight="1" s="32"/>
+    <row r="938" ht="15.75" customHeight="1" s="32"/>
+    <row r="939" ht="15.75" customHeight="1" s="32"/>
+    <row r="940" ht="15.75" customHeight="1" s="32"/>
+    <row r="941" ht="15.75" customHeight="1" s="32"/>
+    <row r="942" ht="15.75" customHeight="1" s="32"/>
+    <row r="943" ht="15.75" customHeight="1" s="32"/>
+    <row r="944" ht="15.75" customHeight="1" s="32"/>
+    <row r="945" ht="15.75" customHeight="1" s="32"/>
+    <row r="946" ht="15.75" customHeight="1" s="32"/>
+    <row r="947" ht="15.75" customHeight="1" s="32"/>
+    <row r="948" ht="15.75" customHeight="1" s="32"/>
+    <row r="949" ht="15.75" customHeight="1" s="32"/>
+    <row r="950" ht="15.75" customHeight="1" s="32"/>
+    <row r="951" ht="15.75" customHeight="1" s="32"/>
+    <row r="952" ht="15.75" customHeight="1" s="32"/>
+    <row r="953" ht="15.75" customHeight="1" s="32"/>
+    <row r="954" ht="15.75" customHeight="1" s="32"/>
+    <row r="955" ht="15.75" customHeight="1" s="32"/>
+    <row r="956" ht="15.75" customHeight="1" s="32"/>
+    <row r="957" ht="15.75" customHeight="1" s="32"/>
+    <row r="958" ht="15.75" customHeight="1" s="32"/>
+    <row r="959" ht="15.75" customHeight="1" s="32"/>
+    <row r="960" ht="15.75" customHeight="1" s="32"/>
+    <row r="961" ht="15.75" customHeight="1" s="32"/>
+    <row r="962" ht="15.75" customHeight="1" s="32"/>
+    <row r="963" ht="15.75" customHeight="1" s="32"/>
+    <row r="964" ht="15.75" customHeight="1" s="32"/>
+    <row r="965" ht="15.75" customHeight="1" s="32"/>
+    <row r="966" ht="15.75" customHeight="1" s="32"/>
+    <row r="967" ht="15.75" customHeight="1" s="32"/>
+    <row r="968" ht="15.75" customHeight="1" s="32"/>
+    <row r="969" ht="15.75" customHeight="1" s="32"/>
+    <row r="970" ht="15.75" customHeight="1" s="32"/>
+    <row r="971" ht="15.75" customHeight="1" s="32"/>
+    <row r="972" ht="15.75" customHeight="1" s="32"/>
+    <row r="973" ht="15.75" customHeight="1" s="32"/>
+    <row r="974" ht="15.75" customHeight="1" s="32"/>
+    <row r="975" ht="15.75" customHeight="1" s="32"/>
+    <row r="976" ht="15.75" customHeight="1" s="32"/>
+    <row r="977" ht="15.75" customHeight="1" s="32"/>
+    <row r="978" ht="15.75" customHeight="1" s="32"/>
+    <row r="979" ht="15.75" customHeight="1" s="32"/>
+    <row r="980" ht="15.75" customHeight="1" s="32"/>
+    <row r="981" ht="15.75" customHeight="1" s="32"/>
+    <row r="982" ht="15.75" customHeight="1" s="32"/>
+    <row r="983" ht="15.75" customHeight="1" s="32"/>
+    <row r="984" ht="15.75" customHeight="1" s="32"/>
+    <row r="985" ht="15.75" customHeight="1" s="32"/>
+    <row r="986" ht="15.75" customHeight="1" s="32"/>
+    <row r="987" ht="15.75" customHeight="1" s="32"/>
+    <row r="988" ht="15.75" customHeight="1" s="32"/>
+    <row r="989" ht="15.75" customHeight="1" s="32"/>
+    <row r="990" ht="15.75" customHeight="1" s="32"/>
+    <row r="991" ht="15.75" customHeight="1" s="32"/>
+    <row r="992" ht="15.75" customHeight="1" s="32"/>
+    <row r="993" ht="15.75" customHeight="1" s="32"/>
+    <row r="994" ht="15.75" customHeight="1" s="32"/>
+    <row r="995" ht="15.75" customHeight="1" s="32"/>
+    <row r="996" ht="15.75" customHeight="1" s="32"/>
+    <row r="997" ht="15.75" customHeight="1" s="32"/>
+    <row r="998" ht="15.75" customHeight="1" s="32"/>
+    <row r="999" ht="15.75" customHeight="1" s="32"/>
+    <row r="1000" ht="15.75" customHeight="1" s="32"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col width="24.75" customWidth="1" style="32" min="1" max="1"/>
+    <col width="56.75" customWidth="1" style="32" min="2" max="2"/>
+    <col width="12.63" customWidth="1" style="32" min="3" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1" s="32">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n"/>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="32">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="36" t="inlineStr">
         <is>
           <t>SPM-28-TC15</t>
         </is>
@@ -9882,7 +11137,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -9928,7 +11183,7 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9940,7 +11195,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -9964,7 +11219,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="21" t="n">
+      <c r="B15" s="31" t="n">
         <v>46295</v>
       </c>
     </row>
@@ -9997,7 +11252,7 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10009,7 +11264,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -10033,7 +11288,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B22" s="31" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -11024,1224 +12279,146 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24.75" customWidth="1" style="32" min="1" max="1"/>
-    <col width="56.75" customWidth="1" style="32" min="2" max="2"/>
-    <col width="12.63" customWidth="1" style="32" min="3" max="6"/>
+    <col width="5" customWidth="1" style="32" min="1" max="1"/>
+    <col width="75" customWidth="1" style="32" min="2" max="2"/>
+    <col width="40" customWidth="1" style="32" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="32">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="32">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-28-TC01</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="84.75" customHeight="1" s="32">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Test data loaded: `npm run fixtures:spm28` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM28 …' events, EVT-000124 to EVT-000130, never anyone else's data).
- Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), Event Coordinator.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="17.25" customHeight="1" s="32">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>1. Click 'Review Queue' in the sidebar</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="71.25" customHeight="1" s="32">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Must appear (Under review, coordinator Daniel Tan): SPM28 Nusantara Product Launch (EVT-000124), SPM28 Harbourline Client Seminar (EVT-000125) | Must not appear: SPM28 Kirana Regional Offsite (EVT-000126, coordinator Priya Raj), SPM28 Straits Journal Club (EVT-000127, coordinator Joel Fernandez)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="98.25" customHeight="1" s="32">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Step 1: The Review Queue page lists 'SPM28 Nusantara Product Launch' (client 'Nusantara Tech Labs', 17 Mar 2027, 'Under review' badge) and 'SPM28 Harbourline Client Seminar'. Other Under review events assigned to Daniel Tan may also appear; only the SPM28 events are checked here. 'SPM28 Kirana Regional Offsite' and 'SPM28 Straits Journal Club' are not listed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17.25" customHeight="1" s="32">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Kristen</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1" s="32">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Creation Date</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="n">
-        <v>46295</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" s="32"/>
-    <row r="10" ht="15.75" customHeight="1" s="32">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="15" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="32">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The Review Queue page lists 'SPM28 Nusantara Product Launch' (client 'Nusantara Tech Labs', 17 Mar 2027, 'Under review' badge) and 'SPM28 Harbourline Client Seminar'. Other Under review events assigned to Daniel Tan may also appear; only the SPM28 events are checked here. 'SPM28 Kirana Regional Offsite' and 'SPM28 Straits Journal Club' are not listed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1" s="32">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15.75" customHeight="1" s="32">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1" s="32">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>Kristen</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15.75" customHeight="1" s="32">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B15" s="21" t="n">
-        <v>46295</v>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1" s="32"/>
-    <row r="17" ht="15.75" customHeight="1" s="32">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="32">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The Review Queue page lists 'SPM28 Nusantara Product Launch' (client 'Nusantara Tech Labs', 17 Mar 2027, 'Under review' badge) and 'SPM28 Harbourline Client Seminar'. Other Under review events assigned to Daniel Tan may also appear; only the SPM28 events are checked here. 'SPM28 Kirana Regional Offsite' and 'SPM28 Straits Journal Club' are not listed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" s="32">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1" s="32">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1" s="32">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>Sammi</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1" s="32">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="n">
-        <v>46296</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1" s="32"/>
-    <row r="24" ht="15.75" customHeight="1" s="32"/>
-    <row r="25" ht="15.75" customHeight="1" s="32"/>
-    <row r="26" ht="15.75" customHeight="1" s="32"/>
-    <row r="27" ht="15.75" customHeight="1" s="32"/>
-    <row r="28" ht="15.75" customHeight="1" s="32"/>
-    <row r="29" ht="15.75" customHeight="1" s="32"/>
-    <row r="30" ht="15.75" customHeight="1" s="32"/>
-    <row r="31" ht="15.75" customHeight="1" s="32"/>
-    <row r="32" ht="15.75" customHeight="1" s="32"/>
-    <row r="33" ht="15.75" customHeight="1" s="32"/>
-    <row r="34" ht="15.75" customHeight="1" s="32"/>
-    <row r="35" ht="15.75" customHeight="1" s="32"/>
-    <row r="36" ht="15.75" customHeight="1" s="32"/>
-    <row r="37" ht="15.75" customHeight="1" s="32"/>
-    <row r="38" ht="15.75" customHeight="1" s="32"/>
-    <row r="39" ht="15.75" customHeight="1" s="32"/>
-    <row r="40" ht="15.75" customHeight="1" s="32"/>
-    <row r="41" ht="15.75" customHeight="1" s="32"/>
-    <row r="42" ht="15.75" customHeight="1" s="32"/>
-    <row r="43" ht="15.75" customHeight="1" s="32"/>
-    <row r="44" ht="15.75" customHeight="1" s="32"/>
-    <row r="45" ht="15.75" customHeight="1" s="32"/>
-    <row r="46" ht="15.75" customHeight="1" s="32"/>
-    <row r="47" ht="15.75" customHeight="1" s="32"/>
-    <row r="48" ht="15.75" customHeight="1" s="32"/>
-    <row r="49" ht="15.75" customHeight="1" s="32"/>
-    <row r="50" ht="15.75" customHeight="1" s="32"/>
-    <row r="51" ht="15.75" customHeight="1" s="32"/>
-    <row r="52" ht="15.75" customHeight="1" s="32"/>
-    <row r="53" ht="15.75" customHeight="1" s="32"/>
-    <row r="54" ht="15.75" customHeight="1" s="32"/>
-    <row r="55" ht="15.75" customHeight="1" s="32"/>
-    <row r="56" ht="15.75" customHeight="1" s="32"/>
-    <row r="57" ht="15.75" customHeight="1" s="32"/>
-    <row r="58" ht="15.75" customHeight="1" s="32"/>
-    <row r="59" ht="15.75" customHeight="1" s="32"/>
-    <row r="60" ht="15.75" customHeight="1" s="32"/>
-    <row r="61" ht="15.75" customHeight="1" s="32"/>
-    <row r="62" ht="15.75" customHeight="1" s="32"/>
-    <row r="63" ht="15.75" customHeight="1" s="32"/>
-    <row r="64" ht="15.75" customHeight="1" s="32"/>
-    <row r="65" ht="15.75" customHeight="1" s="32"/>
-    <row r="66" ht="15.75" customHeight="1" s="32"/>
-    <row r="67" ht="15.75" customHeight="1" s="32"/>
-    <row r="68" ht="15.75" customHeight="1" s="32"/>
-    <row r="69" ht="15.75" customHeight="1" s="32"/>
-    <row r="70" ht="15.75" customHeight="1" s="32"/>
-    <row r="71" ht="15.75" customHeight="1" s="32"/>
-    <row r="72" ht="15.75" customHeight="1" s="32"/>
-    <row r="73" ht="15.75" customHeight="1" s="32"/>
-    <row r="74" ht="15.75" customHeight="1" s="32"/>
-    <row r="75" ht="15.75" customHeight="1" s="32"/>
-    <row r="76" ht="15.75" customHeight="1" s="32"/>
-    <row r="77" ht="15.75" customHeight="1" s="32"/>
-    <row r="78" ht="15.75" customHeight="1" s="32"/>
-    <row r="79" ht="15.75" customHeight="1" s="32"/>
-    <row r="80" ht="15.75" customHeight="1" s="32"/>
-    <row r="81" ht="15.75" customHeight="1" s="32"/>
-    <row r="82" ht="15.75" customHeight="1" s="32"/>
-    <row r="83" ht="15.75" customHeight="1" s="32"/>
-    <row r="84" ht="15.75" customHeight="1" s="32"/>
-    <row r="85" ht="15.75" customHeight="1" s="32"/>
-    <row r="86" ht="15.75" customHeight="1" s="32"/>
-    <row r="87" ht="15.75" customHeight="1" s="32"/>
-    <row r="88" ht="15.75" customHeight="1" s="32"/>
-    <row r="89" ht="15.75" customHeight="1" s="32"/>
-    <row r="90" ht="15.75" customHeight="1" s="32"/>
-    <row r="91" ht="15.75" customHeight="1" s="32"/>
-    <row r="92" ht="15.75" customHeight="1" s="32"/>
-    <row r="93" ht="15.75" customHeight="1" s="32"/>
-    <row r="94" ht="15.75" customHeight="1" s="32"/>
-    <row r="95" ht="15.75" customHeight="1" s="32"/>
-    <row r="96" ht="15.75" customHeight="1" s="32"/>
-    <row r="97" ht="15.75" customHeight="1" s="32"/>
-    <row r="98" ht="15.75" customHeight="1" s="32"/>
-    <row r="99" ht="15.75" customHeight="1" s="32"/>
-    <row r="100" ht="15.75" customHeight="1" s="32"/>
-    <row r="101" ht="15.75" customHeight="1" s="32"/>
-    <row r="102" ht="15.75" customHeight="1" s="32"/>
-    <row r="103" ht="15.75" customHeight="1" s="32"/>
-    <row r="104" ht="15.75" customHeight="1" s="32"/>
-    <row r="105" ht="15.75" customHeight="1" s="32"/>
-    <row r="106" ht="15.75" customHeight="1" s="32"/>
-    <row r="107" ht="15.75" customHeight="1" s="32"/>
-    <row r="108" ht="15.75" customHeight="1" s="32"/>
-    <row r="109" ht="15.75" customHeight="1" s="32"/>
-    <row r="110" ht="15.75" customHeight="1" s="32"/>
-    <row r="111" ht="15.75" customHeight="1" s="32"/>
-    <row r="112" ht="15.75" customHeight="1" s="32"/>
-    <row r="113" ht="15.75" customHeight="1" s="32"/>
-    <row r="114" ht="15.75" customHeight="1" s="32"/>
-    <row r="115" ht="15.75" customHeight="1" s="32"/>
-    <row r="116" ht="15.75" customHeight="1" s="32"/>
-    <row r="117" ht="15.75" customHeight="1" s="32"/>
-    <row r="118" ht="15.75" customHeight="1" s="32"/>
-    <row r="119" ht="15.75" customHeight="1" s="32"/>
-    <row r="120" ht="15.75" customHeight="1" s="32"/>
-    <row r="121" ht="15.75" customHeight="1" s="32"/>
-    <row r="122" ht="15.75" customHeight="1" s="32"/>
-    <row r="123" ht="15.75" customHeight="1" s="32"/>
-    <row r="124" ht="15.75" customHeight="1" s="32"/>
-    <row r="125" ht="15.75" customHeight="1" s="32"/>
-    <row r="126" ht="15.75" customHeight="1" s="32"/>
-    <row r="127" ht="15.75" customHeight="1" s="32"/>
-    <row r="128" ht="15.75" customHeight="1" s="32"/>
-    <row r="129" ht="15.75" customHeight="1" s="32"/>
-    <row r="130" ht="15.75" customHeight="1" s="32"/>
-    <row r="131" ht="15.75" customHeight="1" s="32"/>
-    <row r="132" ht="15.75" customHeight="1" s="32"/>
-    <row r="133" ht="15.75" customHeight="1" s="32"/>
-    <row r="134" ht="15.75" customHeight="1" s="32"/>
-    <row r="135" ht="15.75" customHeight="1" s="32"/>
-    <row r="136" ht="15.75" customHeight="1" s="32"/>
-    <row r="137" ht="15.75" customHeight="1" s="32"/>
-    <row r="138" ht="15.75" customHeight="1" s="32"/>
-    <row r="139" ht="15.75" customHeight="1" s="32"/>
-    <row r="140" ht="15.75" customHeight="1" s="32"/>
-    <row r="141" ht="15.75" customHeight="1" s="32"/>
-    <row r="142" ht="15.75" customHeight="1" s="32"/>
-    <row r="143" ht="15.75" customHeight="1" s="32"/>
-    <row r="144" ht="15.75" customHeight="1" s="32"/>
-    <row r="145" ht="15.75" customHeight="1" s="32"/>
-    <row r="146" ht="15.75" customHeight="1" s="32"/>
-    <row r="147" ht="15.75" customHeight="1" s="32"/>
-    <row r="148" ht="15.75" customHeight="1" s="32"/>
-    <row r="149" ht="15.75" customHeight="1" s="32"/>
-    <row r="150" ht="15.75" customHeight="1" s="32"/>
-    <row r="151" ht="15.75" customHeight="1" s="32"/>
-    <row r="152" ht="15.75" customHeight="1" s="32"/>
-    <row r="153" ht="15.75" customHeight="1" s="32"/>
-    <row r="154" ht="15.75" customHeight="1" s="32"/>
-    <row r="155" ht="15.75" customHeight="1" s="32"/>
-    <row r="156" ht="15.75" customHeight="1" s="32"/>
-    <row r="157" ht="15.75" customHeight="1" s="32"/>
-    <row r="158" ht="15.75" customHeight="1" s="32"/>
-    <row r="159" ht="15.75" customHeight="1" s="32"/>
-    <row r="160" ht="15.75" customHeight="1" s="32"/>
-    <row r="161" ht="15.75" customHeight="1" s="32"/>
-    <row r="162" ht="15.75" customHeight="1" s="32"/>
-    <row r="163" ht="15.75" customHeight="1" s="32"/>
-    <row r="164" ht="15.75" customHeight="1" s="32"/>
-    <row r="165" ht="15.75" customHeight="1" s="32"/>
-    <row r="166" ht="15.75" customHeight="1" s="32"/>
-    <row r="167" ht="15.75" customHeight="1" s="32"/>
-    <row r="168" ht="15.75" customHeight="1" s="32"/>
-    <row r="169" ht="15.75" customHeight="1" s="32"/>
-    <row r="170" ht="15.75" customHeight="1" s="32"/>
-    <row r="171" ht="15.75" customHeight="1" s="32"/>
-    <row r="172" ht="15.75" customHeight="1" s="32"/>
-    <row r="173" ht="15.75" customHeight="1" s="32"/>
-    <row r="174" ht="15.75" customHeight="1" s="32"/>
-    <row r="175" ht="15.75" customHeight="1" s="32"/>
-    <row r="176" ht="15.75" customHeight="1" s="32"/>
-    <row r="177" ht="15.75" customHeight="1" s="32"/>
-    <row r="178" ht="15.75" customHeight="1" s="32"/>
-    <row r="179" ht="15.75" customHeight="1" s="32"/>
-    <row r="180" ht="15.75" customHeight="1" s="32"/>
-    <row r="181" ht="15.75" customHeight="1" s="32"/>
-    <row r="182" ht="15.75" customHeight="1" s="32"/>
-    <row r="183" ht="15.75" customHeight="1" s="32"/>
-    <row r="184" ht="15.75" customHeight="1" s="32"/>
-    <row r="185" ht="15.75" customHeight="1" s="32"/>
-    <row r="186" ht="15.75" customHeight="1" s="32"/>
-    <row r="187" ht="15.75" customHeight="1" s="32"/>
-    <row r="188" ht="15.75" customHeight="1" s="32"/>
-    <row r="189" ht="15.75" customHeight="1" s="32"/>
-    <row r="190" ht="15.75" customHeight="1" s="32"/>
-    <row r="191" ht="15.75" customHeight="1" s="32"/>
-    <row r="192" ht="15.75" customHeight="1" s="32"/>
-    <row r="193" ht="15.75" customHeight="1" s="32"/>
-    <row r="194" ht="15.75" customHeight="1" s="32"/>
-    <row r="195" ht="15.75" customHeight="1" s="32"/>
-    <row r="196" ht="15.75" customHeight="1" s="32"/>
-    <row r="197" ht="15.75" customHeight="1" s="32"/>
-    <row r="198" ht="15.75" customHeight="1" s="32"/>
-    <row r="199" ht="15.75" customHeight="1" s="32"/>
-    <row r="200" ht="15.75" customHeight="1" s="32"/>
-    <row r="201" ht="15.75" customHeight="1" s="32"/>
-    <row r="202" ht="15.75" customHeight="1" s="32"/>
-    <row r="203" ht="15.75" customHeight="1" s="32"/>
-    <row r="204" ht="15.75" customHeight="1" s="32"/>
-    <row r="205" ht="15.75" customHeight="1" s="32"/>
-    <row r="206" ht="15.75" customHeight="1" s="32"/>
-    <row r="207" ht="15.75" customHeight="1" s="32"/>
-    <row r="208" ht="15.75" customHeight="1" s="32"/>
-    <row r="209" ht="15.75" customHeight="1" s="32"/>
-    <row r="210" ht="15.75" customHeight="1" s="32"/>
-    <row r="211" ht="15.75" customHeight="1" s="32"/>
-    <row r="212" ht="15.75" customHeight="1" s="32"/>
-    <row r="213" ht="15.75" customHeight="1" s="32"/>
-    <row r="214" ht="15.75" customHeight="1" s="32"/>
-    <row r="215" ht="15.75" customHeight="1" s="32"/>
-    <row r="216" ht="15.75" customHeight="1" s="32"/>
-    <row r="217" ht="15.75" customHeight="1" s="32"/>
-    <row r="218" ht="15.75" customHeight="1" s="32"/>
-    <row r="219" ht="15.75" customHeight="1" s="32"/>
-    <row r="220" ht="15.75" customHeight="1" s="32"/>
-    <row r="221" ht="15.75" customHeight="1" s="32"/>
-    <row r="222" ht="15.75" customHeight="1" s="32"/>
-    <row r="223" ht="15.75" customHeight="1" s="32"/>
-    <row r="224" ht="15.75" customHeight="1" s="32"/>
-    <row r="225" ht="15.75" customHeight="1" s="32"/>
-    <row r="226" ht="15.75" customHeight="1" s="32"/>
-    <row r="227" ht="15.75" customHeight="1" s="32"/>
-    <row r="228" ht="15.75" customHeight="1" s="32"/>
-    <row r="229" ht="15.75" customHeight="1" s="32"/>
-    <row r="230" ht="15.75" customHeight="1" s="32"/>
-    <row r="231" ht="15.75" customHeight="1" s="32"/>
-    <row r="232" ht="15.75" customHeight="1" s="32"/>
-    <row r="233" ht="15.75" customHeight="1" s="32"/>
-    <row r="234" ht="15.75" customHeight="1" s="32"/>
-    <row r="235" ht="15.75" customHeight="1" s="32"/>
-    <row r="236" ht="15.75" customHeight="1" s="32"/>
-    <row r="237" ht="15.75" customHeight="1" s="32"/>
-    <row r="238" ht="15.75" customHeight="1" s="32"/>
-    <row r="239" ht="15.75" customHeight="1" s="32"/>
-    <row r="240" ht="15.75" customHeight="1" s="32"/>
-    <row r="241" ht="15.75" customHeight="1" s="32"/>
-    <row r="242" ht="15.75" customHeight="1" s="32"/>
-    <row r="243" ht="15.75" customHeight="1" s="32"/>
-    <row r="244" ht="15.75" customHeight="1" s="32"/>
-    <row r="245" ht="15.75" customHeight="1" s="32"/>
-    <row r="246" ht="15.75" customHeight="1" s="32"/>
-    <row r="247" ht="15.75" customHeight="1" s="32"/>
-    <row r="248" ht="15.75" customHeight="1" s="32"/>
-    <row r="249" ht="15.75" customHeight="1" s="32"/>
-    <row r="250" ht="15.75" customHeight="1" s="32"/>
-    <row r="251" ht="15.75" customHeight="1" s="32"/>
-    <row r="252" ht="15.75" customHeight="1" s="32"/>
-    <row r="253" ht="15.75" customHeight="1" s="32"/>
-    <row r="254" ht="15.75" customHeight="1" s="32"/>
-    <row r="255" ht="15.75" customHeight="1" s="32"/>
-    <row r="256" ht="15.75" customHeight="1" s="32"/>
-    <row r="257" ht="15.75" customHeight="1" s="32"/>
-    <row r="258" ht="15.75" customHeight="1" s="32"/>
-    <row r="259" ht="15.75" customHeight="1" s="32"/>
-    <row r="260" ht="15.75" customHeight="1" s="32"/>
-    <row r="261" ht="15.75" customHeight="1" s="32"/>
-    <row r="262" ht="15.75" customHeight="1" s="32"/>
-    <row r="263" ht="15.75" customHeight="1" s="32"/>
-    <row r="264" ht="15.75" customHeight="1" s="32"/>
-    <row r="265" ht="15.75" customHeight="1" s="32"/>
-    <row r="266" ht="15.75" customHeight="1" s="32"/>
-    <row r="267" ht="15.75" customHeight="1" s="32"/>
-    <row r="268" ht="15.75" customHeight="1" s="32"/>
-    <row r="269" ht="15.75" customHeight="1" s="32"/>
-    <row r="270" ht="15.75" customHeight="1" s="32"/>
-    <row r="271" ht="15.75" customHeight="1" s="32"/>
-    <row r="272" ht="15.75" customHeight="1" s="32"/>
-    <row r="273" ht="15.75" customHeight="1" s="32"/>
-    <row r="274" ht="15.75" customHeight="1" s="32"/>
-    <row r="275" ht="15.75" customHeight="1" s="32"/>
-    <row r="276" ht="15.75" customHeight="1" s="32"/>
-    <row r="277" ht="15.75" customHeight="1" s="32"/>
-    <row r="278" ht="15.75" customHeight="1" s="32"/>
-    <row r="279" ht="15.75" customHeight="1" s="32"/>
-    <row r="280" ht="15.75" customHeight="1" s="32"/>
-    <row r="281" ht="15.75" customHeight="1" s="32"/>
-    <row r="282" ht="15.75" customHeight="1" s="32"/>
-    <row r="283" ht="15.75" customHeight="1" s="32"/>
-    <row r="284" ht="15.75" customHeight="1" s="32"/>
-    <row r="285" ht="15.75" customHeight="1" s="32"/>
-    <row r="286" ht="15.75" customHeight="1" s="32"/>
-    <row r="287" ht="15.75" customHeight="1" s="32"/>
-    <row r="288" ht="15.75" customHeight="1" s="32"/>
-    <row r="289" ht="15.75" customHeight="1" s="32"/>
-    <row r="290" ht="15.75" customHeight="1" s="32"/>
-    <row r="291" ht="15.75" customHeight="1" s="32"/>
-    <row r="292" ht="15.75" customHeight="1" s="32"/>
-    <row r="293" ht="15.75" customHeight="1" s="32"/>
-    <row r="294" ht="15.75" customHeight="1" s="32"/>
-    <row r="295" ht="15.75" customHeight="1" s="32"/>
-    <row r="296" ht="15.75" customHeight="1" s="32"/>
-    <row r="297" ht="15.75" customHeight="1" s="32"/>
-    <row r="298" ht="15.75" customHeight="1" s="32"/>
-    <row r="299" ht="15.75" customHeight="1" s="32"/>
-    <row r="300" ht="15.75" customHeight="1" s="32"/>
-    <row r="301" ht="15.75" customHeight="1" s="32"/>
-    <row r="302" ht="15.75" customHeight="1" s="32"/>
-    <row r="303" ht="15.75" customHeight="1" s="32"/>
-    <row r="304" ht="15.75" customHeight="1" s="32"/>
-    <row r="305" ht="15.75" customHeight="1" s="32"/>
-    <row r="306" ht="15.75" customHeight="1" s="32"/>
-    <row r="307" ht="15.75" customHeight="1" s="32"/>
-    <row r="308" ht="15.75" customHeight="1" s="32"/>
-    <row r="309" ht="15.75" customHeight="1" s="32"/>
-    <row r="310" ht="15.75" customHeight="1" s="32"/>
-    <row r="311" ht="15.75" customHeight="1" s="32"/>
-    <row r="312" ht="15.75" customHeight="1" s="32"/>
-    <row r="313" ht="15.75" customHeight="1" s="32"/>
-    <row r="314" ht="15.75" customHeight="1" s="32"/>
-    <row r="315" ht="15.75" customHeight="1" s="32"/>
-    <row r="316" ht="15.75" customHeight="1" s="32"/>
-    <row r="317" ht="15.75" customHeight="1" s="32"/>
-    <row r="318" ht="15.75" customHeight="1" s="32"/>
-    <row r="319" ht="15.75" customHeight="1" s="32"/>
-    <row r="320" ht="15.75" customHeight="1" s="32"/>
-    <row r="321" ht="15.75" customHeight="1" s="32"/>
-    <row r="322" ht="15.75" customHeight="1" s="32"/>
-    <row r="323" ht="15.75" customHeight="1" s="32"/>
-    <row r="324" ht="15.75" customHeight="1" s="32"/>
-    <row r="325" ht="15.75" customHeight="1" s="32"/>
-    <row r="326" ht="15.75" customHeight="1" s="32"/>
-    <row r="327" ht="15.75" customHeight="1" s="32"/>
-    <row r="328" ht="15.75" customHeight="1" s="32"/>
-    <row r="329" ht="15.75" customHeight="1" s="32"/>
-    <row r="330" ht="15.75" customHeight="1" s="32"/>
-    <row r="331" ht="15.75" customHeight="1" s="32"/>
-    <row r="332" ht="15.75" customHeight="1" s="32"/>
-    <row r="333" ht="15.75" customHeight="1" s="32"/>
-    <row r="334" ht="15.75" customHeight="1" s="32"/>
-    <row r="335" ht="15.75" customHeight="1" s="32"/>
-    <row r="336" ht="15.75" customHeight="1" s="32"/>
-    <row r="337" ht="15.75" customHeight="1" s="32"/>
-    <row r="338" ht="15.75" customHeight="1" s="32"/>
-    <row r="339" ht="15.75" customHeight="1" s="32"/>
-    <row r="340" ht="15.75" customHeight="1" s="32"/>
-    <row r="341" ht="15.75" customHeight="1" s="32"/>
-    <row r="342" ht="15.75" customHeight="1" s="32"/>
-    <row r="343" ht="15.75" customHeight="1" s="32"/>
-    <row r="344" ht="15.75" customHeight="1" s="32"/>
-    <row r="345" ht="15.75" customHeight="1" s="32"/>
-    <row r="346" ht="15.75" customHeight="1" s="32"/>
-    <row r="347" ht="15.75" customHeight="1" s="32"/>
-    <row r="348" ht="15.75" customHeight="1" s="32"/>
-    <row r="349" ht="15.75" customHeight="1" s="32"/>
-    <row r="350" ht="15.75" customHeight="1" s="32"/>
-    <row r="351" ht="15.75" customHeight="1" s="32"/>
-    <row r="352" ht="15.75" customHeight="1" s="32"/>
-    <row r="353" ht="15.75" customHeight="1" s="32"/>
-    <row r="354" ht="15.75" customHeight="1" s="32"/>
-    <row r="355" ht="15.75" customHeight="1" s="32"/>
-    <row r="356" ht="15.75" customHeight="1" s="32"/>
-    <row r="357" ht="15.75" customHeight="1" s="32"/>
-    <row r="358" ht="15.75" customHeight="1" s="32"/>
-    <row r="359" ht="15.75" customHeight="1" s="32"/>
-    <row r="360" ht="15.75" customHeight="1" s="32"/>
-    <row r="361" ht="15.75" customHeight="1" s="32"/>
-    <row r="362" ht="15.75" customHeight="1" s="32"/>
-    <row r="363" ht="15.75" customHeight="1" s="32"/>
-    <row r="364" ht="15.75" customHeight="1" s="32"/>
-    <row r="365" ht="15.75" customHeight="1" s="32"/>
-    <row r="366" ht="15.75" customHeight="1" s="32"/>
-    <row r="367" ht="15.75" customHeight="1" s="32"/>
-    <row r="368" ht="15.75" customHeight="1" s="32"/>
-    <row r="369" ht="15.75" customHeight="1" s="32"/>
-    <row r="370" ht="15.75" customHeight="1" s="32"/>
-    <row r="371" ht="15.75" customHeight="1" s="32"/>
-    <row r="372" ht="15.75" customHeight="1" s="32"/>
-    <row r="373" ht="15.75" customHeight="1" s="32"/>
-    <row r="374" ht="15.75" customHeight="1" s="32"/>
-    <row r="375" ht="15.75" customHeight="1" s="32"/>
-    <row r="376" ht="15.75" customHeight="1" s="32"/>
-    <row r="377" ht="15.75" customHeight="1" s="32"/>
-    <row r="378" ht="15.75" customHeight="1" s="32"/>
-    <row r="379" ht="15.75" customHeight="1" s="32"/>
-    <row r="380" ht="15.75" customHeight="1" s="32"/>
-    <row r="381" ht="15.75" customHeight="1" s="32"/>
-    <row r="382" ht="15.75" customHeight="1" s="32"/>
-    <row r="383" ht="15.75" customHeight="1" s="32"/>
-    <row r="384" ht="15.75" customHeight="1" s="32"/>
-    <row r="385" ht="15.75" customHeight="1" s="32"/>
-    <row r="386" ht="15.75" customHeight="1" s="32"/>
-    <row r="387" ht="15.75" customHeight="1" s="32"/>
-    <row r="388" ht="15.75" customHeight="1" s="32"/>
-    <row r="389" ht="15.75" customHeight="1" s="32"/>
-    <row r="390" ht="15.75" customHeight="1" s="32"/>
-    <row r="391" ht="15.75" customHeight="1" s="32"/>
-    <row r="392" ht="15.75" customHeight="1" s="32"/>
-    <row r="393" ht="15.75" customHeight="1" s="32"/>
-    <row r="394" ht="15.75" customHeight="1" s="32"/>
-    <row r="395" ht="15.75" customHeight="1" s="32"/>
-    <row r="396" ht="15.75" customHeight="1" s="32"/>
-    <row r="397" ht="15.75" customHeight="1" s="32"/>
-    <row r="398" ht="15.75" customHeight="1" s="32"/>
-    <row r="399" ht="15.75" customHeight="1" s="32"/>
-    <row r="400" ht="15.75" customHeight="1" s="32"/>
-    <row r="401" ht="15.75" customHeight="1" s="32"/>
-    <row r="402" ht="15.75" customHeight="1" s="32"/>
-    <row r="403" ht="15.75" customHeight="1" s="32"/>
-    <row r="404" ht="15.75" customHeight="1" s="32"/>
-    <row r="405" ht="15.75" customHeight="1" s="32"/>
-    <row r="406" ht="15.75" customHeight="1" s="32"/>
-    <row r="407" ht="15.75" customHeight="1" s="32"/>
-    <row r="408" ht="15.75" customHeight="1" s="32"/>
-    <row r="409" ht="15.75" customHeight="1" s="32"/>
-    <row r="410" ht="15.75" customHeight="1" s="32"/>
-    <row r="411" ht="15.75" customHeight="1" s="32"/>
-    <row r="412" ht="15.75" customHeight="1" s="32"/>
-    <row r="413" ht="15.75" customHeight="1" s="32"/>
-    <row r="414" ht="15.75" customHeight="1" s="32"/>
-    <row r="415" ht="15.75" customHeight="1" s="32"/>
-    <row r="416" ht="15.75" customHeight="1" s="32"/>
-    <row r="417" ht="15.75" customHeight="1" s="32"/>
-    <row r="418" ht="15.75" customHeight="1" s="32"/>
-    <row r="419" ht="15.75" customHeight="1" s="32"/>
-    <row r="420" ht="15.75" customHeight="1" s="32"/>
-    <row r="421" ht="15.75" customHeight="1" s="32"/>
-    <row r="422" ht="15.75" customHeight="1" s="32"/>
-    <row r="423" ht="15.75" customHeight="1" s="32"/>
-    <row r="424" ht="15.75" customHeight="1" s="32"/>
-    <row r="425" ht="15.75" customHeight="1" s="32"/>
-    <row r="426" ht="15.75" customHeight="1" s="32"/>
-    <row r="427" ht="15.75" customHeight="1" s="32"/>
-    <row r="428" ht="15.75" customHeight="1" s="32"/>
-    <row r="429" ht="15.75" customHeight="1" s="32"/>
-    <row r="430" ht="15.75" customHeight="1" s="32"/>
-    <row r="431" ht="15.75" customHeight="1" s="32"/>
-    <row r="432" ht="15.75" customHeight="1" s="32"/>
-    <row r="433" ht="15.75" customHeight="1" s="32"/>
-    <row r="434" ht="15.75" customHeight="1" s="32"/>
-    <row r="435" ht="15.75" customHeight="1" s="32"/>
-    <row r="436" ht="15.75" customHeight="1" s="32"/>
-    <row r="437" ht="15.75" customHeight="1" s="32"/>
-    <row r="438" ht="15.75" customHeight="1" s="32"/>
-    <row r="439" ht="15.75" customHeight="1" s="32"/>
-    <row r="440" ht="15.75" customHeight="1" s="32"/>
-    <row r="441" ht="15.75" customHeight="1" s="32"/>
-    <row r="442" ht="15.75" customHeight="1" s="32"/>
-    <row r="443" ht="15.75" customHeight="1" s="32"/>
-    <row r="444" ht="15.75" customHeight="1" s="32"/>
-    <row r="445" ht="15.75" customHeight="1" s="32"/>
-    <row r="446" ht="15.75" customHeight="1" s="32"/>
-    <row r="447" ht="15.75" customHeight="1" s="32"/>
-    <row r="448" ht="15.75" customHeight="1" s="32"/>
-    <row r="449" ht="15.75" customHeight="1" s="32"/>
-    <row r="450" ht="15.75" customHeight="1" s="32"/>
-    <row r="451" ht="15.75" customHeight="1" s="32"/>
-    <row r="452" ht="15.75" customHeight="1" s="32"/>
-    <row r="453" ht="15.75" customHeight="1" s="32"/>
-    <row r="454" ht="15.75" customHeight="1" s="32"/>
-    <row r="455" ht="15.75" customHeight="1" s="32"/>
-    <row r="456" ht="15.75" customHeight="1" s="32"/>
-    <row r="457" ht="15.75" customHeight="1" s="32"/>
-    <row r="458" ht="15.75" customHeight="1" s="32"/>
-    <row r="459" ht="15.75" customHeight="1" s="32"/>
-    <row r="460" ht="15.75" customHeight="1" s="32"/>
-    <row r="461" ht="15.75" customHeight="1" s="32"/>
-    <row r="462" ht="15.75" customHeight="1" s="32"/>
-    <row r="463" ht="15.75" customHeight="1" s="32"/>
-    <row r="464" ht="15.75" customHeight="1" s="32"/>
-    <row r="465" ht="15.75" customHeight="1" s="32"/>
-    <row r="466" ht="15.75" customHeight="1" s="32"/>
-    <row r="467" ht="15.75" customHeight="1" s="32"/>
-    <row r="468" ht="15.75" customHeight="1" s="32"/>
-    <row r="469" ht="15.75" customHeight="1" s="32"/>
-    <row r="470" ht="15.75" customHeight="1" s="32"/>
-    <row r="471" ht="15.75" customHeight="1" s="32"/>
-    <row r="472" ht="15.75" customHeight="1" s="32"/>
-    <row r="473" ht="15.75" customHeight="1" s="32"/>
-    <row r="474" ht="15.75" customHeight="1" s="32"/>
-    <row r="475" ht="15.75" customHeight="1" s="32"/>
-    <row r="476" ht="15.75" customHeight="1" s="32"/>
-    <row r="477" ht="15.75" customHeight="1" s="32"/>
-    <row r="478" ht="15.75" customHeight="1" s="32"/>
-    <row r="479" ht="15.75" customHeight="1" s="32"/>
-    <row r="480" ht="15.75" customHeight="1" s="32"/>
-    <row r="481" ht="15.75" customHeight="1" s="32"/>
-    <row r="482" ht="15.75" customHeight="1" s="32"/>
-    <row r="483" ht="15.75" customHeight="1" s="32"/>
-    <row r="484" ht="15.75" customHeight="1" s="32"/>
-    <row r="485" ht="15.75" customHeight="1" s="32"/>
-    <row r="486" ht="15.75" customHeight="1" s="32"/>
-    <row r="487" ht="15.75" customHeight="1" s="32"/>
-    <row r="488" ht="15.75" customHeight="1" s="32"/>
-    <row r="489" ht="15.75" customHeight="1" s="32"/>
-    <row r="490" ht="15.75" customHeight="1" s="32"/>
-    <row r="491" ht="15.75" customHeight="1" s="32"/>
-    <row r="492" ht="15.75" customHeight="1" s="32"/>
-    <row r="493" ht="15.75" customHeight="1" s="32"/>
-    <row r="494" ht="15.75" customHeight="1" s="32"/>
-    <row r="495" ht="15.75" customHeight="1" s="32"/>
-    <row r="496" ht="15.75" customHeight="1" s="32"/>
-    <row r="497" ht="15.75" customHeight="1" s="32"/>
-    <row r="498" ht="15.75" customHeight="1" s="32"/>
-    <row r="499" ht="15.75" customHeight="1" s="32"/>
-    <row r="500" ht="15.75" customHeight="1" s="32"/>
-    <row r="501" ht="15.75" customHeight="1" s="32"/>
-    <row r="502" ht="15.75" customHeight="1" s="32"/>
-    <row r="503" ht="15.75" customHeight="1" s="32"/>
-    <row r="504" ht="15.75" customHeight="1" s="32"/>
-    <row r="505" ht="15.75" customHeight="1" s="32"/>
-    <row r="506" ht="15.75" customHeight="1" s="32"/>
-    <row r="507" ht="15.75" customHeight="1" s="32"/>
-    <row r="508" ht="15.75" customHeight="1" s="32"/>
-    <row r="509" ht="15.75" customHeight="1" s="32"/>
-    <row r="510" ht="15.75" customHeight="1" s="32"/>
-    <row r="511" ht="15.75" customHeight="1" s="32"/>
-    <row r="512" ht="15.75" customHeight="1" s="32"/>
-    <row r="513" ht="15.75" customHeight="1" s="32"/>
-    <row r="514" ht="15.75" customHeight="1" s="32"/>
-    <row r="515" ht="15.75" customHeight="1" s="32"/>
-    <row r="516" ht="15.75" customHeight="1" s="32"/>
-    <row r="517" ht="15.75" customHeight="1" s="32"/>
-    <row r="518" ht="15.75" customHeight="1" s="32"/>
-    <row r="519" ht="15.75" customHeight="1" s="32"/>
-    <row r="520" ht="15.75" customHeight="1" s="32"/>
-    <row r="521" ht="15.75" customHeight="1" s="32"/>
-    <row r="522" ht="15.75" customHeight="1" s="32"/>
-    <row r="523" ht="15.75" customHeight="1" s="32"/>
-    <row r="524" ht="15.75" customHeight="1" s="32"/>
-    <row r="525" ht="15.75" customHeight="1" s="32"/>
-    <row r="526" ht="15.75" customHeight="1" s="32"/>
-    <row r="527" ht="15.75" customHeight="1" s="32"/>
-    <row r="528" ht="15.75" customHeight="1" s="32"/>
-    <row r="529" ht="15.75" customHeight="1" s="32"/>
-    <row r="530" ht="15.75" customHeight="1" s="32"/>
-    <row r="531" ht="15.75" customHeight="1" s="32"/>
-    <row r="532" ht="15.75" customHeight="1" s="32"/>
-    <row r="533" ht="15.75" customHeight="1" s="32"/>
-    <row r="534" ht="15.75" customHeight="1" s="32"/>
-    <row r="535" ht="15.75" customHeight="1" s="32"/>
-    <row r="536" ht="15.75" customHeight="1" s="32"/>
-    <row r="537" ht="15.75" customHeight="1" s="32"/>
-    <row r="538" ht="15.75" customHeight="1" s="32"/>
-    <row r="539" ht="15.75" customHeight="1" s="32"/>
-    <row r="540" ht="15.75" customHeight="1" s="32"/>
-    <row r="541" ht="15.75" customHeight="1" s="32"/>
-    <row r="542" ht="15.75" customHeight="1" s="32"/>
-    <row r="543" ht="15.75" customHeight="1" s="32"/>
-    <row r="544" ht="15.75" customHeight="1" s="32"/>
-    <row r="545" ht="15.75" customHeight="1" s="32"/>
-    <row r="546" ht="15.75" customHeight="1" s="32"/>
-    <row r="547" ht="15.75" customHeight="1" s="32"/>
-    <row r="548" ht="15.75" customHeight="1" s="32"/>
-    <row r="549" ht="15.75" customHeight="1" s="32"/>
-    <row r="550" ht="15.75" customHeight="1" s="32"/>
-    <row r="551" ht="15.75" customHeight="1" s="32"/>
-    <row r="552" ht="15.75" customHeight="1" s="32"/>
-    <row r="553" ht="15.75" customHeight="1" s="32"/>
-    <row r="554" ht="15.75" customHeight="1" s="32"/>
-    <row r="555" ht="15.75" customHeight="1" s="32"/>
-    <row r="556" ht="15.75" customHeight="1" s="32"/>
-    <row r="557" ht="15.75" customHeight="1" s="32"/>
-    <row r="558" ht="15.75" customHeight="1" s="32"/>
-    <row r="559" ht="15.75" customHeight="1" s="32"/>
-    <row r="560" ht="15.75" customHeight="1" s="32"/>
-    <row r="561" ht="15.75" customHeight="1" s="32"/>
-    <row r="562" ht="15.75" customHeight="1" s="32"/>
-    <row r="563" ht="15.75" customHeight="1" s="32"/>
-    <row r="564" ht="15.75" customHeight="1" s="32"/>
-    <row r="565" ht="15.75" customHeight="1" s="32"/>
-    <row r="566" ht="15.75" customHeight="1" s="32"/>
-    <row r="567" ht="15.75" customHeight="1" s="32"/>
-    <row r="568" ht="15.75" customHeight="1" s="32"/>
-    <row r="569" ht="15.75" customHeight="1" s="32"/>
-    <row r="570" ht="15.75" customHeight="1" s="32"/>
-    <row r="571" ht="15.75" customHeight="1" s="32"/>
-    <row r="572" ht="15.75" customHeight="1" s="32"/>
-    <row r="573" ht="15.75" customHeight="1" s="32"/>
-    <row r="574" ht="15.75" customHeight="1" s="32"/>
-    <row r="575" ht="15.75" customHeight="1" s="32"/>
-    <row r="576" ht="15.75" customHeight="1" s="32"/>
-    <row r="577" ht="15.75" customHeight="1" s="32"/>
-    <row r="578" ht="15.75" customHeight="1" s="32"/>
-    <row r="579" ht="15.75" customHeight="1" s="32"/>
-    <row r="580" ht="15.75" customHeight="1" s="32"/>
-    <row r="581" ht="15.75" customHeight="1" s="32"/>
-    <row r="582" ht="15.75" customHeight="1" s="32"/>
-    <row r="583" ht="15.75" customHeight="1" s="32"/>
-    <row r="584" ht="15.75" customHeight="1" s="32"/>
-    <row r="585" ht="15.75" customHeight="1" s="32"/>
-    <row r="586" ht="15.75" customHeight="1" s="32"/>
-    <row r="587" ht="15.75" customHeight="1" s="32"/>
-    <row r="588" ht="15.75" customHeight="1" s="32"/>
-    <row r="589" ht="15.75" customHeight="1" s="32"/>
-    <row r="590" ht="15.75" customHeight="1" s="32"/>
-    <row r="591" ht="15.75" customHeight="1" s="32"/>
-    <row r="592" ht="15.75" customHeight="1" s="32"/>
-    <row r="593" ht="15.75" customHeight="1" s="32"/>
-    <row r="594" ht="15.75" customHeight="1" s="32"/>
-    <row r="595" ht="15.75" customHeight="1" s="32"/>
-    <row r="596" ht="15.75" customHeight="1" s="32"/>
-    <row r="597" ht="15.75" customHeight="1" s="32"/>
-    <row r="598" ht="15.75" customHeight="1" s="32"/>
-    <row r="599" ht="15.75" customHeight="1" s="32"/>
-    <row r="600" ht="15.75" customHeight="1" s="32"/>
-    <row r="601" ht="15.75" customHeight="1" s="32"/>
-    <row r="602" ht="15.75" customHeight="1" s="32"/>
-    <row r="603" ht="15.75" customHeight="1" s="32"/>
-    <row r="604" ht="15.75" customHeight="1" s="32"/>
-    <row r="605" ht="15.75" customHeight="1" s="32"/>
-    <row r="606" ht="15.75" customHeight="1" s="32"/>
-    <row r="607" ht="15.75" customHeight="1" s="32"/>
-    <row r="608" ht="15.75" customHeight="1" s="32"/>
-    <row r="609" ht="15.75" customHeight="1" s="32"/>
-    <row r="610" ht="15.75" customHeight="1" s="32"/>
-    <row r="611" ht="15.75" customHeight="1" s="32"/>
-    <row r="612" ht="15.75" customHeight="1" s="32"/>
-    <row r="613" ht="15.75" customHeight="1" s="32"/>
-    <row r="614" ht="15.75" customHeight="1" s="32"/>
-    <row r="615" ht="15.75" customHeight="1" s="32"/>
-    <row r="616" ht="15.75" customHeight="1" s="32"/>
-    <row r="617" ht="15.75" customHeight="1" s="32"/>
-    <row r="618" ht="15.75" customHeight="1" s="32"/>
-    <row r="619" ht="15.75" customHeight="1" s="32"/>
-    <row r="620" ht="15.75" customHeight="1" s="32"/>
-    <row r="621" ht="15.75" customHeight="1" s="32"/>
-    <row r="622" ht="15.75" customHeight="1" s="32"/>
-    <row r="623" ht="15.75" customHeight="1" s="32"/>
-    <row r="624" ht="15.75" customHeight="1" s="32"/>
-    <row r="625" ht="15.75" customHeight="1" s="32"/>
-    <row r="626" ht="15.75" customHeight="1" s="32"/>
-    <row r="627" ht="15.75" customHeight="1" s="32"/>
-    <row r="628" ht="15.75" customHeight="1" s="32"/>
-    <row r="629" ht="15.75" customHeight="1" s="32"/>
-    <row r="630" ht="15.75" customHeight="1" s="32"/>
-    <row r="631" ht="15.75" customHeight="1" s="32"/>
-    <row r="632" ht="15.75" customHeight="1" s="32"/>
-    <row r="633" ht="15.75" customHeight="1" s="32"/>
-    <row r="634" ht="15.75" customHeight="1" s="32"/>
-    <row r="635" ht="15.75" customHeight="1" s="32"/>
-    <row r="636" ht="15.75" customHeight="1" s="32"/>
-    <row r="637" ht="15.75" customHeight="1" s="32"/>
-    <row r="638" ht="15.75" customHeight="1" s="32"/>
-    <row r="639" ht="15.75" customHeight="1" s="32"/>
-    <row r="640" ht="15.75" customHeight="1" s="32"/>
-    <row r="641" ht="15.75" customHeight="1" s="32"/>
-    <row r="642" ht="15.75" customHeight="1" s="32"/>
-    <row r="643" ht="15.75" customHeight="1" s="32"/>
-    <row r="644" ht="15.75" customHeight="1" s="32"/>
-    <row r="645" ht="15.75" customHeight="1" s="32"/>
-    <row r="646" ht="15.75" customHeight="1" s="32"/>
-    <row r="647" ht="15.75" customHeight="1" s="32"/>
-    <row r="648" ht="15.75" customHeight="1" s="32"/>
-    <row r="649" ht="15.75" customHeight="1" s="32"/>
-    <row r="650" ht="15.75" customHeight="1" s="32"/>
-    <row r="651" ht="15.75" customHeight="1" s="32"/>
-    <row r="652" ht="15.75" customHeight="1" s="32"/>
-    <row r="653" ht="15.75" customHeight="1" s="32"/>
-    <row r="654" ht="15.75" customHeight="1" s="32"/>
-    <row r="655" ht="15.75" customHeight="1" s="32"/>
-    <row r="656" ht="15.75" customHeight="1" s="32"/>
-    <row r="657" ht="15.75" customHeight="1" s="32"/>
-    <row r="658" ht="15.75" customHeight="1" s="32"/>
-    <row r="659" ht="15.75" customHeight="1" s="32"/>
-    <row r="660" ht="15.75" customHeight="1" s="32"/>
-    <row r="661" ht="15.75" customHeight="1" s="32"/>
-    <row r="662" ht="15.75" customHeight="1" s="32"/>
-    <row r="663" ht="15.75" customHeight="1" s="32"/>
-    <row r="664" ht="15.75" customHeight="1" s="32"/>
-    <row r="665" ht="15.75" customHeight="1" s="32"/>
-    <row r="666" ht="15.75" customHeight="1" s="32"/>
-    <row r="667" ht="15.75" customHeight="1" s="32"/>
-    <row r="668" ht="15.75" customHeight="1" s="32"/>
-    <row r="669" ht="15.75" customHeight="1" s="32"/>
-    <row r="670" ht="15.75" customHeight="1" s="32"/>
-    <row r="671" ht="15.75" customHeight="1" s="32"/>
-    <row r="672" ht="15.75" customHeight="1" s="32"/>
-    <row r="673" ht="15.75" customHeight="1" s="32"/>
-    <row r="674" ht="15.75" customHeight="1" s="32"/>
-    <row r="675" ht="15.75" customHeight="1" s="32"/>
-    <row r="676" ht="15.75" customHeight="1" s="32"/>
-    <row r="677" ht="15.75" customHeight="1" s="32"/>
-    <row r="678" ht="15.75" customHeight="1" s="32"/>
-    <row r="679" ht="15.75" customHeight="1" s="32"/>
-    <row r="680" ht="15.75" customHeight="1" s="32"/>
-    <row r="681" ht="15.75" customHeight="1" s="32"/>
-    <row r="682" ht="15.75" customHeight="1" s="32"/>
-    <row r="683" ht="15.75" customHeight="1" s="32"/>
-    <row r="684" ht="15.75" customHeight="1" s="32"/>
-    <row r="685" ht="15.75" customHeight="1" s="32"/>
-    <row r="686" ht="15.75" customHeight="1" s="32"/>
-    <row r="687" ht="15.75" customHeight="1" s="32"/>
-    <row r="688" ht="15.75" customHeight="1" s="32"/>
-    <row r="689" ht="15.75" customHeight="1" s="32"/>
-    <row r="690" ht="15.75" customHeight="1" s="32"/>
-    <row r="691" ht="15.75" customHeight="1" s="32"/>
-    <row r="692" ht="15.75" customHeight="1" s="32"/>
-    <row r="693" ht="15.75" customHeight="1" s="32"/>
-    <row r="694" ht="15.75" customHeight="1" s="32"/>
-    <row r="695" ht="15.75" customHeight="1" s="32"/>
-    <row r="696" ht="15.75" customHeight="1" s="32"/>
-    <row r="697" ht="15.75" customHeight="1" s="32"/>
-    <row r="698" ht="15.75" customHeight="1" s="32"/>
-    <row r="699" ht="15.75" customHeight="1" s="32"/>
-    <row r="700" ht="15.75" customHeight="1" s="32"/>
-    <row r="701" ht="15.75" customHeight="1" s="32"/>
-    <row r="702" ht="15.75" customHeight="1" s="32"/>
-    <row r="703" ht="15.75" customHeight="1" s="32"/>
-    <row r="704" ht="15.75" customHeight="1" s="32"/>
-    <row r="705" ht="15.75" customHeight="1" s="32"/>
-    <row r="706" ht="15.75" customHeight="1" s="32"/>
-    <row r="707" ht="15.75" customHeight="1" s="32"/>
-    <row r="708" ht="15.75" customHeight="1" s="32"/>
-    <row r="709" ht="15.75" customHeight="1" s="32"/>
-    <row r="710" ht="15.75" customHeight="1" s="32"/>
-    <row r="711" ht="15.75" customHeight="1" s="32"/>
-    <row r="712" ht="15.75" customHeight="1" s="32"/>
-    <row r="713" ht="15.75" customHeight="1" s="32"/>
-    <row r="714" ht="15.75" customHeight="1" s="32"/>
-    <row r="715" ht="15.75" customHeight="1" s="32"/>
-    <row r="716" ht="15.75" customHeight="1" s="32"/>
-    <row r="717" ht="15.75" customHeight="1" s="32"/>
-    <row r="718" ht="15.75" customHeight="1" s="32"/>
-    <row r="719" ht="15.75" customHeight="1" s="32"/>
-    <row r="720" ht="15.75" customHeight="1" s="32"/>
-    <row r="721" ht="15.75" customHeight="1" s="32"/>
-    <row r="722" ht="15.75" customHeight="1" s="32"/>
-    <row r="723" ht="15.75" customHeight="1" s="32"/>
-    <row r="724" ht="15.75" customHeight="1" s="32"/>
-    <row r="725" ht="15.75" customHeight="1" s="32"/>
-    <row r="726" ht="15.75" customHeight="1" s="32"/>
-    <row r="727" ht="15.75" customHeight="1" s="32"/>
-    <row r="728" ht="15.75" customHeight="1" s="32"/>
-    <row r="729" ht="15.75" customHeight="1" s="32"/>
-    <row r="730" ht="15.75" customHeight="1" s="32"/>
-    <row r="731" ht="15.75" customHeight="1" s="32"/>
-    <row r="732" ht="15.75" customHeight="1" s="32"/>
-    <row r="733" ht="15.75" customHeight="1" s="32"/>
-    <row r="734" ht="15.75" customHeight="1" s="32"/>
-    <row r="735" ht="15.75" customHeight="1" s="32"/>
-    <row r="736" ht="15.75" customHeight="1" s="32"/>
-    <row r="737" ht="15.75" customHeight="1" s="32"/>
-    <row r="738" ht="15.75" customHeight="1" s="32"/>
-    <row r="739" ht="15.75" customHeight="1" s="32"/>
-    <row r="740" ht="15.75" customHeight="1" s="32"/>
-    <row r="741" ht="15.75" customHeight="1" s="32"/>
-    <row r="742" ht="15.75" customHeight="1" s="32"/>
-    <row r="743" ht="15.75" customHeight="1" s="32"/>
-    <row r="744" ht="15.75" customHeight="1" s="32"/>
-    <row r="745" ht="15.75" customHeight="1" s="32"/>
-    <row r="746" ht="15.75" customHeight="1" s="32"/>
-    <row r="747" ht="15.75" customHeight="1" s="32"/>
-    <row r="748" ht="15.75" customHeight="1" s="32"/>
-    <row r="749" ht="15.75" customHeight="1" s="32"/>
-    <row r="750" ht="15.75" customHeight="1" s="32"/>
-    <row r="751" ht="15.75" customHeight="1" s="32"/>
-    <row r="752" ht="15.75" customHeight="1" s="32"/>
-    <row r="753" ht="15.75" customHeight="1" s="32"/>
-    <row r="754" ht="15.75" customHeight="1" s="32"/>
-    <row r="755" ht="15.75" customHeight="1" s="32"/>
-    <row r="756" ht="15.75" customHeight="1" s="32"/>
-    <row r="757" ht="15.75" customHeight="1" s="32"/>
-    <row r="758" ht="15.75" customHeight="1" s="32"/>
-    <row r="759" ht="15.75" customHeight="1" s="32"/>
-    <row r="760" ht="15.75" customHeight="1" s="32"/>
-    <row r="761" ht="15.75" customHeight="1" s="32"/>
-    <row r="762" ht="15.75" customHeight="1" s="32"/>
-    <row r="763" ht="15.75" customHeight="1" s="32"/>
-    <row r="764" ht="15.75" customHeight="1" s="32"/>
-    <row r="765" ht="15.75" customHeight="1" s="32"/>
-    <row r="766" ht="15.75" customHeight="1" s="32"/>
-    <row r="767" ht="15.75" customHeight="1" s="32"/>
-    <row r="768" ht="15.75" customHeight="1" s="32"/>
-    <row r="769" ht="15.75" customHeight="1" s="32"/>
-    <row r="770" ht="15.75" customHeight="1" s="32"/>
-    <row r="771" ht="15.75" customHeight="1" s="32"/>
-    <row r="772" ht="15.75" customHeight="1" s="32"/>
-    <row r="773" ht="15.75" customHeight="1" s="32"/>
-    <row r="774" ht="15.75" customHeight="1" s="32"/>
-    <row r="775" ht="15.75" customHeight="1" s="32"/>
-    <row r="776" ht="15.75" customHeight="1" s="32"/>
-    <row r="777" ht="15.75" customHeight="1" s="32"/>
-    <row r="778" ht="15.75" customHeight="1" s="32"/>
-    <row r="779" ht="15.75" customHeight="1" s="32"/>
-    <row r="780" ht="15.75" customHeight="1" s="32"/>
-    <row r="781" ht="15.75" customHeight="1" s="32"/>
-    <row r="782" ht="15.75" customHeight="1" s="32"/>
-    <row r="783" ht="15.75" customHeight="1" s="32"/>
-    <row r="784" ht="15.75" customHeight="1" s="32"/>
-    <row r="785" ht="15.75" customHeight="1" s="32"/>
-    <row r="786" ht="15.75" customHeight="1" s="32"/>
-    <row r="787" ht="15.75" customHeight="1" s="32"/>
-    <row r="788" ht="15.75" customHeight="1" s="32"/>
-    <row r="789" ht="15.75" customHeight="1" s="32"/>
-    <row r="790" ht="15.75" customHeight="1" s="32"/>
-    <row r="791" ht="15.75" customHeight="1" s="32"/>
-    <row r="792" ht="15.75" customHeight="1" s="32"/>
-    <row r="793" ht="15.75" customHeight="1" s="32"/>
-    <row r="794" ht="15.75" customHeight="1" s="32"/>
-    <row r="795" ht="15.75" customHeight="1" s="32"/>
-    <row r="796" ht="15.75" customHeight="1" s="32"/>
-    <row r="797" ht="15.75" customHeight="1" s="32"/>
-    <row r="798" ht="15.75" customHeight="1" s="32"/>
-    <row r="799" ht="15.75" customHeight="1" s="32"/>
-    <row r="800" ht="15.75" customHeight="1" s="32"/>
-    <row r="801" ht="15.75" customHeight="1" s="32"/>
-    <row r="802" ht="15.75" customHeight="1" s="32"/>
-    <row r="803" ht="15.75" customHeight="1" s="32"/>
-    <row r="804" ht="15.75" customHeight="1" s="32"/>
-    <row r="805" ht="15.75" customHeight="1" s="32"/>
-    <row r="806" ht="15.75" customHeight="1" s="32"/>
-    <row r="807" ht="15.75" customHeight="1" s="32"/>
-    <row r="808" ht="15.75" customHeight="1" s="32"/>
-    <row r="809" ht="15.75" customHeight="1" s="32"/>
-    <row r="810" ht="15.75" customHeight="1" s="32"/>
-    <row r="811" ht="15.75" customHeight="1" s="32"/>
-    <row r="812" ht="15.75" customHeight="1" s="32"/>
-    <row r="813" ht="15.75" customHeight="1" s="32"/>
-    <row r="814" ht="15.75" customHeight="1" s="32"/>
-    <row r="815" ht="15.75" customHeight="1" s="32"/>
-    <row r="816" ht="15.75" customHeight="1" s="32"/>
-    <row r="817" ht="15.75" customHeight="1" s="32"/>
-    <row r="818" ht="15.75" customHeight="1" s="32"/>
-    <row r="819" ht="15.75" customHeight="1" s="32"/>
-    <row r="820" ht="15.75" customHeight="1" s="32"/>
-    <row r="821" ht="15.75" customHeight="1" s="32"/>
-    <row r="822" ht="15.75" customHeight="1" s="32"/>
-    <row r="823" ht="15.75" customHeight="1" s="32"/>
-    <row r="824" ht="15.75" customHeight="1" s="32"/>
-    <row r="825" ht="15.75" customHeight="1" s="32"/>
-    <row r="826" ht="15.75" customHeight="1" s="32"/>
-    <row r="827" ht="15.75" customHeight="1" s="32"/>
-    <row r="828" ht="15.75" customHeight="1" s="32"/>
-    <row r="829" ht="15.75" customHeight="1" s="32"/>
-    <row r="830" ht="15.75" customHeight="1" s="32"/>
-    <row r="831" ht="15.75" customHeight="1" s="32"/>
-    <row r="832" ht="15.75" customHeight="1" s="32"/>
-    <row r="833" ht="15.75" customHeight="1" s="32"/>
-    <row r="834" ht="15.75" customHeight="1" s="32"/>
-    <row r="835" ht="15.75" customHeight="1" s="32"/>
-    <row r="836" ht="15.75" customHeight="1" s="32"/>
-    <row r="837" ht="15.75" customHeight="1" s="32"/>
-    <row r="838" ht="15.75" customHeight="1" s="32"/>
-    <row r="839" ht="15.75" customHeight="1" s="32"/>
-    <row r="840" ht="15.75" customHeight="1" s="32"/>
-    <row r="841" ht="15.75" customHeight="1" s="32"/>
-    <row r="842" ht="15.75" customHeight="1" s="32"/>
-    <row r="843" ht="15.75" customHeight="1" s="32"/>
-    <row r="844" ht="15.75" customHeight="1" s="32"/>
-    <row r="845" ht="15.75" customHeight="1" s="32"/>
-    <row r="846" ht="15.75" customHeight="1" s="32"/>
-    <row r="847" ht="15.75" customHeight="1" s="32"/>
-    <row r="848" ht="15.75" customHeight="1" s="32"/>
-    <row r="849" ht="15.75" customHeight="1" s="32"/>
-    <row r="850" ht="15.75" customHeight="1" s="32"/>
-    <row r="851" ht="15.75" customHeight="1" s="32"/>
-    <row r="852" ht="15.75" customHeight="1" s="32"/>
-    <row r="853" ht="15.75" customHeight="1" s="32"/>
-    <row r="854" ht="15.75" customHeight="1" s="32"/>
-    <row r="855" ht="15.75" customHeight="1" s="32"/>
-    <row r="856" ht="15.75" customHeight="1" s="32"/>
-    <row r="857" ht="15.75" customHeight="1" s="32"/>
-    <row r="858" ht="15.75" customHeight="1" s="32"/>
-    <row r="859" ht="15.75" customHeight="1" s="32"/>
-    <row r="860" ht="15.75" customHeight="1" s="32"/>
-    <row r="861" ht="15.75" customHeight="1" s="32"/>
-    <row r="862" ht="15.75" customHeight="1" s="32"/>
-    <row r="863" ht="15.75" customHeight="1" s="32"/>
-    <row r="864" ht="15.75" customHeight="1" s="32"/>
-    <row r="865" ht="15.75" customHeight="1" s="32"/>
-    <row r="866" ht="15.75" customHeight="1" s="32"/>
-    <row r="867" ht="15.75" customHeight="1" s="32"/>
-    <row r="868" ht="15.75" customHeight="1" s="32"/>
-    <row r="869" ht="15.75" customHeight="1" s="32"/>
-    <row r="870" ht="15.75" customHeight="1" s="32"/>
-    <row r="871" ht="15.75" customHeight="1" s="32"/>
-    <row r="872" ht="15.75" customHeight="1" s="32"/>
-    <row r="873" ht="15.75" customHeight="1" s="32"/>
-    <row r="874" ht="15.75" customHeight="1" s="32"/>
-    <row r="875" ht="15.75" customHeight="1" s="32"/>
-    <row r="876" ht="15.75" customHeight="1" s="32"/>
-    <row r="877" ht="15.75" customHeight="1" s="32"/>
-    <row r="878" ht="15.75" customHeight="1" s="32"/>
-    <row r="879" ht="15.75" customHeight="1" s="32"/>
-    <row r="880" ht="15.75" customHeight="1" s="32"/>
-    <row r="881" ht="15.75" customHeight="1" s="32"/>
-    <row r="882" ht="15.75" customHeight="1" s="32"/>
-    <row r="883" ht="15.75" customHeight="1" s="32"/>
-    <row r="884" ht="15.75" customHeight="1" s="32"/>
-    <row r="885" ht="15.75" customHeight="1" s="32"/>
-    <row r="886" ht="15.75" customHeight="1" s="32"/>
-    <row r="887" ht="15.75" customHeight="1" s="32"/>
-    <row r="888" ht="15.75" customHeight="1" s="32"/>
-    <row r="889" ht="15.75" customHeight="1" s="32"/>
-    <row r="890" ht="15.75" customHeight="1" s="32"/>
-    <row r="891" ht="15.75" customHeight="1" s="32"/>
-    <row r="892" ht="15.75" customHeight="1" s="32"/>
-    <row r="893" ht="15.75" customHeight="1" s="32"/>
-    <row r="894" ht="15.75" customHeight="1" s="32"/>
-    <row r="895" ht="15.75" customHeight="1" s="32"/>
-    <row r="896" ht="15.75" customHeight="1" s="32"/>
-    <row r="897" ht="15.75" customHeight="1" s="32"/>
-    <row r="898" ht="15.75" customHeight="1" s="32"/>
-    <row r="899" ht="15.75" customHeight="1" s="32"/>
-    <row r="900" ht="15.75" customHeight="1" s="32"/>
-    <row r="901" ht="15.75" customHeight="1" s="32"/>
-    <row r="902" ht="15.75" customHeight="1" s="32"/>
-    <row r="903" ht="15.75" customHeight="1" s="32"/>
-    <row r="904" ht="15.75" customHeight="1" s="32"/>
-    <row r="905" ht="15.75" customHeight="1" s="32"/>
-    <row r="906" ht="15.75" customHeight="1" s="32"/>
-    <row r="907" ht="15.75" customHeight="1" s="32"/>
-    <row r="908" ht="15.75" customHeight="1" s="32"/>
-    <row r="909" ht="15.75" customHeight="1" s="32"/>
-    <row r="910" ht="15.75" customHeight="1" s="32"/>
-    <row r="911" ht="15.75" customHeight="1" s="32"/>
-    <row r="912" ht="15.75" customHeight="1" s="32"/>
-    <row r="913" ht="15.75" customHeight="1" s="32"/>
-    <row r="914" ht="15.75" customHeight="1" s="32"/>
-    <row r="915" ht="15.75" customHeight="1" s="32"/>
-    <row r="916" ht="15.75" customHeight="1" s="32"/>
-    <row r="917" ht="15.75" customHeight="1" s="32"/>
-    <row r="918" ht="15.75" customHeight="1" s="32"/>
-    <row r="919" ht="15.75" customHeight="1" s="32"/>
-    <row r="920" ht="15.75" customHeight="1" s="32"/>
-    <row r="921" ht="15.75" customHeight="1" s="32"/>
-    <row r="922" ht="15.75" customHeight="1" s="32"/>
-    <row r="923" ht="15.75" customHeight="1" s="32"/>
-    <row r="924" ht="15.75" customHeight="1" s="32"/>
-    <row r="925" ht="15.75" customHeight="1" s="32"/>
-    <row r="926" ht="15.75" customHeight="1" s="32"/>
-    <row r="927" ht="15.75" customHeight="1" s="32"/>
-    <row r="928" ht="15.75" customHeight="1" s="32"/>
-    <row r="929" ht="15.75" customHeight="1" s="32"/>
-    <row r="930" ht="15.75" customHeight="1" s="32"/>
-    <row r="931" ht="15.75" customHeight="1" s="32"/>
-    <row r="932" ht="15.75" customHeight="1" s="32"/>
-    <row r="933" ht="15.75" customHeight="1" s="32"/>
-    <row r="934" ht="15.75" customHeight="1" s="32"/>
-    <row r="935" ht="15.75" customHeight="1" s="32"/>
-    <row r="936" ht="15.75" customHeight="1" s="32"/>
-    <row r="937" ht="15.75" customHeight="1" s="32"/>
-    <row r="938" ht="15.75" customHeight="1" s="32"/>
-    <row r="939" ht="15.75" customHeight="1" s="32"/>
-    <row r="940" ht="15.75" customHeight="1" s="32"/>
-    <row r="941" ht="15.75" customHeight="1" s="32"/>
-    <row r="942" ht="15.75" customHeight="1" s="32"/>
-    <row r="943" ht="15.75" customHeight="1" s="32"/>
-    <row r="944" ht="15.75" customHeight="1" s="32"/>
-    <row r="945" ht="15.75" customHeight="1" s="32"/>
-    <row r="946" ht="15.75" customHeight="1" s="32"/>
-    <row r="947" ht="15.75" customHeight="1" s="32"/>
-    <row r="948" ht="15.75" customHeight="1" s="32"/>
-    <row r="949" ht="15.75" customHeight="1" s="32"/>
-    <row r="950" ht="15.75" customHeight="1" s="32"/>
-    <row r="951" ht="15.75" customHeight="1" s="32"/>
-    <row r="952" ht="15.75" customHeight="1" s="32"/>
-    <row r="953" ht="15.75" customHeight="1" s="32"/>
-    <row r="954" ht="15.75" customHeight="1" s="32"/>
-    <row r="955" ht="15.75" customHeight="1" s="32"/>
-    <row r="956" ht="15.75" customHeight="1" s="32"/>
-    <row r="957" ht="15.75" customHeight="1" s="32"/>
-    <row r="958" ht="15.75" customHeight="1" s="32"/>
-    <row r="959" ht="15.75" customHeight="1" s="32"/>
-    <row r="960" ht="15.75" customHeight="1" s="32"/>
-    <row r="961" ht="15.75" customHeight="1" s="32"/>
-    <row r="962" ht="15.75" customHeight="1" s="32"/>
-    <row r="963" ht="15.75" customHeight="1" s="32"/>
-    <row r="964" ht="15.75" customHeight="1" s="32"/>
-    <row r="965" ht="15.75" customHeight="1" s="32"/>
-    <row r="966" ht="15.75" customHeight="1" s="32"/>
-    <row r="967" ht="15.75" customHeight="1" s="32"/>
-    <row r="968" ht="15.75" customHeight="1" s="32"/>
-    <row r="969" ht="15.75" customHeight="1" s="32"/>
-    <row r="970" ht="15.75" customHeight="1" s="32"/>
-    <row r="971" ht="15.75" customHeight="1" s="32"/>
-    <row r="972" ht="15.75" customHeight="1" s="32"/>
-    <row r="973" ht="15.75" customHeight="1" s="32"/>
-    <row r="974" ht="15.75" customHeight="1" s="32"/>
-    <row r="975" ht="15.75" customHeight="1" s="32"/>
-    <row r="976" ht="15.75" customHeight="1" s="32"/>
-    <row r="977" ht="15.75" customHeight="1" s="32"/>
-    <row r="978" ht="15.75" customHeight="1" s="32"/>
-    <row r="979" ht="15.75" customHeight="1" s="32"/>
-    <row r="980" ht="15.75" customHeight="1" s="32"/>
-    <row r="981" ht="15.75" customHeight="1" s="32"/>
-    <row r="982" ht="15.75" customHeight="1" s="32"/>
-    <row r="983" ht="15.75" customHeight="1" s="32"/>
-    <row r="984" ht="15.75" customHeight="1" s="32"/>
-    <row r="985" ht="15.75" customHeight="1" s="32"/>
-    <row r="986" ht="15.75" customHeight="1" s="32"/>
-    <row r="987" ht="15.75" customHeight="1" s="32"/>
-    <row r="988" ht="15.75" customHeight="1" s="32"/>
-    <row r="989" ht="15.75" customHeight="1" s="32"/>
-    <row r="990" ht="15.75" customHeight="1" s="32"/>
-    <row r="991" ht="15.75" customHeight="1" s="32"/>
-    <row r="992" ht="15.75" customHeight="1" s="32"/>
-    <row r="993" ht="15.75" customHeight="1" s="32"/>
-    <row r="994" ht="15.75" customHeight="1" s="32"/>
-    <row r="995" ht="15.75" customHeight="1" s="32"/>
-    <row r="996" ht="15.75" customHeight="1" s="32"/>
-    <row r="997" ht="15.75" customHeight="1" s="32"/>
-    <row r="998" ht="15.75" customHeight="1" s="32"/>
-    <row r="999" ht="15.75" customHeight="1" s="32"/>
-    <row r="1000" ht="15.75" customHeight="1" s="32"/>
+    <row r="1">
+      <c r="A1" s="37" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="37" t="inlineStr">
+        <is>
+          <t>Question / ambiguity for the PO or developer</t>
+        </is>
+      </c>
+      <c r="C1" s="37" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="44.5" customHeight="1" s="32">
+      <c r="A2" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="38" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-09-30: The review page shows 'Under review' (SPM-30 behaviour), not 'Submitted' as in the EventReview mockup. The mockup needs updating.</t>
+        </is>
+      </c>
+      <c r="C2" s="38" t="n"/>
+    </row>
+    <row r="3" ht="31" customHeight="1" s="32">
+      <c r="A3" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="38" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-09-30: Approving moves the event to 'Approved'. SPM-54 moves it on to 'Planning'.</t>
+        </is>
+      </c>
+      <c r="C3" s="38" t="n"/>
+    </row>
+    <row r="4" ht="71.5" customHeight="1" s="32">
+      <c r="A4" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="38" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-09-30: Incomplete information is flagged only ('Not provided' markers and a summary alert) and never blocks Approve. Per discussion #80, approval means there is sufficient information for planning, and that is the coordinator's judgment; per #72, mandatory fields are not defined.</t>
+        </is>
+      </c>
+      <c r="C4" s="38" t="n"/>
+    </row>
+    <row r="5" ht="58" customHeight="1" s="32">
+      <c r="A5" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="38" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-09-30: Clarifications are out of scope for SPM-28 - neither raising them ('Ask the organiser for clarification' in the mockup) nor showing existing ones. AC3 is met by flagging fields that were not provided.</t>
+        </is>
+      </c>
+      <c r="C5" s="38" t="n"/>
+    </row>
+    <row r="6" ht="31" customHeight="1" s="32">
+      <c r="A6" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="38" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-09-30: No organiser notification on approve/reject in SPM-28.</t>
+        </is>
+      </c>
+      <c r="C6" s="38" t="n"/>
+    </row>
+    <row r="7" ht="44.5" customHeight="1" s="32">
+      <c r="A7" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="38" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-09-30: The organiser sees the rejection reason in a red banner at the top of the event Overview ('This request was rejected' + reason).</t>
+        </is>
+      </c>
+      <c r="C7" s="38" t="n"/>
+    </row>
+    <row r="8" ht="31" customHeight="1" s="32">
+      <c r="A8" s="38" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="38" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-09-30: Approve requires a confirmation dialog (tested in TC08 and TC09).</t>
+        </is>
+      </c>
+      <c r="C8" s="38" t="n"/>
+    </row>
+    <row r="9" ht="44.5" customHeight="1" s="32">
+      <c r="A9" s="38" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="38" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-09-30: The server will only allow approve/reject from 'Under review'. Not reachable from the UI, so no manual test case; cover it with a unit test.</t>
+        </is>
+      </c>
+      <c r="C9" s="38" t="n"/>
+    </row>
+    <row r="10" ht="85" customHeight="1" s="32">
+      <c r="A10" s="38" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="38" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-09-30: Test data. Every case uses the 'SPM28 …' events from `npm run fixtures:spm28` (scripts/seed-spm28.ts), which deletes and recreates only those events - never a full `npx prisma db seed`. TC08 and TC10 change data; their preconditions say to run it before and after. The same events are in prisma/seed.ts, so a full reseed also includes them.</t>
+        </is>
+      </c>
+      <c r="C10" s="38" t="n"/>
+    </row>
+    <row r="11" ht="58" customHeight="1" s="32">
+      <c r="A11" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-09-30: Opening the review page of a request that is no longer Under review redirects to the event page (TC15), instead of showing a 'Nothing to review' message. A coordinator who is not assigned still sees 'You can't review this request' (TC03).</t>
+        </is>
+      </c>
+      <c r="C11" s="38" t="n"/>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -12273,13 +12450,13 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-28-TC02</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="111.75" customHeight="1" s="32">
+      <c r="B2" s="36" t="inlineStr">
+        <is>
+          <t>SPM-28-TC01</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="84.75" customHeight="1" s="32">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -12288,8 +12465,7 @@
       <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm28` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM28 …' events, EVT-000124 to EVT-000130, never anyone else's data).
- Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), Event Coordinator.
- Daniel Tan also coordinates 'SPM28 Straits Research Symposium' (Planning) and 'SPM28 Meridian Wealth Forum' (Approved).</t>
+ Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), Event Coordinator.</t>
         </is>
       </c>
     </row>
@@ -12305,7 +12481,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30.75" customHeight="1" s="32">
+    <row r="5" ht="71.25" customHeight="1" s="32">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -12313,11 +12489,11 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Must not appear: SPM28 Straits Research Symposium (EVT-000128, Planning), SPM28 Meridian Wealth Forum (EVT-000129, Approved)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="57.75" customHeight="1" s="32">
+          <t>Must appear (Under review, coordinator Daniel Tan): SPM28 Nusantara Product Launch (EVT-000124), SPM28 Harbourline Client Seminar (EVT-000125) | Must not appear: SPM28 Kirana Regional Offsite (EVT-000126, coordinator Priya Raj), SPM28 Straits Journal Club (EVT-000127, coordinator Joel Fernandez)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="98.25" customHeight="1" s="32">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -12325,7 +12501,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Step 1: Neither 'SPM28 Straits Research Symposium' nor 'SPM28 Meridian Wealth Forum' is listed, even though Daniel Tan is their coordinator. Every listed event shows the 'Under review' badge.</t>
+          <t>Step 1: The Review Queue page lists 'SPM28 Nusantara Product Launch' (client 'Nusantara Tech Labs', 17 Mar 2027, 'Under review' badge) and 'SPM28 Harbourline Client Seminar'. Other Under review events assigned to Daniel Tan may also appear; only the SPM28 events are checked here. 'SPM28 Kirana Regional Offsite' and 'SPM28 Straits Journal Club' are not listed.</t>
         </is>
       </c>
     </row>
@@ -12335,7 +12511,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -12367,9 +12543,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: Neither 'SPM28 Straits Research Symposium' nor 'SPM28 Meridian Wealth Forum' is listed, even though Daniel Tan is their coordinator. Every listed event shows the 'Under review' badge.</t>
+      <c r="B11" s="36" t="inlineStr">
+        <is>
+          <t>Step 1: The Review Queue page lists 'SPM28 Nusantara Product Launch' (client 'Nusantara Tech Labs', 17 Mar 2027, 'Under review' badge) and 'SPM28 Harbourline Client Seminar'. Other Under review events assigned to Daniel Tan may also appear; only the SPM28 events are checked here. 'SPM28 Kirana Regional Offsite' and 'SPM28 Straits Journal Club' are not listed.</t>
         </is>
       </c>
     </row>
@@ -12379,7 +12555,7 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12391,7 +12567,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -12415,7 +12591,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="21" t="n">
+      <c r="B15" s="31" t="n">
         <v>46295</v>
       </c>
     </row>
@@ -12434,9 +12610,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: Neither 'SPM28 Straits Research Symposium' nor 'SPM28 Meridian Wealth Forum' is listed, even though Daniel Tan is their coordinator. Every listed event shows the 'Under review' badge.</t>
+      <c r="B18" s="36" t="inlineStr">
+        <is>
+          <t>Step 1: The Review Queue page lists 'SPM28 Nusantara Product Launch' (client 'Nusantara Tech Labs', 17 Mar 2027, 'Under review' badge) and 'SPM28 Harbourline Client Seminar'. Other Under review events assigned to Daniel Tan may also appear; only the SPM28 events are checked here. 'SPM28 Kirana Regional Offsite' and 'SPM28 Straits Journal Club' are not listed.</t>
         </is>
       </c>
     </row>
@@ -12446,7 +12622,7 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12458,7 +12634,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -12482,7 +12658,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B22" s="31" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -13498,13 +13674,13 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-28-TC03</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="98.25" customHeight="1" s="32">
+      <c r="B2" s="36" t="inlineStr">
+        <is>
+          <t>SPM-28-TC02</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="111.75" customHeight="1" s="32">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -13513,11 +13689,12 @@
       <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm28` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM28 …' events, EVT-000124 to EVT-000130, never anyone else's data).
- Logged in as Priya Raj (priya.raj@connectsphere.com / password123), Event Coordinator not assigned to 'SPM28 Nusantara Product Launch' (its coordinator is Daniel Tan).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="84.75" customHeight="1" s="32">
+ Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), Event Coordinator.
+ Daniel Tan also coordinates 'SPM28 Straits Research Symposium' (Planning) and 'SPM28 Meridian Wealth Forum' (Approved).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17.25" customHeight="1" s="32">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -13525,9 +13702,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>1. Click 'Review Queue' in the sidebar
- 2. Click 'All Events' in the sidebar and open 'SPM28 Nusantara Product Launch'
- 3. Type /events/EVT-000124/review after the site address in the browser address bar (e.g. http://localhost:3000/events/EVT-000124/review) and press Enter</t>
+          <t>1. Click 'Review Queue' in the sidebar</t>
         </is>
       </c>
     </row>
@@ -13539,11 +13714,11 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Event: SPM28 Nusantara Product Launch (EVT-000124, coordinator Daniel Tan) | User: Priya Raj</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="111.75" customHeight="1" s="32">
+          <t>Must not appear: SPM28 Straits Research Symposium (EVT-000128, Planning), SPM28 Meridian Wealth Forum (EVT-000129, Approved)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="57.75" customHeight="1" s="32">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -13551,9 +13726,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Step 1: 'SPM28 Nusantara Product Launch' is not listed.
- Step 2: The event page opens with the 'Under review' badge, but shows no 'This request is waiting for your review' alert and no 'Review request' button.
- Step 3: A red alert 'You can't review this request' reads 'Only the coordinator assigned to this request can review it.' None of the request details and no 'Approve — planning can start' or 'Reject this request' options are shown.</t>
+          <t>Step 1: Neither 'SPM28 Straits Research Symposium' nor 'SPM28 Meridian Wealth Forum' is listed, even though Daniel Tan is their coordinator. Every listed event shows the 'Under review' badge.</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13736,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -13595,11 +13768,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Step 1: 'SPM28 Nusantara Product Launch' is not listed.
- Step 2: The event page opens with the 'Under review' badge, but shows no 'This request is waiting for your review' alert and no 'Review request' button.
- Step 3: A red alert 'You can't review this request' reads 'Only the coordinator assigned to this request can review it.' None of the request details and no 'Approve — planning can start' or 'Reject this request' options are shown.</t>
+      <c r="B11" s="36" t="inlineStr">
+        <is>
+          <t>Step 1: Neither 'SPM28 Straits Research Symposium' nor 'SPM28 Meridian Wealth Forum' is listed, even though Daniel Tan is their coordinator. Every listed event shows the 'Under review' badge.</t>
         </is>
       </c>
     </row>
@@ -13609,7 +13780,7 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13621,7 +13792,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -13645,7 +13816,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="21" t="n">
+      <c r="B15" s="31" t="n">
         <v>46295</v>
       </c>
     </row>
@@ -13664,11 +13835,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Step 1: 'SPM28 Nusantara Product Launch' is not listed.
- Step 2: The event page opens with the 'Under review' badge, but shows no 'This request is waiting for your review' alert and no 'Review request' button.
- Step 3: A red alert 'You can't review this request' reads 'Only the coordinator assigned to this request can review it.' None of the request details and no 'Approve — planning can start' or 'Reject this request' options are shown.</t>
+      <c r="B18" s="36" t="inlineStr">
+        <is>
+          <t>Step 1: Neither 'SPM28 Straits Research Symposium' nor 'SPM28 Meridian Wealth Forum' is listed, even though Daniel Tan is their coordinator. Every listed event shows the 'Under review' badge.</t>
         </is>
       </c>
     </row>
@@ -13678,7 +13847,7 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13690,7 +13859,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -13714,7 +13883,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B22" s="31" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -14730,13 +14899,13 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-28-TC04</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="71.25" customHeight="1" s="32">
+      <c r="B2" s="36" t="inlineStr">
+        <is>
+          <t>SPM-28-TC03</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="98.25" customHeight="1" s="32">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -14744,12 +14913,12 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>Logged out.
- Accounts: Grace Lim (grace.lim@connectsphere.com / password123), Event Operations Manager; Sari Widodo (sari.widodo@nusantaratec.com / password123), Event Organiser; Marcus Wong (marcus.wong@connectsphere.com / password123), Venue Staff.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="165.75" customHeight="1" s="32">
+          <t>Test data loaded: `npm run fixtures:spm28` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM28 …' events, EVT-000124 to EVT-000130, never anyone else's data).
+ Logged in as Priya Raj (priya.raj@connectsphere.com / password123), Event Coordinator not assigned to 'SPM28 Nusantara Product Launch' (its coordinator is Daniel Tan).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="84.75" customHeight="1" s="32">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -14757,15 +14926,9 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>1. Log in as Grace Lim
- 2. Check the sidebar for a 'Review Queue' link
- 3. Type /queue after the site address in the browser address bar (e.g. http://localhost:3000/queue) and press Enter
- 4. Log out and log in as Sari Widodo
- 5. Check the sidebar for a 'Review Queue' link
- 6. Type /queue after the site address in the browser address bar (e.g. http://localhost:3000/queue) and press Enter
- 7. Log out and log in as Marcus Wong
- 8. Check the sidebar for a 'Review Queue' link
- 9. Type /queue after the site address in the browser address bar (e.g. http://localhost:3000/queue) and press Enter</t>
+          <t>1. Click 'Review Queue' in the sidebar
+ 2. Click 'All Events' in the sidebar and open 'SPM28 Nusantara Product Launch'
+ 3. Type /events/EVT-000124/review after the site address in the browser address bar (e.g. http://localhost:3000/events/EVT-000124/review) and press Enter</t>
         </is>
       </c>
     </row>
@@ -14777,11 +14940,11 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Roles: Event Operations Manager, Event Organiser, Venue Staff</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="192.75" customHeight="1" s="32">
+          <t>Event: SPM28 Nusantara Product Launch (EVT-000124, coordinator Daniel Tan) | User: Priya Raj</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="111.75" customHeight="1" s="32">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -14789,15 +14952,9 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Step 1: The Dashboard opens.
- Step 2: No 'Review Queue' link is shown.
- Step 3: The refusal message 'Reviewing event requests is the Event Coordinator's role. You can still see events you are involved in from All Events.' is shown, and no list of requests.
- Step 4: The Dashboard opens.
- Step 5: No 'Review Queue' link is shown.
- Step 6: The same refusal message as step 3 is shown, and no list of requests.
- Step 7: The Dashboard opens.
- Step 8: No 'Review Queue' link is shown.
- Step 9: The same refusal message as step 3 is shown, and no list of requests.</t>
+          <t>Step 1: 'SPM28 Nusantara Product Launch' is not listed.
+ Step 2: The event page opens with the 'Under review' badge, but shows no 'This request is waiting for your review' alert and no 'Review request' button.
+ Step 3: A red alert 'You can't review this request' reads 'Only the coordinator assigned to this request can review it.' None of the request details and no 'Approve — planning can start' or 'Reject this request' options are shown.</t>
         </is>
       </c>
     </row>
@@ -14807,7 +14964,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -14839,17 +14996,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The Dashboard opens.
-Step 2: No 'Review Queue' link is shown.
-Step 3: The refusal message 'Reviewing event requests is the Event Coordinator's role. You can still see events you are involved in from All Events.' is shown, and no list of requests.
-Step 4: The Dashboard opens.
-Step 5: No 'Review Queue' link is shown.
-Step 6: The same refusal message as step 3 is shown, and no list of requests.
-Step 7: The Dashboard opens.
-Step 8: No 'Review Queue' link is shown.
-Step 9: The same refusal message as step 3 is shown, and no list of requests.</t>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Step 1: 'SPM28 Nusantara Product Launch' is not listed.
+ Step 2: The event page opens with the 'Under review' badge, but shows no 'This request is waiting for your review' alert and no 'Review request' button.
+ Step 3: A red alert 'You can't review this request' reads 'Only the coordinator assigned to this request can review it.' None of the request details and no 'Approve — planning can start' or 'Reject this request' options are shown.</t>
         </is>
       </c>
     </row>
@@ -14859,7 +15010,7 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14871,7 +15022,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -14895,7 +15046,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="21" t="n">
+      <c r="B15" s="31" t="n">
         <v>46295</v>
       </c>
     </row>
@@ -14914,17 +15065,11 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The Dashboard opens.
-Step 2: No 'Review Queue' link is shown.
-Step 3: The refusal message 'Reviewing event requests is the Event Coordinator's role. You can still see events you are involved in from All Events.' is shown, and no list of requests.
-Step 4: The Dashboard opens.
-Step 5: No 'Review Queue' link is shown.
-Step 6: The same refusal message as step 3 is shown, and no list of requests.
-Step 7: The Dashboard opens.
-Step 8: No 'Review Queue' link is shown.
-Step 9: The same refusal message as step 3 is shown, and no list of requests.</t>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Step 1: 'SPM28 Nusantara Product Launch' is not listed.
+ Step 2: The event page opens with the 'Under review' badge, but shows no 'This request is waiting for your review' alert and no 'Review request' button.
+ Step 3: A red alert 'You can't review this request' reads 'Only the coordinator assigned to this request can review it.' None of the request details and no 'Approve — planning can start' or 'Reject this request' options are shown.</t>
         </is>
       </c>
     </row>
@@ -14934,7 +15079,7 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14946,7 +15091,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -14970,7 +15115,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B22" s="31" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -15986,13 +16131,13 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-28-TC05</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="84.75" customHeight="1" s="32">
+      <c r="B2" s="36" t="inlineStr">
+        <is>
+          <t>SPM-28-TC04</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="71.25" customHeight="1" s="32">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -16000,12 +16145,12 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>Test data loaded: `npm run fixtures:spm28` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM28 …' events, EVT-000124 to EVT-000130, never anyone else's data).
- Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), Event Coordinator.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30.75" customHeight="1" s="32">
+          <t>Logged out.
+ Accounts: Grace Lim (grace.lim@connectsphere.com / password123), Event Operations Manager; Sari Widodo (sari.widodo@nusantaratec.com / password123), Event Organiser; Marcus Wong (marcus.wong@connectsphere.com / password123), Venue Staff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="165.75" customHeight="1" s="32">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -16013,12 +16158,19 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>1. Click 'Review Queue' in the sidebar
- 2. Click 'SPM28 Nusantara Product Launch'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="152.25" customHeight="1" s="32">
+          <t>1. Log in as Grace Lim
+ 2. Check the sidebar for a 'Review Queue' link
+ 3. Type /queue after the site address in the browser address bar (e.g. http://localhost:3000/queue) and press Enter
+ 4. Log out and log in as Sari Widodo
+ 5. Check the sidebar for a 'Review Queue' link
+ 6. Type /queue after the site address in the browser address bar (e.g. http://localhost:3000/queue) and press Enter
+ 7. Log out and log in as Marcus Wong
+ 8. Check the sidebar for a 'Review Queue' link
+ 9. Type /queue after the site address in the browser address bar (e.g. http://localhost:3000/queue) and press Enter</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30.75" customHeight="1" s="32">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -16026,11 +16178,11 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Event: SPM28 Nusantara Product Launch (EVT-000124) | Client: Nusantara Tech Labs | Organiser: Sari Widodo | Category: Exhibition | Purpose: Regional product launch and press event | Description: Press event with livestream and product demonstration area. | When: 17 Mar 2027, 15:00–19:00 | Expected attendance: 200 | Preferred layout: Theatre | Registration: Not enabled | Facilities: High-density WiFi (required), Raised stage (required), Livestream capability (required), Green room (nice-to-have) | Equipment: LED Video Wall Panel × 4, Streaming Encoder × 1 | Accessibility needs and Special requirements: left empty by the organiser</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="138.75" customHeight="1" s="32">
+          <t>Roles: Event Operations Manager, Event Organiser, Venue Staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="192.75" customHeight="1" s="32">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -16038,8 +16190,15 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Step 1: The Review Queue page opens and lists 'SPM28 Nusantara Product Launch'.
- Step 2: The 'Review request' page opens, with 'SPM28 Nusantara Product Launch' under the title and the 'Under review' badge. The 'What was requested' card shows every value in the test data next to its label, each facility followed by '(required)' or '(nice-to-have)', and each equipment item as 'name × quantity'. Accessibility needs and Special requirements show a 'Not provided' marker. No raw stored values (e.g. 'under_review', 'theatre') are shown.</t>
+          <t>Step 1: The Dashboard opens.
+ Step 2: No 'Review Queue' link is shown.
+ Step 3: The refusal message 'Reviewing event requests is the Event Coordinator's role. You can still see events you are involved in from All Events.' is shown, and no list of requests.
+ Step 4: The Dashboard opens.
+ Step 5: No 'Review Queue' link is shown.
+ Step 6: The same refusal message as step 3 is shown, and no list of requests.
+ Step 7: The Dashboard opens.
+ Step 8: No 'Review Queue' link is shown.
+ Step 9: The same refusal message as step 3 is shown, and no list of requests.</t>
         </is>
       </c>
     </row>
@@ -16049,7 +16208,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -16081,10 +16240,17 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The Review Queue page opens and lists 'SPM28 Nusantara Product Launch'.
-Step 2: The 'Review request' page opens, with 'SPM28 Nusantara Product Launch' under the title and the 'Under review' badge. The 'What was requested' card shows every value in the test data next to its label, each facility followed by '(required)' or '(nice-to-have)', and each equipment item as 'name × quantity'. Accessibility needs and Special requirements show a 'Not provided' marker. No raw stored values (e.g. 'under_review', 'theatre') are shown.</t>
+      <c r="B11" s="36" t="inlineStr">
+        <is>
+          <t>Step 1: The Dashboard opens.
+Step 2: No 'Review Queue' link is shown.
+Step 3: The refusal message 'Reviewing event requests is the Event Coordinator's role. You can still see events you are involved in from All Events.' is shown, and no list of requests.
+Step 4: The Dashboard opens.
+Step 5: No 'Review Queue' link is shown.
+Step 6: The same refusal message as step 3 is shown, and no list of requests.
+Step 7: The Dashboard opens.
+Step 8: No 'Review Queue' link is shown.
+Step 9: The same refusal message as step 3 is shown, and no list of requests.</t>
         </is>
       </c>
     </row>
@@ -16094,7 +16260,7 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16106,7 +16272,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -16130,7 +16296,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="21" t="n">
+      <c r="B15" s="31" t="n">
         <v>46295</v>
       </c>
     </row>
@@ -16149,10 +16315,17 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The Review Queue page opens and lists 'SPM28 Nusantara Product Launch'.
-Step 2: The 'Review request' page opens, with 'SPM28 Nusantara Product Launch' under the title and the 'Under review' badge. The 'What was requested' card shows every value in the test data next to its label, each facility followed by '(required)' or '(nice-to-have)', and each equipment item as 'name × quantity'. Accessibility needs and Special requirements show a 'Not provided' marker. No raw stored values (e.g. 'under_review', 'theatre') are shown.</t>
+      <c r="B18" s="36" t="inlineStr">
+        <is>
+          <t>Step 1: The Dashboard opens.
+Step 2: No 'Review Queue' link is shown.
+Step 3: The refusal message 'Reviewing event requests is the Event Coordinator's role. You can still see events you are involved in from All Events.' is shown, and no list of requests.
+Step 4: The Dashboard opens.
+Step 5: No 'Review Queue' link is shown.
+Step 6: The same refusal message as step 3 is shown, and no list of requests.
+Step 7: The Dashboard opens.
+Step 8: No 'Review Queue' link is shown.
+Step 9: The same refusal message as step 3 is shown, and no list of requests.</t>
         </is>
       </c>
     </row>
@@ -16162,7 +16335,7 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16174,7 +16347,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -16198,7 +16371,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B22" s="31" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -17214,13 +17387,13 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-28-TC06</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="125.25" customHeight="1" s="32">
+      <c r="B2" s="36" t="inlineStr">
+        <is>
+          <t>SPM-28-TC05</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="84.75" customHeight="1" s="32">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -17229,8 +17402,7 @@
       <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm28` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM28 …' events, EVT-000124 to EVT-000130, never anyone else's data).
- Logged in as Joel Fernandez (joel.fernandez@connectsphere.com / password123), Event Coordinator assigned to 'SPM28 Straits Journal Club' (Under review).
- The request has no description, accessibility needs, special requirements, facilities or equipment.</t>
+ Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), Event Coordinator.</t>
         </is>
       </c>
     </row>
@@ -17243,11 +17415,11 @@
       <c r="B4" s="9" t="inlineStr">
         <is>
           <t>1. Click 'Review Queue' in the sidebar
- 2. Click 'SPM28 Straits Journal Club'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="57.75" customHeight="1" s="32">
+ 2. Click 'SPM28 Nusantara Product Launch'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="152.25" customHeight="1" s="32">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -17255,11 +17427,11 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Event: SPM28 Straits Journal Club (EVT-000127) | Empty: Description, Accessibility needs, Special requirements, Facilities, Equipment | Filled: Purpose 'Monthly journal club', Expected attendance 30, Layout Boardroom</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="111.75" customHeight="1" s="32">
+          <t>Event: SPM28 Nusantara Product Launch (EVT-000124) | Client: Nusantara Tech Labs | Organiser: Sari Widodo | Category: Exhibition | Purpose: Regional product launch and press event | Description: Press event with livestream and product demonstration area. | When: 17 Mar 2027, 15:00–19:00 | Expected attendance: 200 | Preferred layout: Theatre | Registration: Not enabled | Facilities: High-density WiFi (required), Raised stage (required), Livestream capability (required), Green room (nice-to-have) | Equipment: LED Video Wall Panel × 4, Streaming Encoder × 1 | Accessibility needs and Special requirements: left empty by the organiser</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="138.75" customHeight="1" s="32">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -17267,8 +17439,8 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Step 1: The Review Queue page opens and lists 'SPM28 Straits Journal Club'.
- Step 2: A yellow alert 'Some information was not provided' lists 'Description, Accessibility needs, Special requirements, Facilities, Equipment'. In 'What was requested', each of those rows shows a 'Not provided' marker (not blank or hidden). Purpose shows 'Monthly journal club', Expected attendance shows 30 and Preferred layout shows 'Boardroom'.</t>
+          <t>Step 1: The Review Queue page opens and lists 'SPM28 Nusantara Product Launch'.
+ Step 2: The 'Review request' page opens, with 'SPM28 Nusantara Product Launch' under the title and the 'Under review' badge. The 'What was requested' card shows every value in the test data next to its label, each facility followed by '(required)' or '(nice-to-have)', and each equipment item as 'name × quantity'. Accessibility needs and Special requirements show a 'Not provided' marker. No raw stored values (e.g. 'under_review', 'theatre') are shown.</t>
         </is>
       </c>
     </row>
@@ -17278,7 +17450,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -17310,10 +17482,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The Review Queue page opens and lists 'SPM28 Straits Journal Club'.
-Step 2: A yellow alert 'Some information was not provided' lists 'Description, Accessibility needs, Special requirements, Facilities, Equipment'. In 'What was requested', each of those rows shows a 'Not provided' marker (not blank or hidden). Purpose shows 'Monthly journal club', Expected attendance shows 30 and Preferred layout shows 'Boardroom'.</t>
+      <c r="B11" s="36" t="inlineStr">
+        <is>
+          <t>Step 1: The Review Queue page opens and lists 'SPM28 Nusantara Product Launch'.
+Step 2: The 'Review request' page opens, with 'SPM28 Nusantara Product Launch' under the title and the 'Under review' badge. The 'What was requested' card shows every value in the test data next to its label, each facility followed by '(required)' or '(nice-to-have)', and each equipment item as 'name × quantity'. Accessibility needs and Special requirements show a 'Not provided' marker. No raw stored values (e.g. 'under_review', 'theatre') are shown.</t>
         </is>
       </c>
     </row>
@@ -17323,7 +17495,7 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17335,7 +17507,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -17359,7 +17531,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="21" t="n">
+      <c r="B15" s="31" t="n">
         <v>46295</v>
       </c>
     </row>
@@ -17378,10 +17550,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>Step 1: The Review Queue page opens and lists 'SPM28 Straits Journal Club'.
-Step 2: A yellow alert 'Some information was not provided' lists 'Description, Accessibility needs, Special requirements, Facilities, Equipment'. In 'What was requested', each of those rows shows a 'Not provided' marker (not blank or hidden). Purpose shows 'Monthly journal club', Expected attendance shows 30 and Preferred layout shows 'Boardroom'.</t>
+      <c r="B18" s="36" t="inlineStr">
+        <is>
+          <t>Step 1: The Review Queue page opens and lists 'SPM28 Nusantara Product Launch'.
+Step 2: The 'Review request' page opens, with 'SPM28 Nusantara Product Launch' under the title and the 'Under review' badge. The 'What was requested' card shows every value in the test data next to its label, each facility followed by '(required)' or '(nice-to-have)', and each equipment item as 'name × quantity'. Accessibility needs and Special requirements show a 'Not provided' marker. No raw stored values (e.g. 'under_review', 'theatre') are shown.</t>
         </is>
       </c>
     </row>
@@ -17391,7 +17563,7 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17403,7 +17575,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -17427,7 +17599,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B22" s="31" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -18443,9 +18615,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-28-TC07</t>
+      <c r="B2" s="36" t="inlineStr">
+        <is>
+          <t>SPM-28-TC06</t>
         </is>
       </c>
     </row>
@@ -18458,11 +18630,12 @@
       <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm28` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM28 …' events, EVT-000124 to EVT-000130, never anyone else's data).
- Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), coordinator of 'SPM28 Nusantara Product Launch' (Under review).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="71.25" customHeight="1" s="32">
+ Logged in as Joel Fernandez (joel.fernandez@connectsphere.com / password123), Event Coordinator assigned to 'SPM28 Straits Journal Club' (Under review).
+ The request has no description, accessibility needs, special requirements, facilities or equipment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30.75" customHeight="1" s="32">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -18470,12 +18643,12 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>1. Click 'All Events' in the sidebar and open 'SPM28 Nusantara Product Launch'
- 2. Click 'Review request' in the alert</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30.75" customHeight="1" s="32">
+          <t>1. Click 'Review Queue' in the sidebar
+ 2. Click 'SPM28 Straits Journal Club'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="57.75" customHeight="1" s="32">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -18483,11 +18656,11 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Event: SPM28 Nusantara Product Launch (EVT-000124) | User: Daniel Tan (assigned coordinator)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="98.25" customHeight="1" s="32">
+          <t>Event: SPM28 Straits Journal Club (EVT-000127) | Empty: Description, Accessibility needs, Special requirements, Facilities, Equipment | Filled: Purpose 'Monthly journal club', Expected attendance 30, Layout Boardroom</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="111.75" customHeight="1" s="32">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -18495,8 +18668,8 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Step 1: A blue alert 'This request is waiting for your review' with a 'Review request' button is shown above the Details card.
- Step 2: The 'Review request' page for 'SPM28 Nusantara Product Launch' opens with the 'Under review' badge and the 'Your decision' card.</t>
+          <t>Step 1: The Review Queue page opens and lists 'SPM28 Straits Journal Club'.
+ Step 2: A yellow alert 'Some information was not provided' lists 'Description, Accessibility needs, Special requirements, Facilities, Equipment'. In 'What was requested', each of those rows shows a 'Not provided' marker (not blank or hidden). Purpose shows 'Monthly journal club', Expected attendance shows 30 and Preferred layout shows 'Boardroom'.</t>
         </is>
       </c>
     </row>
@@ -18506,7 +18679,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -18538,10 +18711,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Step 1: A blue alert 'This request is waiting for your review' with a 'Review request' button is shown above the Details card.
- Step 2: The 'Review request' page for 'SPM28 Nusantara Product Launch' opens with the 'Under review' badge and the 'Your decision' card.</t>
+      <c r="B11" s="36" t="inlineStr">
+        <is>
+          <t>Step 1: The Review Queue page opens and lists 'SPM28 Straits Journal Club'.
+Step 2: A yellow alert 'Some information was not provided' lists 'Description, Accessibility needs, Special requirements, Facilities, Equipment'. In 'What was requested', each of those rows shows a 'Not provided' marker (not blank or hidden). Purpose shows 'Monthly journal club', Expected attendance shows 30 and Preferred layout shows 'Boardroom'.</t>
         </is>
       </c>
     </row>
@@ -18551,7 +18724,7 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18563,7 +18736,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -18575,7 +18748,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -18587,7 +18760,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="27" t="n">
+      <c r="B15" s="31" t="n">
         <v>46295</v>
       </c>
     </row>
@@ -18606,10 +18779,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Step 1: A blue alert 'This request is waiting for your review' with a 'Review request' button is shown above the Details card.
- Step 2: The 'Review request' page for 'SPM28 Nusantara Product Launch' opens with the 'Under review' badge and the 'Your decision' card.</t>
+      <c r="B18" s="36" t="inlineStr">
+        <is>
+          <t>Step 1: The Review Queue page opens and lists 'SPM28 Straits Journal Club'.
+Step 2: A yellow alert 'Some information was not provided' lists 'Description, Accessibility needs, Special requirements, Facilities, Equipment'. In 'What was requested', each of those rows shows a 'Not provided' marker (not blank or hidden). Purpose shows 'Monthly journal club', Expected attendance shows 30 and Preferred layout shows 'Boardroom'.</t>
         </is>
       </c>
     </row>
@@ -18619,7 +18792,7 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18631,7 +18804,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -18655,7 +18828,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B22" s="31" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -19671,13 +19844,13 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SPM-28-TC08</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="179.25" customHeight="1" s="32">
+      <c r="B2" s="36" t="inlineStr">
+        <is>
+          <t>SPM-28-TC07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="125.25" customHeight="1" s="32">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -19686,13 +19859,11 @@
       <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Test data loaded: `npm run fixtures:spm28` has been run from the project folder since the last full `npx prisma db seed` (it only touches the 'SPM28 …' events, EVT-000124 to EVT-000130, never anyone else's data).
- Before: run `npm run fixtures:spm28` so 'SPM28 Harbourline Client Seminar' is back to Under review.
- Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), coordinator of 'SPM28 Harbourline Client Seminar' (Under review).
- After: run `npm run fixtures:spm28` so the next tester starts from the same state. It deletes and recreates only the 'SPM28 …' events - do NOT run `npx prisma db seed`, which wipes everyone's data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="111.75" customHeight="1" s="32">
+ Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), coordinator of 'SPM28 Nusantara Product Launch' (Under review).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="71.25" customHeight="1" s="32">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -19700,17 +19871,12 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>1. Click 'Review Queue' in the sidebar
- 2. Click 'SPM28 Harbourline Client Seminar'
- 3. Select 'Approve — planning can start'
- 4. Click 'Approve request'
- 5. Click 'Approve' in the dialog
- 6. Click 'Review Queue' in the sidebar
- 7. Click 'All Events' in the sidebar and look for 'SPM28 Harbourline Client Seminar'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.25" customHeight="1" s="32">
+          <t>1. Click 'All Events' in the sidebar and open 'SPM28 Nusantara Product Launch'
+ 2. Click 'Review request' in the alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30.75" customHeight="1" s="32">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -19718,11 +19884,11 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Event: SPM28 Harbourline Client Seminar (EVT-000125) | Outcome: Approve</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="206.25" customHeight="1" s="32">
+          <t>Event: SPM28 Nusantara Product Launch (EVT-000124) | User: Daniel Tan (assigned coordinator)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="98.25" customHeight="1" s="32">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -19730,12 +19896,8 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Step 2: The 'Review request' page opens with the 'Under review' badge.
- Step 3: The option is highlighted and an 'Approve request' button is shown.
- Step 4: A dialog 'Approve this request?' appears, saying the event moves from Under review to Approved. The status has not changed yet.
- Step 5: A green 'Request approved' alert reads '"SPM28 Harbourline Client Seminar" is now Approved. Planning can start.' The status badge changes from 'Under review' to 'Approved' and the 'Your decision' card disappears.
- Step 6: 'SPM28 Harbourline Client Seminar' is no longer listed.
- Step 7: The event page shows the 'Approved' status badge, and no 'This request is waiting for your review' alert.</t>
+          <t>Step 1: A blue alert 'This request is waiting for your review' with a 'Review request' button is shown above the Details card.
+ Step 2: The 'Review request' page for 'SPM28 Nusantara Product Launch' opens with the 'Under review' badge and the 'Your decision' card.</t>
         </is>
       </c>
     </row>
@@ -19745,7 +19907,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -19779,12 +19941,8 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Step 2: The 'Review request' page opens with the 'Under review' badge.
- Step 3: The option is highlighted and an 'Approve request' button is shown.
- Step 4: A dialog 'Approve this request?' appears, saying the event moves from Under review to Approved. The status has not changed yet.
- Step 5: A green 'Request approved' alert reads '"SPM28 Harbourline Client Seminar" is now Approved. Planning can start.' The status badge changes from 'Under review' to 'Approved' and the 'Your decision' card disappears.
- Step 6: 'SPM28 Harbourline Client Seminar' is no longer listed.
- Step 7: The event page shows the 'Approved' status badge, and no 'This request is waiting for your review' alert.</t>
+          <t>Step 1: A blue alert 'This request is waiting for your review' with a 'Review request' button is shown above the Details card.
+ Step 2: The 'Review request' page for 'SPM28 Nusantara Product Launch' opens with the 'Under review' badge and the 'Your decision' card.</t>
         </is>
       </c>
     </row>
@@ -19851,12 +20009,8 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Step 2: The 'Review request' page opens with the 'Under review' badge.
- Step 3: The option is highlighted and an 'Approve request' button is shown.
- Step 4: A dialog 'Approve this request?' appears, saying the event moves from Under review to Approved. The status has not changed yet.
- Step 5: A green 'Request approved' alert reads '"SPM28 Harbourline Client Seminar" is now Approved. Planning can start.' The status badge changes from 'Under review' to 'Approved' and the 'Your decision' card disappears.
- Step 6: 'SPM28 Harbourline Client Seminar' is no longer listed.
- Step 7: The event page shows the 'Approved' status badge, and no 'This request is waiting for your review' alert.</t>
+          <t>Step 1: A blue alert 'This request is waiting for your review' with a 'Review request' button is shown above the Details card.
+ Step 2: The 'Review request' page for 'SPM28 Nusantara Product Launch' opens with the 'Under review' badge and the 'Your decision' card.</t>
         </is>
       </c>
     </row>
@@ -19866,7 +20020,7 @@
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -19878,7 +20032,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -19902,7 +20056,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B22" s="31" t="n">
         <v>46296</v>
       </c>
     </row>

--- a/docs/test-cases/SPM-28_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-28_Test_Cases.xlsx
@@ -31,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -63,6 +63,9 @@
     <font>
       <name val="Arial"/>
       <color theme="1"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
     </font>
   </fonts>
   <fills count="4">
@@ -159,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -254,6 +257,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -758,11 +764,15 @@
       </c>
       <c r="G7" s="36" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H7" s="36" t="n"/>
-      <c r="I7" s="36" t="n"/>
+      <c r="I7" s="36" t="inlineStr">
+        <is>
+          <t>Week 7 #5</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -16109,7 +16119,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="32" min="1" max="1"/>
@@ -16117,46 +16127,53 @@
     <col width="12.63" customWidth="1" style="32" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="32">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="32">
+      <c r="A1" s="39" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): The Event Operations Manager is now shown as the 'Event Coordinator Lead' (SPM-84 AC1, forum #129, Week 7 Change #5) - the same role, accounts, permissions and pages. Read 'Operations Manager', 'Event Operations Manager' or 'Ops Manager' in this case as 'Event Coordinator Lead'; on screen the role is shown under its new name, and refusals say 'Assigning coordinators is the Event Coordinator Lead's role.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="32">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="32">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="36" t="inlineStr">
-        <is>
-          <t>SPM-28-TC04</t>
-        </is>
-      </c>
+      <c r="B2" s="3" t="n"/>
     </row>
     <row r="3" ht="71.25" customHeight="1" s="32">
       <c r="A3" s="5" t="inlineStr">
         <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B3" s="36" t="inlineStr">
+        <is>
+          <t>SPM-28-TC04</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="165.75" customHeight="1" s="32">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Logged out.
  Accounts: Grace Lim (grace.lim@connectsphere.com / password123), Event Operations Manager; Sari Widodo (sari.widodo@nusantaratec.com / password123), Event Organiser; Marcus Wong (marcus.wong@connectsphere.com / password123), Venue Staff.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="165.75" customHeight="1" s="32">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="5" ht="30.75" customHeight="1" s="32">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>1. Log in as Grace Lim
  2. Check the sidebar for a 'Review Queue' link
@@ -16170,25 +16187,25 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30.75" customHeight="1" s="32">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Roles: Event Operations Manager, Event Organiser, Venue Staff</t>
-        </is>
-      </c>
-    </row>
     <row r="6" ht="192.75" customHeight="1" s="32">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Roles: Event Operations Manager, Event Organiser, Venue Staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" s="32">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Step 1: The Dashboard opens.
  Step 2: No 'Review Queue' link is shown.
@@ -16202,45 +16219,45 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="32">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="36" t="inlineStr">
-        <is>
-          <t>Kristen</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="15.75" customHeight="1" s="32">
       <c r="A8" s="5" t="inlineStr">
         <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="36" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="32">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B9" s="12" t="n">
         <v>46295</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="32"/>
-    <row r="10" ht="15.75" customHeight="1" s="32">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="32"/>
+    <row r="11" ht="15.75" customHeight="1" s="32">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="15" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="32">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="15" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="32">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>Step 1: The Dashboard opens.
 Step 2: No 'Review Queue' link is shown.
@@ -16254,68 +16271,68 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="32">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="28" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="15.75" customHeight="1" s="32">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="29" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="32">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>Kristen</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="32">
       <c r="A15" s="17" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="32">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="31" t="n">
+      <c r="B16" s="31" t="n">
         <v>46295</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="32"/>
-    <row r="17" ht="15.75" customHeight="1" s="32">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="17" ht="15.75" customHeight="1" s="32"/>
+    <row r="18" ht="15.75" customHeight="1" s="32">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="32">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="B18" s="14" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="32">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="36" t="inlineStr">
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t>Step 1: The Dashboard opens.
 Step 2: No 'Review Queue' link is shown.
@@ -16329,53 +16346,52 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="32">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="28" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="15.75" customHeight="1" s="32">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B20" s="29" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B20" s="28" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="32">
       <c r="A21" s="17" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>Sammi</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B21" s="29" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="32">
       <c r="A22" s="17" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>Sammi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="32">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="31" t="n">
+      <c r="B23" s="31" t="n">
         <v>46296</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="32"/>
     <row r="24" ht="15.75" customHeight="1" s="32"/>
     <row r="25" ht="15.75" customHeight="1" s="32"/>
     <row r="26" ht="15.75" customHeight="1" s="32"/>
@@ -17354,6 +17370,9 @@
     <row r="999" ht="15.75" customHeight="1" s="32"/>
     <row r="1000" ht="15.75" customHeight="1" s="32"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
